--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D325F8D9-5DB8-4230-B057-035682FD1491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AF3AC5-BA51-4464-A8AD-078CE6583EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -397,960 +397,961 @@
     <t>3551102:1</t>
   </si>
   <si>
+    <t>3551301:1</t>
+  </si>
+  <si>
+    <t>3041101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高</t>
+  </si>
+  <si>
+    <t>攻击提高</t>
+  </si>
+  <si>
+    <t>防御提高</t>
+  </si>
+  <si>
+    <t>生命提高</t>
+  </si>
+  <si>
+    <t>击中回血效果提高</t>
+  </si>
+  <si>
+    <t>暴击几率提高</t>
+  </si>
+  <si>
+    <t>暴击伤害提高</t>
+  </si>
+  <si>
+    <t>伤害提高</t>
+  </si>
+  <si>
+    <t>受到伤害提高</t>
+  </si>
+  <si>
+    <t>持续伤害提高</t>
+  </si>
+  <si>
+    <t>受到持续伤害提高</t>
+  </si>
+  <si>
+    <t>attr_value_7_variable_id</t>
+  </si>
+  <si>
+    <t>attr_value_7_type</t>
+  </si>
+  <si>
+    <t>attr_value_7</t>
+  </si>
+  <si>
+    <t>参数7关联的变量id</t>
+  </si>
+  <si>
+    <t>参数7数值类型</t>
+  </si>
+  <si>
+    <t>参数7</t>
+  </si>
+  <si>
+    <t>移动速度提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3540201:1</t>
+  </si>
+  <si>
+    <t>3540401:1</t>
+  </si>
+  <si>
+    <t>3540402:1</t>
+  </si>
+  <si>
+    <t>3540601:1</t>
+  </si>
+  <si>
+    <t>3540602:1</t>
+  </si>
+  <si>
+    <t>3540801:1</t>
+  </si>
+  <si>
+    <t>3540802:1</t>
+  </si>
+  <si>
+    <t>3541001:1</t>
+  </si>
+  <si>
+    <t>3541002:1</t>
+  </si>
+  <si>
+    <t>3541201:1</t>
+  </si>
+  <si>
+    <t>3541401:1</t>
+  </si>
+  <si>
+    <t>3541601:1</t>
+  </si>
+  <si>
+    <t>3541602:1</t>
+  </si>
+  <si>
+    <t>3541801:1</t>
+  </si>
+  <si>
+    <t>3541802:1</t>
+  </si>
+  <si>
+    <t>3542001:1</t>
+  </si>
+  <si>
+    <t>3542002:1</t>
+  </si>
+  <si>
+    <t>3542201:1</t>
+  </si>
+  <si>
+    <t>3542202:1</t>
+  </si>
+  <si>
+    <t>3542401:1</t>
+  </si>
+  <si>
+    <t>3540205:1</t>
+  </si>
+  <si>
+    <t>3540207:1</t>
+  </si>
+  <si>
+    <t>3540405:1</t>
+  </si>
+  <si>
+    <t>3540407:1</t>
+  </si>
+  <si>
+    <t>3540605:1</t>
+  </si>
+  <si>
+    <t>3540607:1</t>
+  </si>
+  <si>
+    <t>3540805:1</t>
+  </si>
+  <si>
+    <t>3540807:1</t>
+  </si>
+  <si>
+    <t>3541005:1</t>
+  </si>
+  <si>
+    <t>3541007:1</t>
+  </si>
+  <si>
+    <t>3541205:1</t>
+  </si>
+  <si>
+    <t>3541207:1</t>
+  </si>
+  <si>
+    <t>3541405:1</t>
+  </si>
+  <si>
+    <t>3541407:1</t>
+  </si>
+  <si>
+    <t>3541605:1</t>
+  </si>
+  <si>
+    <t>3541607:1</t>
+  </si>
+  <si>
+    <t>3541805:1</t>
+  </si>
+  <si>
+    <t>3541807:1</t>
+  </si>
+  <si>
+    <t>3542005:1</t>
+  </si>
+  <si>
+    <t>3542007:1</t>
+  </si>
+  <si>
+    <t>3542205:1</t>
+  </si>
+  <si>
+    <t>3542207:1</t>
+  </si>
+  <si>
+    <t>3542405:1</t>
+  </si>
+  <si>
+    <t>3542407:1</t>
+  </si>
+  <si>
+    <t>3551302:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3551501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重冰霜新星</t>
+  </si>
+  <si>
+    <t>冰霜新星造成冰冻几率提高</t>
+  </si>
+  <si>
+    <t>冰冻时受到冰元素伤害</t>
+  </si>
+  <si>
+    <t>释放冰霜新星时，对敌人造成的冰冻几率增加【参数1万分比】</t>
+  </si>
+  <si>
+    <t>双重冰冻造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰冻命中造成额外伤害</t>
+  </si>
+  <si>
+    <t>击中冰冻目标造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰霜新星额外冰冻几率</t>
+  </si>
+  <si>
+    <t>攻击次数触发冰霜新星</t>
+  </si>
+  <si>
+    <t>攻击使目标冰冻</t>
+  </si>
+  <si>
+    <t>3550902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>攻击提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>防御提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>生命提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>击中回血效果提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>暴击几率提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>暴击伤害提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>受到伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>受到持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>移动速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>获取护盾提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>全属性伤害提高</t>
+  </si>
+  <si>
+    <t>受到全属性伤害提高</t>
+  </si>
+  <si>
+    <t>全属性持续伤害提高</t>
+  </si>
+  <si>
+    <t>受到全属性持续伤害提高</t>
+  </si>
+  <si>
+    <t>移动速度提高</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+  </si>
+  <si>
+    <t>技能效果-通用</t>
+  </si>
+  <si>
+    <t>技能效果-冰</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒死亡释放瘟疫</t>
+  </si>
+  <si>
+    <t>瘟疫状态</t>
+  </si>
+  <si>
+    <t>技能效果-火</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-电</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-毒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动释放陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧状态受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石造成燃烧命中率增加</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时死亡触发死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链弹射效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发触电伤害时释放电磁爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560201:1</t>
+  </si>
+  <si>
+    <t>3560202:1</t>
+  </si>
+  <si>
+    <t>3560205:1</t>
+  </si>
+  <si>
+    <t>3560206:1</t>
+  </si>
+  <si>
+    <t>3560501:2</t>
+  </si>
+  <si>
+    <t>3560502:1</t>
+  </si>
+  <si>
+    <t>3560503:1</t>
+  </si>
+  <si>
+    <t>3560701:1</t>
+  </si>
+  <si>
+    <t>3560901:1</t>
+  </si>
+  <si>
+    <t>3570201:1</t>
+  </si>
+  <si>
+    <t>3570202:1</t>
+  </si>
+  <si>
+    <t>3570501:1</t>
+  </si>
+  <si>
+    <t>3570502:1</t>
+  </si>
+  <si>
+    <t>3570701:2</t>
+  </si>
+  <si>
+    <t>3570702:1</t>
+  </si>
+  <si>
+    <t>3570703:1</t>
+  </si>
+  <si>
+    <t>3570901:1</t>
+  </si>
+  <si>
+    <t>3571101:1</t>
+  </si>
+  <si>
+    <t>3571102:1</t>
+  </si>
+  <si>
+    <t>3571103:1</t>
+  </si>
+  <si>
+    <t>3580201:1</t>
+  </si>
+  <si>
+    <t>3580202:1</t>
+  </si>
+  <si>
+    <t>3580207:1</t>
+  </si>
+  <si>
+    <t>3580501:2</t>
+  </si>
+  <si>
+    <t>3580502:1</t>
+  </si>
+  <si>
+    <t>3580503:1</t>
+  </si>
+  <si>
+    <t>3580701:1</t>
+  </si>
+  <si>
+    <t>3580902:1</t>
+  </si>
+  <si>
+    <t>3580903:1</t>
+  </si>
+  <si>
+    <t>3561102:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561103:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>每【参数1】次攻击，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>燃烧时，受到全种类攻击承受伤害提高【参数1万分比】</t>
+  </si>
+  <si>
+    <t>陨石造成伤害时，燃烧效果的命中率提升【参数1万分比】</t>
+  </si>
+  <si>
+    <t>燃烧时，死亡，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>每次受到攻击会额外受到等同于[电元素最终伤害]【参数1万分比】</t>
+  </si>
+  <si>
+    <t>闪电链可弹射【参数1】次，同1个目标最多可被选择【参数2】次，每次弹射造成的伤害降低第1次命中造成伤害的【参数3万分比】</t>
+  </si>
+  <si>
+    <t>触电时，触发触电伤害，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>【瘟疫：附近任意目标施加瘟疫状态。】</t>
+  </si>
+  <si>
+    <t>3571302:1</t>
+  </si>
+  <si>
+    <t>3571303:1</t>
+  </si>
+  <si>
+    <t>技能效果-生存</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>损失血量触发获得护盾</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时触发技能受到全属性伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发额外回血</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外回复击回X倍的血量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值大于等于百万分比时触发技能触发全属性伤害提升</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值低于百万分比时触发技能触发受到全属性伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时触发技能复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-范围</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放技能多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击效果，额外造成X次X%的伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩触发释放半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600201:2</t>
+  </si>
+  <si>
+    <t>3600202:1</t>
+  </si>
+  <si>
+    <t>3600203:1</t>
+  </si>
+  <si>
+    <t>3600401:1</t>
+  </si>
+  <si>
+    <t>3600402:1</t>
+  </si>
+  <si>
+    <t>3600702:1</t>
+  </si>
+  <si>
+    <t>3600703:1</t>
+  </si>
+  <si>
+    <t>3601002:1</t>
+  </si>
+  <si>
+    <t>3601003:1</t>
+  </si>
+  <si>
+    <t>3601301:1</t>
+  </si>
+  <si>
+    <t>3601302:1</t>
+  </si>
+  <si>
+    <t>3601303:1</t>
+  </si>
+  <si>
+    <t>3610301:1</t>
+  </si>
+  <si>
+    <t>3610302:1</t>
+  </si>
+  <si>
+    <t>3610303:1</t>
+  </si>
+  <si>
+    <t>3610501:1</t>
+  </si>
+  <si>
+    <t>3610702:1</t>
+  </si>
+  <si>
+    <t>3610703:1</t>
+  </si>
+  <si>
+    <t>3590201:1</t>
+  </si>
+  <si>
+    <t>3590202:1</t>
+  </si>
+  <si>
+    <t>3590203:1</t>
+  </si>
+  <si>
+    <t>3590401:1</t>
+  </si>
+  <si>
+    <t>3590602:1</t>
+  </si>
+  <si>
+    <t>3590603:1</t>
+  </si>
+  <si>
+    <t>3590802:1</t>
+  </si>
+  <si>
+    <t>3590803:1</t>
+  </si>
+  <si>
+    <t>3591001:1</t>
+  </si>
+  <si>
+    <t>3591201:1</t>
+  </si>
+  <si>
+    <t>3591202:1</t>
+  </si>
+  <si>
+    <t>3591203:1</t>
+  </si>
+  <si>
+    <t>3591401:1</t>
+  </si>
+  <si>
+    <t>3591402:1</t>
+  </si>
+  <si>
+    <t>3591403:1</t>
+  </si>
+  <si>
+    <t>3591602:1</t>
+  </si>
+  <si>
+    <t>3591603:1</t>
+  </si>
+  <si>
+    <t>3591902:1</t>
+  </si>
+  <si>
+    <t>3600701:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数触发技能重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击技能暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能攻击累计额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀暴击触发斩杀血线变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590802:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3610901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611303:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611502:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611503:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590803:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名称</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数描述</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>低血时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-光环效果影响范围变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标血量低于百万分比触发斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀血线提高效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581202:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581207:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_value_8_variable_id</t>
+  </si>
+  <si>
+    <t>attr_value_8_type</t>
+  </si>
+  <si>
+    <t>attr_value_8</t>
+  </si>
+  <si>
+    <t>参数8关联的变量id</t>
+  </si>
+  <si>
+    <t>参数8数值类型</t>
+  </si>
+  <si>
+    <t>参数8</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>3041108:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591002:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591003:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+  </si>
+  <si>
+    <t>3570503:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
+  </si>
+  <si>
+    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
+  </si>
+  <si>
+    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
+  </si>
+  <si>
+    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时造成额外伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒受到额外中毒伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580702:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活回复血量、触发次数、触发间隔</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591908:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561401:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561402:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561408:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590405:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命暴击状态攻速提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回血效果提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
     <t>3551103:2</t>
-  </si>
-  <si>
-    <t>3551301:1</t>
-  </si>
-  <si>
-    <t>3041101:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高</t>
-  </si>
-  <si>
-    <t>攻击提高</t>
-  </si>
-  <si>
-    <t>防御提高</t>
-  </si>
-  <si>
-    <t>生命提高</t>
-  </si>
-  <si>
-    <t>击中回血效果提高</t>
-  </si>
-  <si>
-    <t>暴击几率提高</t>
-  </si>
-  <si>
-    <t>暴击伤害提高</t>
-  </si>
-  <si>
-    <t>伤害提高</t>
-  </si>
-  <si>
-    <t>受到伤害提高</t>
-  </si>
-  <si>
-    <t>持续伤害提高</t>
-  </si>
-  <si>
-    <t>受到持续伤害提高</t>
-  </si>
-  <si>
-    <t>attr_value_7_variable_id</t>
-  </si>
-  <si>
-    <t>attr_value_7_type</t>
-  </si>
-  <si>
-    <t>attr_value_7</t>
-  </si>
-  <si>
-    <t>参数7关联的变量id</t>
-  </si>
-  <si>
-    <t>参数7数值类型</t>
-  </si>
-  <si>
-    <t>参数7</t>
-  </si>
-  <si>
-    <t>移动速度提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3540201:1</t>
-  </si>
-  <si>
-    <t>3540401:1</t>
-  </si>
-  <si>
-    <t>3540402:1</t>
-  </si>
-  <si>
-    <t>3540601:1</t>
-  </si>
-  <si>
-    <t>3540602:1</t>
-  </si>
-  <si>
-    <t>3540801:1</t>
-  </si>
-  <si>
-    <t>3540802:1</t>
-  </si>
-  <si>
-    <t>3541001:1</t>
-  </si>
-  <si>
-    <t>3541002:1</t>
-  </si>
-  <si>
-    <t>3541201:1</t>
-  </si>
-  <si>
-    <t>3541401:1</t>
-  </si>
-  <si>
-    <t>3541601:1</t>
-  </si>
-  <si>
-    <t>3541602:1</t>
-  </si>
-  <si>
-    <t>3541801:1</t>
-  </si>
-  <si>
-    <t>3541802:1</t>
-  </si>
-  <si>
-    <t>3542001:1</t>
-  </si>
-  <si>
-    <t>3542002:1</t>
-  </si>
-  <si>
-    <t>3542201:1</t>
-  </si>
-  <si>
-    <t>3542202:1</t>
-  </si>
-  <si>
-    <t>3542401:1</t>
-  </si>
-  <si>
-    <t>3540205:1</t>
-  </si>
-  <si>
-    <t>3540207:1</t>
-  </si>
-  <si>
-    <t>3540405:1</t>
-  </si>
-  <si>
-    <t>3540407:1</t>
-  </si>
-  <si>
-    <t>3540605:1</t>
-  </si>
-  <si>
-    <t>3540607:1</t>
-  </si>
-  <si>
-    <t>3540805:1</t>
-  </si>
-  <si>
-    <t>3540807:1</t>
-  </si>
-  <si>
-    <t>3541005:1</t>
-  </si>
-  <si>
-    <t>3541007:1</t>
-  </si>
-  <si>
-    <t>3541205:1</t>
-  </si>
-  <si>
-    <t>3541207:1</t>
-  </si>
-  <si>
-    <t>3541405:1</t>
-  </si>
-  <si>
-    <t>3541407:1</t>
-  </si>
-  <si>
-    <t>3541605:1</t>
-  </si>
-  <si>
-    <t>3541607:1</t>
-  </si>
-  <si>
-    <t>3541805:1</t>
-  </si>
-  <si>
-    <t>3541807:1</t>
-  </si>
-  <si>
-    <t>3542005:1</t>
-  </si>
-  <si>
-    <t>3542007:1</t>
-  </si>
-  <si>
-    <t>3542205:1</t>
-  </si>
-  <si>
-    <t>3542207:1</t>
-  </si>
-  <si>
-    <t>3542405:1</t>
-  </si>
-  <si>
-    <t>3542407:1</t>
-  </si>
-  <si>
-    <t>3551302:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3551501:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重冰霜新星</t>
-  </si>
-  <si>
-    <t>冰霜新星造成冰冻几率提高</t>
-  </si>
-  <si>
-    <t>冰冻时受到冰元素伤害</t>
-  </si>
-  <si>
-    <t>释放冰霜新星时，对敌人造成的冰冻几率增加【参数1万分比】</t>
-  </si>
-  <si>
-    <t>双重冰冻造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰冻命中造成额外伤害</t>
-  </si>
-  <si>
-    <t>击中冰冻目标造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰霜新星额外冰冻几率</t>
-  </si>
-  <si>
-    <t>攻击次数触发冰霜新星</t>
-  </si>
-  <si>
-    <t>攻击使目标冰冻</t>
-  </si>
-  <si>
-    <t>3550902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>攻击提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>防御提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>生命提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>击中回血效果提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>暴击几率提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>暴击伤害提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>受到伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>受到持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>移动速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>获取护盾提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>全属性伤害提高</t>
-  </si>
-  <si>
-    <t>受到全属性伤害提高</t>
-  </si>
-  <si>
-    <t>全属性持续伤害提高</t>
-  </si>
-  <si>
-    <t>受到全属性持续伤害提高</t>
-  </si>
-  <si>
-    <t>移动速度提高</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-  </si>
-  <si>
-    <t>技能效果-通用</t>
-  </si>
-  <si>
-    <t>技能效果-冰</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒死亡释放瘟疫</t>
-  </si>
-  <si>
-    <t>瘟疫状态</t>
-  </si>
-  <si>
-    <t>技能效果-火</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-电</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-毒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动释放陨石</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧状态受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石造成燃烧命中率增加</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时死亡触发死亡爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链弹射效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放闪电链</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发触电伤害时释放电磁爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发传染</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560201:1</t>
-  </si>
-  <si>
-    <t>3560202:1</t>
-  </si>
-  <si>
-    <t>3560205:1</t>
-  </si>
-  <si>
-    <t>3560206:1</t>
-  </si>
-  <si>
-    <t>3560501:2</t>
-  </si>
-  <si>
-    <t>3560502:1</t>
-  </si>
-  <si>
-    <t>3560503:1</t>
-  </si>
-  <si>
-    <t>3560701:1</t>
-  </si>
-  <si>
-    <t>3560901:1</t>
-  </si>
-  <si>
-    <t>3570201:1</t>
-  </si>
-  <si>
-    <t>3570202:1</t>
-  </si>
-  <si>
-    <t>3570501:1</t>
-  </si>
-  <si>
-    <t>3570502:1</t>
-  </si>
-  <si>
-    <t>3570701:2</t>
-  </si>
-  <si>
-    <t>3570702:1</t>
-  </si>
-  <si>
-    <t>3570703:1</t>
-  </si>
-  <si>
-    <t>3570901:1</t>
-  </si>
-  <si>
-    <t>3571101:1</t>
-  </si>
-  <si>
-    <t>3571102:1</t>
-  </si>
-  <si>
-    <t>3571103:1</t>
-  </si>
-  <si>
-    <t>3580201:1</t>
-  </si>
-  <si>
-    <t>3580202:1</t>
-  </si>
-  <si>
-    <t>3580207:1</t>
-  </si>
-  <si>
-    <t>3580501:2</t>
-  </si>
-  <si>
-    <t>3580502:1</t>
-  </si>
-  <si>
-    <t>3580503:1</t>
-  </si>
-  <si>
-    <t>3580701:1</t>
-  </si>
-  <si>
-    <t>3580902:1</t>
-  </si>
-  <si>
-    <t>3580903:1</t>
-  </si>
-  <si>
-    <t>3561102:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561103:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>每【参数1】次攻击，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>燃烧时，受到全种类攻击承受伤害提高【参数1万分比】</t>
-  </si>
-  <si>
-    <t>陨石造成伤害时，燃烧效果的命中率提升【参数1万分比】</t>
-  </si>
-  <si>
-    <t>燃烧时，死亡，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>每次受到攻击会额外受到等同于[电元素最终伤害]【参数1万分比】</t>
-  </si>
-  <si>
-    <t>闪电链可弹射【参数1】次，同1个目标最多可被选择【参数2】次，每次弹射造成的伤害降低第1次命中造成伤害的【参数3万分比】</t>
-  </si>
-  <si>
-    <t>触电时，触发触电伤害，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>【瘟疫：附近任意目标施加瘟疫状态。】</t>
-  </si>
-  <si>
-    <t>3571302:1</t>
-  </si>
-  <si>
-    <t>3571303:1</t>
-  </si>
-  <si>
-    <t>技能效果-生存</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>损失血量触发获得护盾</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时触发技能受到全属性伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发额外回血</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外回复击回X倍的血量</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值大于等于百万分比时触发技能触发全属性伤害提升</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值低于百万分比时触发技能触发受到全属性伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时触发技能复活</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-范围</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放技能多重打击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重打击效果，额外造成X次X%的伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放旋风斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋风斩触发释放半月斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600201:2</t>
-  </si>
-  <si>
-    <t>3600202:1</t>
-  </si>
-  <si>
-    <t>3600203:1</t>
-  </si>
-  <si>
-    <t>3600401:1</t>
-  </si>
-  <si>
-    <t>3600402:1</t>
-  </si>
-  <si>
-    <t>3600702:1</t>
-  </si>
-  <si>
-    <t>3600703:1</t>
-  </si>
-  <si>
-    <t>3601002:1</t>
-  </si>
-  <si>
-    <t>3601003:1</t>
-  </si>
-  <si>
-    <t>3601301:1</t>
-  </si>
-  <si>
-    <t>3601302:1</t>
-  </si>
-  <si>
-    <t>3601303:1</t>
-  </si>
-  <si>
-    <t>3610301:1</t>
-  </si>
-  <si>
-    <t>3610302:1</t>
-  </si>
-  <si>
-    <t>3610303:1</t>
-  </si>
-  <si>
-    <t>3610501:1</t>
-  </si>
-  <si>
-    <t>3610702:1</t>
-  </si>
-  <si>
-    <t>3610703:1</t>
-  </si>
-  <si>
-    <t>3590201:1</t>
-  </si>
-  <si>
-    <t>3590202:1</t>
-  </si>
-  <si>
-    <t>3590203:1</t>
-  </si>
-  <si>
-    <t>3590401:1</t>
-  </si>
-  <si>
-    <t>3590602:1</t>
-  </si>
-  <si>
-    <t>3590603:1</t>
-  </si>
-  <si>
-    <t>3590802:1</t>
-  </si>
-  <si>
-    <t>3590803:1</t>
-  </si>
-  <si>
-    <t>3591001:1</t>
-  </si>
-  <si>
-    <t>3591201:1</t>
-  </si>
-  <si>
-    <t>3591202:1</t>
-  </si>
-  <si>
-    <t>3591203:1</t>
-  </si>
-  <si>
-    <t>3591401:1</t>
-  </si>
-  <si>
-    <t>3591402:1</t>
-  </si>
-  <si>
-    <t>3591403:1</t>
-  </si>
-  <si>
-    <t>3591602:1</t>
-  </si>
-  <si>
-    <t>3591603:1</t>
-  </si>
-  <si>
-    <t>3591902:1</t>
-  </si>
-  <si>
-    <t>3600701:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数触发技能重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击技能暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能攻击累计额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀暴击触发斩杀血线变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590802:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3610901:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611301:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611303:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611701:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611502:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611503:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590803:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名称</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数描述</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>低血时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-光环效果影响范围变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标血量低于百万分比触发斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀血线提高效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581201:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581202:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581207:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>attr_value_8_variable_id</t>
-  </si>
-  <si>
-    <t>attr_value_8_type</t>
-  </si>
-  <si>
-    <t>attr_value_8</t>
-  </si>
-  <si>
-    <t>参数8关联的变量id</t>
-  </si>
-  <si>
-    <t>参数8数值类型</t>
-  </si>
-  <si>
-    <t>参数8</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>3041108:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591002:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591003:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-  </si>
-  <si>
-    <t>3570503:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
-  </si>
-  <si>
-    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
-  </si>
-  <si>
-    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
-  </si>
-  <si>
-    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时造成额外伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒受到额外中毒伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580702:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活回复血量、触发次数、触发间隔</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591908:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561401:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561402:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561408:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590405:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命暴击状态攻速提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3592101:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回血效果提高</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2116,13 +2117,13 @@
         <v>65</v>
       </c>
       <c r="AA2" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="AB2" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>328</v>
-      </c>
       <c r="AC2" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
@@ -2196,22 +2197,22 @@
         <v>24</v>
       </c>
       <c r="X3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y3" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Z3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="Z3" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="AA3" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="AB3" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>330</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
@@ -2231,16 +2232,16 @@
         <v>64</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>30</v>
@@ -2285,22 +2286,22 @@
         <v>41</v>
       </c>
       <c r="X4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y4" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="Z4" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="AA4" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="AB4" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AC4" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="AC4" s="7" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
@@ -2418,10 +2419,10 @@
         <v>47</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K6" s="6">
         <v>1</v>
@@ -2472,7 +2473,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AB6" s="6">
         <v>1</v>
@@ -2498,19 +2499,19 @@
         <v>3540200</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K7" s="15">
         <v>2</v>
@@ -2540,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U7" s="15">
         <v>4000</v>
@@ -2552,7 +2553,7 @@
         <v>10000</v>
       </c>
       <c r="X7" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Y7" s="15">
         <v>1</v>
@@ -2587,19 +2588,19 @@
         <v>3540400</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K8" s="15">
         <v>2</v>
@@ -2608,7 +2609,7 @@
         <v>500</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="N8" s="15">
         <v>1</v>
@@ -2629,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="U8" s="15">
         <v>4000</v>
@@ -2641,7 +2642,7 @@
         <v>10000</v>
       </c>
       <c r="X8" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Y8" s="15">
         <v>1</v>
@@ -2676,19 +2677,19 @@
         <v>3540600</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K9" s="15">
         <v>2</v>
@@ -2697,7 +2698,7 @@
         <v>500</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N9" s="15">
         <v>1</v>
@@ -2718,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U9" s="15">
         <v>4000</v>
@@ -2730,7 +2731,7 @@
         <v>10000</v>
       </c>
       <c r="X9" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Y9" s="15">
         <v>1</v>
@@ -2765,19 +2766,19 @@
         <v>3540800</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K10" s="15">
         <v>3</v>
@@ -2786,7 +2787,7 @@
         <v>50000</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N10" s="15">
         <v>1</v>
@@ -2807,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="T10" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U10" s="15">
         <v>4000</v>
@@ -2819,7 +2820,7 @@
         <v>10000</v>
       </c>
       <c r="X10" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Y10" s="15">
         <v>1</v>
@@ -2854,19 +2855,19 @@
         <v>3541000</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K11" s="15">
         <v>2</v>
@@ -2875,7 +2876,7 @@
         <v>500</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N11" s="15">
         <v>1</v>
@@ -2896,7 +2897,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="U11" s="15">
         <v>4000</v>
@@ -2908,7 +2909,7 @@
         <v>10000</v>
       </c>
       <c r="X11" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Y11" s="15">
         <v>1</v>
@@ -2943,19 +2944,19 @@
         <v>3541200</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K12" s="15">
         <v>2</v>
@@ -2985,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="T12" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="U12" s="15">
         <v>4000</v>
@@ -2997,7 +2998,7 @@
         <v>10000</v>
       </c>
       <c r="X12" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="Y12" s="15">
         <v>1</v>
@@ -3032,19 +3033,19 @@
         <v>3541400</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K13" s="15">
         <v>2</v>
@@ -3074,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U13" s="15">
         <v>4000</v>
@@ -3086,7 +3087,7 @@
         <v>10000</v>
       </c>
       <c r="X13" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Y13" s="15">
         <v>1</v>
@@ -3121,19 +3122,19 @@
         <v>3541600</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K14" s="15">
         <v>2</v>
@@ -3142,7 +3143,7 @@
         <v>500</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N14" s="15">
         <v>1</v>
@@ -3163,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U14" s="15">
         <v>4000</v>
@@ -3175,7 +3176,7 @@
         <v>10000</v>
       </c>
       <c r="X14" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Y14" s="15">
         <v>1</v>
@@ -3210,19 +3211,19 @@
         <v>3541800</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K15" s="15">
         <v>2</v>
@@ -3231,7 +3232,7 @@
         <v>500</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N15" s="15">
         <v>1</v>
@@ -3252,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="U15" s="15">
         <v>4000</v>
@@ -3264,7 +3265,7 @@
         <v>10000</v>
       </c>
       <c r="X15" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y15" s="15">
         <v>1</v>
@@ -3299,19 +3300,19 @@
         <v>3542000</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K16" s="15">
         <v>2</v>
@@ -3320,7 +3321,7 @@
         <v>500</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N16" s="15">
         <v>1</v>
@@ -3341,7 +3342,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="U16" s="15">
         <v>4000</v>
@@ -3353,7 +3354,7 @@
         <v>10000</v>
       </c>
       <c r="X16" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Y16" s="15">
         <v>1</v>
@@ -3388,19 +3389,19 @@
         <v>3542200</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K17" s="15">
         <v>2</v>
@@ -3409,7 +3410,7 @@
         <v>500</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N17" s="15">
         <v>1</v>
@@ -3430,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U17" s="15">
         <v>4000</v>
@@ -3442,7 +3443,7 @@
         <v>10000</v>
       </c>
       <c r="X17" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y17" s="15">
         <v>1</v>
@@ -3477,19 +3478,19 @@
         <v>3542400</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K18" s="15">
         <v>2</v>
@@ -3519,7 +3520,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U18" s="15">
         <v>4000</v>
@@ -3531,7 +3532,7 @@
         <v>10000</v>
       </c>
       <c r="X18" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y18" s="15">
         <v>1</v>
@@ -3566,19 +3567,19 @@
         <v>3542600</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -3608,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -3620,7 +3621,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -3658,13 +3659,13 @@
         <v>69</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J20" s="17" t="s">
         <v>43</v>
@@ -3706,7 +3707,7 @@
         <v>79</v>
       </c>
       <c r="W20" s="17">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="X20" s="17" t="s">
         <v>43</v>
@@ -3747,13 +3748,13 @@
         <v>71</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J21" s="17" t="s">
         <v>80</v>
@@ -3762,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="L21" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M21" s="17" t="s">
         <v>81</v>
@@ -3836,13 +3837,13 @@
         <v>72</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -3925,13 +3926,13 @@
         <v>74</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>85</v>
@@ -3943,7 +3944,7 @@
         <v>3000</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N23" s="17">
         <v>0</v>
@@ -4011,16 +4012,16 @@
         <v>3551100</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>86</v>
@@ -4029,7 +4030,7 @@
         <v>3</v>
       </c>
       <c r="L24" s="17">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="M24" s="17" t="s">
         <v>87</v>
@@ -4038,10 +4039,10 @@
         <v>1</v>
       </c>
       <c r="O24" s="17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>88</v>
+        <v>374</v>
       </c>
       <c r="Q24" s="17">
         <v>1</v>
@@ -4100,19 +4101,19 @@
         <v>3551300</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K25" s="17">
         <v>2</v>
@@ -4121,7 +4122,7 @@
         <v>5000</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N25" s="17">
         <v>1</v>
@@ -4189,19 +4190,19 @@
         <v>3551500</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K26" s="17">
         <v>2</v>
@@ -4278,19 +4279,19 @@
         <v>3560200</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J27" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K27" s="18">
         <v>2</v>
@@ -4299,7 +4300,7 @@
         <v>5000</v>
       </c>
       <c r="M27" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="N27" s="18">
         <v>1</v>
@@ -4320,13 +4321,13 @@
         <v>0</v>
       </c>
       <c r="T27" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="U27" s="18">
         <v>4000</v>
       </c>
       <c r="V27" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="W27" s="18">
         <v>1500</v>
@@ -4341,7 +4342,7 @@
         <v>1</v>
       </c>
       <c r="AA27" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AB27" s="18">
         <v>1</v>
@@ -4367,19 +4368,19 @@
         <v>3560500</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J28" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K28" s="18">
         <v>1</v>
@@ -4388,16 +4389,16 @@
         <v>8</v>
       </c>
       <c r="M28" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="N28" s="18">
+        <v>1</v>
+      </c>
+      <c r="O28" s="18">
+        <v>10000</v>
+      </c>
+      <c r="P28" s="18" t="s">
         <v>210</v>
-      </c>
-      <c r="N28" s="18">
-        <v>1</v>
-      </c>
-      <c r="O28" s="18">
-        <v>10000</v>
-      </c>
-      <c r="P28" s="18" t="s">
-        <v>211</v>
       </c>
       <c r="Q28" s="18">
         <v>1</v>
@@ -4456,19 +4457,19 @@
         <v>3560700</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K29" s="18">
         <v>2</v>
@@ -4545,19 +4546,19 @@
         <v>3560900</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K30" s="18">
         <v>2</v>
@@ -4634,16 +4635,16 @@
         <v>3561100</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J31" s="18" t="s">
         <v>43</v>
@@ -4655,7 +4656,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N31" s="18">
         <v>2</v>
@@ -4664,7 +4665,7 @@
         <v>10000</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q31" s="18">
         <v>1</v>
@@ -4723,19 +4724,19 @@
         <v>3561400</v>
       </c>
       <c r="F32" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H32" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="G32" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>346</v>
-      </c>
       <c r="I32" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K32" s="18">
         <v>2</v>
@@ -4744,7 +4745,7 @@
         <v>3500</v>
       </c>
       <c r="M32" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="N32" s="18">
         <v>35</v>
@@ -4786,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="AA32" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AB32" s="18">
         <v>1</v>
@@ -4812,19 +4813,19 @@
         <v>3570200</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J33" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K33" s="19">
         <v>2</v>
@@ -4833,7 +4834,7 @@
         <v>4000</v>
       </c>
       <c r="M33" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N33" s="19">
         <v>1</v>
@@ -4854,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U33" s="19">
         <v>4000</v>
@@ -4901,19 +4902,19 @@
         <v>3570500</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K34" s="19">
         <v>1</v>
@@ -4922,7 +4923,7 @@
         <v>3</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N34" s="19">
         <v>1</v>
@@ -4931,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="P34" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q34" s="19">
         <v>2</v>
@@ -4990,19 +4991,19 @@
         <v>3570700</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K35" s="19">
         <v>1</v>
@@ -5011,7 +5012,7 @@
         <v>8</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N35" s="19">
         <v>2</v>
@@ -5020,7 +5021,7 @@
         <v>10000</v>
       </c>
       <c r="P35" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q35" s="19">
         <v>1</v>
@@ -5079,19 +5080,19 @@
         <v>3570900</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K36" s="19">
         <v>2</v>
@@ -5100,7 +5101,7 @@
         <v>2000</v>
       </c>
       <c r="M36" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="N36" s="19">
         <v>1</v>
@@ -5168,19 +5169,19 @@
         <v>3571100</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K37" s="19">
         <v>2</v>
@@ -5189,16 +5190,16 @@
         <v>10000</v>
       </c>
       <c r="M37" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="N37" s="19">
+        <v>1</v>
+      </c>
+      <c r="O37" s="19">
+        <v>1</v>
+      </c>
+      <c r="P37" s="19" t="s">
         <v>223</v>
-      </c>
-      <c r="N37" s="19">
-        <v>1</v>
-      </c>
-      <c r="O37" s="19">
-        <v>1</v>
-      </c>
-      <c r="P37" s="19" t="s">
-        <v>224</v>
       </c>
       <c r="Q37" s="19">
         <v>1</v>
@@ -5257,16 +5258,16 @@
         <v>3571300</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J38" s="19" t="s">
         <v>43</v>
@@ -5278,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N38" s="19">
         <v>2</v>
@@ -5287,7 +5288,7 @@
         <v>10000</v>
       </c>
       <c r="P38" s="19" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="Q38" s="19">
         <v>1</v>
@@ -5346,19 +5347,19 @@
         <v>3580200</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J39" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K39" s="20">
         <v>2</v>
@@ -5367,7 +5368,7 @@
         <v>3000</v>
       </c>
       <c r="M39" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="N39" s="20">
         <v>1</v>
@@ -5388,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="T39" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U39" s="20">
         <v>4000</v>
@@ -5400,7 +5401,7 @@
         <v>10000</v>
       </c>
       <c r="X39" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="Y39" s="20">
         <v>1</v>
@@ -5409,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="AA39" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AB39" s="20">
         <v>1</v>
@@ -5435,19 +5436,19 @@
         <v>3580500</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J40" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K40" s="20">
         <v>1</v>
@@ -5456,7 +5457,7 @@
         <v>8</v>
       </c>
       <c r="M40" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N40" s="20">
         <v>2</v>
@@ -5465,7 +5466,7 @@
         <v>10000</v>
       </c>
       <c r="P40" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Q40" s="20">
         <v>1</v>
@@ -5524,19 +5525,19 @@
         <v>3580700</v>
       </c>
       <c r="F41" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="I41" s="13" t="s">
         <v>359</v>
       </c>
-      <c r="G41" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="H41" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>360</v>
-      </c>
       <c r="J41" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K41" s="20">
         <v>1</v>
@@ -5545,7 +5546,7 @@
         <v>5</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N41" s="20">
         <v>2</v>
@@ -5613,16 +5614,16 @@
         <v>3580900</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J42" s="20" t="s">
         <v>43</v>
@@ -5634,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N42" s="20">
         <v>2</v>
@@ -5643,7 +5644,7 @@
         <v>10000</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q42" s="20">
         <v>1</v>
@@ -5702,19 +5703,19 @@
         <v>3581200</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="K43" s="20">
         <v>2</v>
@@ -5723,7 +5724,7 @@
         <v>3000</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N43" s="20">
         <v>0</v>
@@ -5744,7 +5745,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="U43" s="20">
         <v>4000</v>
@@ -5756,7 +5757,7 @@
         <v>10000</v>
       </c>
       <c r="X43" s="20" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="Y43" s="20">
         <v>1</v>
@@ -5765,7 +5766,7 @@
         <v>10</v>
       </c>
       <c r="AA43" s="20" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AB43" s="20">
         <v>1</v>
@@ -5791,15 +5792,15 @@
         <v>3590200</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H44" s="13"/>
       <c r="I44" s="13"/>
       <c r="J44" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K44" s="24">
         <v>3</v>
@@ -5808,7 +5809,7 @@
         <v>200000</v>
       </c>
       <c r="M44" s="24" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N44" s="24">
         <v>2</v>
@@ -5817,7 +5818,7 @@
         <v>10000</v>
       </c>
       <c r="P44" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="Q44" s="24">
         <v>1</v>
@@ -5876,15 +5877,15 @@
         <v>3590400</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H45" s="13"/>
       <c r="I45" s="13"/>
       <c r="J45" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="K45" s="24">
         <v>3</v>
@@ -5914,7 +5915,7 @@
         <v>59030001</v>
       </c>
       <c r="T45" s="24" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="U45" s="24">
         <v>-1</v>
@@ -5961,10 +5962,10 @@
         <v>3590600</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
@@ -5978,7 +5979,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="N46" s="24">
         <v>2</v>
@@ -5987,7 +5988,7 @@
         <v>10000</v>
       </c>
       <c r="P46" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q46" s="24">
         <v>1</v>
@@ -6046,10 +6047,10 @@
         <v>3590800</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
@@ -6063,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="N47" s="24">
         <v>2</v>
@@ -6072,7 +6073,7 @@
         <v>10000</v>
       </c>
       <c r="P47" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Q47" s="24">
         <v>1</v>
@@ -6131,15 +6132,15 @@
         <v>3591000</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
       <c r="J48" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K48" s="24">
         <v>2</v>
@@ -6148,16 +6149,16 @@
         <v>0</v>
       </c>
       <c r="M48" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N48" s="24">
+        <v>1</v>
+      </c>
+      <c r="O48" s="24">
+        <v>0</v>
+      </c>
+      <c r="P48" s="24" t="s">
         <v>343</v>
-      </c>
-      <c r="N48" s="24">
-        <v>1</v>
-      </c>
-      <c r="O48" s="24">
-        <v>0</v>
-      </c>
-      <c r="P48" s="24" t="s">
-        <v>344</v>
       </c>
       <c r="Q48" s="24">
         <v>3</v>
@@ -6216,15 +6217,15 @@
         <v>3591200</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
       <c r="J49" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K49" s="24">
         <v>3</v>
@@ -6233,7 +6234,7 @@
         <v>1000000</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6242,7 +6243,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6301,15 +6302,15 @@
         <v>3591400</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K50" s="24">
         <v>3</v>
@@ -6318,7 +6319,7 @@
         <v>500000</v>
       </c>
       <c r="M50" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N50" s="24">
         <v>2</v>
@@ -6327,7 +6328,7 @@
         <v>10000</v>
       </c>
       <c r="P50" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q50" s="24">
         <v>1</v>
@@ -6386,10 +6387,10 @@
         <v>3591600</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
@@ -6403,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -6412,7 +6413,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -6471,10 +6472,10 @@
         <v>3591900</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
@@ -6488,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="N52" s="24">
         <v>1</v>
@@ -6530,7 +6531,7 @@
         <v>1</v>
       </c>
       <c r="AA52" s="24" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AB52" s="24">
         <v>1</v>
@@ -6556,10 +6557,10 @@
         <v>3541800</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H53" s="13"/>
       <c r="I53" s="13"/>
@@ -6641,10 +6642,10 @@
         <v>3541800</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
@@ -6726,15 +6727,15 @@
         <v>3592100</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="24" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K55" s="24">
         <v>2</v>
@@ -6811,15 +6812,15 @@
         <v>3600200</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
       <c r="J56" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K56" s="21">
         <v>1</v>
@@ -6828,7 +6829,7 @@
         <v>8</v>
       </c>
       <c r="M56" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="N56" s="21">
         <v>2</v>
@@ -6837,7 +6838,7 @@
         <v>10000</v>
       </c>
       <c r="P56" s="21" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q56" s="21">
         <v>1</v>
@@ -6896,24 +6897,24 @@
         <v>3600400</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
       <c r="J57" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="K57" s="21">
+        <v>1</v>
+      </c>
+      <c r="L57" s="21">
+        <v>1</v>
+      </c>
+      <c r="M57" s="21" t="s">
         <v>265</v>
-      </c>
-      <c r="K57" s="21">
-        <v>1</v>
-      </c>
-      <c r="L57" s="21">
-        <v>1</v>
-      </c>
-      <c r="M57" s="21" t="s">
-        <v>266</v>
       </c>
       <c r="N57" s="21">
         <v>2</v>
@@ -6981,15 +6982,15 @@
         <v>3600700</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K58" s="21">
         <v>1</v>
@@ -6998,7 +6999,7 @@
         <v>8</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N58" s="21">
         <v>2</v>
@@ -7007,7 +7008,7 @@
         <v>10000</v>
       </c>
       <c r="P58" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q58" s="21">
         <v>1</v>
@@ -7066,10 +7067,10 @@
         <v>3601000</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
@@ -7083,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N59" s="21">
         <v>2</v>
@@ -7092,7 +7093,7 @@
         <v>10000</v>
       </c>
       <c r="P59" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q59" s="21">
         <v>1</v>
@@ -7151,15 +7152,15 @@
         <v>3541600</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K60" s="21">
         <v>2</v>
@@ -7236,15 +7237,15 @@
         <v>3541800</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
       <c r="J61" s="21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K61" s="21">
         <v>2</v>
@@ -7321,15 +7322,15 @@
         <v>3601300</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="K62" s="21">
         <v>2</v>
@@ -7338,7 +7339,7 @@
         <v>10000</v>
       </c>
       <c r="M62" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N62" s="21">
         <v>2</v>
@@ -7347,7 +7348,7 @@
         <v>2000</v>
       </c>
       <c r="P62" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q62" s="21">
         <v>1</v>
@@ -7406,15 +7407,15 @@
         <v>3610300</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
       <c r="J63" s="22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K63" s="22">
         <v>1</v>
@@ -7423,7 +7424,7 @@
         <v>8</v>
       </c>
       <c r="M63" s="22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N63" s="22">
         <v>2</v>
@@ -7432,7 +7433,7 @@
         <v>10000</v>
       </c>
       <c r="P63" s="22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q63" s="22">
         <v>1</v>
@@ -7491,15 +7492,15 @@
         <v>3610500</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
       <c r="J64" s="22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K64" s="22">
         <v>2</v>
@@ -7576,10 +7577,10 @@
         <v>3610700</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
@@ -7593,7 +7594,7 @@
         <v>0</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="N65" s="22">
         <v>2</v>
@@ -7602,7 +7603,7 @@
         <v>10000</v>
       </c>
       <c r="P65" s="22" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q65" s="22">
         <v>1</v>
@@ -7661,15 +7662,15 @@
         <v>3541400</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K66" s="22">
         <v>2</v>
@@ -7746,15 +7747,15 @@
         <v>3610900</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
       <c r="J67" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K67" s="22">
         <v>1</v>
@@ -7831,10 +7832,10 @@
         <v>3611100</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
@@ -7916,15 +7917,15 @@
         <v>3611300</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K69" s="22">
         <v>3</v>
@@ -7942,7 +7943,7 @@
         <v>0</v>
       </c>
       <c r="P69" s="22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q69" s="22">
         <v>1</v>
@@ -8001,10 +8002,10 @@
         <v>3611500</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="13"/>
@@ -8018,7 +8019,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="N70" s="22">
         <v>2</v>
@@ -8027,7 +8028,7 @@
         <v>10000</v>
       </c>
       <c r="P70" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q70" s="22">
         <v>1</v>
@@ -8086,15 +8087,15 @@
         <v>3611700</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K71" s="22">
         <v>3</v>
@@ -8171,10 +8172,10 @@
         <v>3590800</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
@@ -8188,7 +8189,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="N72" s="22">
         <v>2</v>
@@ -8197,7 +8198,7 @@
         <v>10000</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AF3AC5-BA51-4464-A8AD-078CE6583EED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E89779E-6FAA-4DF9-B7FD-A79767996087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
-    <sheet name="备注" sheetId="2" r:id="rId2"/>
+    <sheet name="新表结构" sheetId="3" r:id="rId2"/>
+    <sheet name="备注" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -125,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="533">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1352,6 +1353,549 @@
   </si>
   <si>
     <t>3551103:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数8结算间隔时间</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑属性id</t>
+  </si>
+  <si>
+    <t>技能效果</t>
+  </si>
+  <si>
+    <t>技能名称</t>
+  </si>
+  <si>
+    <t>参数描述</t>
+  </si>
+  <si>
+    <t>效果叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算间隔时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复中buff组的cd时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
+    <t>参数6</t>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果最大叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果基础命中率（万分比）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果触发间隔（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数4LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发的技能id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数9</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数10</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数11</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数12</t>
+  </si>
+  <si>
+    <t>参数13</t>
+  </si>
+  <si>
+    <t>击中回复生命值-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中回复效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数14</t>
+  </si>
+  <si>
+    <t>参数15</t>
+  </si>
+  <si>
+    <t>参数16</t>
+  </si>
+  <si>
+    <t>击中回复生命值-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-目标最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数17</t>
+  </si>
+  <si>
+    <t>参数18</t>
+  </si>
+  <si>
+    <t>参数19</t>
+  </si>
+  <si>
+    <t>参数20</t>
+  </si>
+  <si>
+    <t>参数21</t>
+  </si>
+  <si>
+    <t>参数22</t>
+  </si>
+  <si>
+    <t>参数28</t>
+  </si>
+  <si>
+    <t>参数29</t>
+  </si>
+  <si>
+    <t>获得护盾-自身生命百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-自身已损失生命万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发自动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数30</t>
+  </si>
+  <si>
+    <t>参数31</t>
+  </si>
+  <si>
+    <t>参数32</t>
+  </si>
+  <si>
+    <t>参数33</t>
+  </si>
+  <si>
+    <t>参数34</t>
+  </si>
+  <si>
+    <t>参数35</t>
+  </si>
+  <si>
+    <t>参数36</t>
+  </si>
+  <si>
+    <t>参数37</t>
+  </si>
+  <si>
+    <t>参数38</t>
+  </si>
+  <si>
+    <t>参数39</t>
+  </si>
+  <si>
+    <t>参数40</t>
+  </si>
+  <si>
+    <t>参数41</t>
+  </si>
+  <si>
+    <t>参数42</t>
+  </si>
+  <si>
+    <t>参数43</t>
+  </si>
+  <si>
+    <t>参数44</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复生命</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中目标</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘟疫</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>电磁爆发</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-万分比</t>
+  </si>
+  <si>
+    <t>技能增加-普通攻击范围万分比</t>
+  </si>
+  <si>
+    <t>攻击提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-攻击的元素类型</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数25LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数45</t>
+  </si>
+  <si>
+    <t>参数46</t>
+  </si>
+  <si>
+    <t>参数47</t>
+  </si>
+  <si>
+    <t>参数48</t>
+  </si>
+  <si>
+    <t>参数49</t>
+  </si>
+  <si>
+    <t>参数50</t>
+  </si>
+  <si>
+    <t>参数51</t>
+  </si>
+  <si>
+    <t>参数52</t>
+  </si>
+  <si>
+    <t>参数53</t>
+  </si>
+  <si>
+    <t>参数54</t>
+  </si>
+  <si>
+    <t>参数55</t>
+  </si>
+  <si>
+    <t>参数56</t>
+  </si>
+  <si>
+    <t>生命上限提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命上限提高-百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击范围提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击目标数量提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+  </si>
+  <si>
+    <t>auto_cd</t>
+  </si>
+  <si>
+    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
+  </si>
+  <si>
+    <t>release_ratio</t>
+  </si>
+  <si>
+    <t>参数-释放几率</t>
+  </si>
+  <si>
+    <t>release_num</t>
+  </si>
+  <si>
+    <t>参数-释放次数</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>参数-释放的技能id</t>
+  </si>
+  <si>
+    <t>total_attack_num</t>
+  </si>
+  <si>
+    <t>参数-累计发起攻击次数时</t>
+  </si>
+  <si>
+    <t>lose_hp_ratio</t>
+  </si>
+  <si>
+    <t>参数-损失自身生命最大值百万分比时</t>
+  </si>
+  <si>
+    <t>kill_target_after</t>
+  </si>
+  <si>
+    <t>参数-击杀目标后</t>
+  </si>
+  <si>
+    <t>after_attack_crit</t>
+  </si>
+  <si>
+    <t>参数-攻击暴击后</t>
+  </si>
+  <si>
+    <t>after_use_skill</t>
+  </si>
+  <si>
+    <t>参数-释放【技能id】后</t>
+  </si>
+  <si>
+    <t>cycle_time</t>
+  </si>
+  <si>
+    <t>参数-每过固定时间（毫秒）时</t>
+  </si>
+  <si>
+    <t>after_skill_hit</t>
+  </si>
+  <si>
+    <t>参数-【技能id】命中后</t>
+  </si>
+  <si>
+    <t>after_self_death</t>
+  </si>
+  <si>
+    <t>参数-自身死亡后释放</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+  </si>
+  <si>
+    <t>self_have_effect</t>
+  </si>
+  <si>
+    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_have_effect</t>
+  </si>
+  <si>
+    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_over</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_under</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>to_target_effect_hit</t>
+  </si>
+  <si>
+    <t>参数-对目标施加【效果id】命中时</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542801:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542601:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543001:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542607:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542807:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543007:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542605:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542805:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543005:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -1974,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2301,7 +2845,7 @@
         <v>332</v>
       </c>
       <c r="AC4" s="7" t="s">
-        <v>333</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
@@ -3579,7 +4123,7 @@
         <v>177</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>127</v>
+        <v>525</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -3609,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>150</v>
+        <v>530</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -3621,7 +4165,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>151</v>
+        <v>527</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -3640,189 +4184,189 @@
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A20" s="17">
-        <v>55010001</v>
-      </c>
-      <c r="B20" s="17">
-        <v>5501</v>
-      </c>
-      <c r="C20" s="17">
-        <v>1</v>
-      </c>
-      <c r="D20" s="17">
-        <v>0</v>
-      </c>
-      <c r="E20" s="17">
-        <v>3550200</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>351</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="K20" s="17">
-        <v>0</v>
-      </c>
-      <c r="L20" s="17">
-        <v>0</v>
-      </c>
-      <c r="M20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="N20" s="17">
-        <v>0</v>
-      </c>
-      <c r="O20" s="17">
-        <v>0</v>
-      </c>
-      <c r="P20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q20" s="17">
-        <v>0</v>
-      </c>
-      <c r="R20" s="17">
-        <v>0</v>
-      </c>
-      <c r="S20" s="17">
-        <v>0</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U20" s="17">
-        <v>2000</v>
-      </c>
-      <c r="V20" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="W20" s="17">
-        <v>1000</v>
-      </c>
-      <c r="X20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y20" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB20" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="17">
+      <c r="A20" s="15">
+        <v>54140001</v>
+      </c>
+      <c r="B20" s="15">
+        <v>5414</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>0</v>
+      </c>
+      <c r="E20" s="15">
+        <v>3542800</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>524</v>
+      </c>
+      <c r="K20" s="15">
+        <v>2</v>
+      </c>
+      <c r="L20" s="15">
+        <v>5000</v>
+      </c>
+      <c r="M20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" s="15">
+        <v>0</v>
+      </c>
+      <c r="O20" s="15">
+        <v>0</v>
+      </c>
+      <c r="P20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q20" s="15">
+        <v>0</v>
+      </c>
+      <c r="R20" s="15">
+        <v>0</v>
+      </c>
+      <c r="S20" s="15">
+        <v>0</v>
+      </c>
+      <c r="T20" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="U20" s="15">
+        <v>-1</v>
+      </c>
+      <c r="V20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X20" s="15" t="s">
+        <v>528</v>
+      </c>
+      <c r="Y20" s="15">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB20" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A21" s="17">
-        <v>55020001</v>
-      </c>
-      <c r="B21" s="17">
-        <v>5502</v>
-      </c>
-      <c r="C21" s="17">
-        <v>1</v>
-      </c>
-      <c r="D21" s="17">
-        <v>0</v>
-      </c>
-      <c r="E21" s="17">
-        <v>3550500</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>352</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="K21" s="17">
-        <v>1</v>
-      </c>
-      <c r="L21" s="17">
-        <v>12</v>
-      </c>
-      <c r="M21" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="N21" s="17">
+      <c r="A21" s="15">
+        <v>54150001</v>
+      </c>
+      <c r="B21" s="15">
+        <v>5415</v>
+      </c>
+      <c r="C21" s="15">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15">
+        <v>3543000</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>523</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="K21" s="15">
         <v>2</v>
       </c>
-      <c r="O21" s="17">
+      <c r="L21" s="15">
         <v>10000</v>
       </c>
-      <c r="P21" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q21" s="17">
-        <v>1</v>
-      </c>
-      <c r="R21" s="17">
-        <v>1</v>
-      </c>
-      <c r="S21" s="17">
-        <v>5000001</v>
-      </c>
-      <c r="T21" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="U21" s="17">
-        <v>4000</v>
-      </c>
-      <c r="V21" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="W21" s="17">
+      <c r="M21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="N21" s="15">
+        <v>0</v>
+      </c>
+      <c r="O21" s="15">
+        <v>0</v>
+      </c>
+      <c r="P21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q21" s="15">
+        <v>0</v>
+      </c>
+      <c r="R21" s="15">
+        <v>0</v>
+      </c>
+      <c r="S21" s="15">
+        <v>0</v>
+      </c>
+      <c r="T21" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="U21" s="15">
+        <v>-1</v>
+      </c>
+      <c r="V21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" s="15">
         <v>10000</v>
       </c>
-      <c r="X21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y21" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB21" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC21" s="17">
+      <c r="X21" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="Y21" s="15">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="15">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB21" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="15">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A22" s="17">
-        <v>55030001</v>
+        <v>55010001</v>
       </c>
       <c r="B22" s="17">
-        <v>5503</v>
+        <v>5501</v>
       </c>
       <c r="C22" s="17">
         <v>1</v>
@@ -3831,19 +4375,19 @@
         <v>0</v>
       </c>
       <c r="E22" s="17">
-        <v>3550700</v>
+        <v>3550200</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -3852,40 +4396,40 @@
         <v>0</v>
       </c>
       <c r="L22" s="17">
+        <v>0</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N22" s="17">
+        <v>0</v>
+      </c>
+      <c r="O22" s="17">
+        <v>0</v>
+      </c>
+      <c r="P22" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q22" s="17">
+        <v>0</v>
+      </c>
+      <c r="R22" s="17">
+        <v>0</v>
+      </c>
+      <c r="S22" s="17">
+        <v>0</v>
+      </c>
+      <c r="T22" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U22" s="17">
+        <v>2000</v>
+      </c>
+      <c r="V22" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="W22" s="17">
         <v>1000</v>
-      </c>
-      <c r="M22" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="N22" s="17">
-        <v>2</v>
-      </c>
-      <c r="O22" s="17">
-        <v>10000</v>
-      </c>
-      <c r="P22" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q22" s="17">
-        <v>1</v>
-      </c>
-      <c r="R22" s="17">
-        <v>1</v>
-      </c>
-      <c r="S22" s="17">
-        <v>5000001</v>
-      </c>
-      <c r="T22" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="U22" s="17">
-        <v>4000</v>
-      </c>
-      <c r="V22" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="W22" s="17">
-        <v>10000</v>
       </c>
       <c r="X22" s="17" t="s">
         <v>43</v>
@@ -3908,10 +4452,10 @@
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A23" s="17">
-        <v>55040001</v>
+        <v>55020001</v>
       </c>
       <c r="B23" s="17">
-        <v>5504</v>
+        <v>5502</v>
       </c>
       <c r="C23" s="17">
         <v>1</v>
@@ -3920,58 +4464,58 @@
         <v>0</v>
       </c>
       <c r="E23" s="17">
-        <v>3550900</v>
+        <v>3550500</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K23" s="17">
+        <v>1</v>
+      </c>
+      <c r="L23" s="17">
+        <v>12</v>
+      </c>
+      <c r="M23" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="N23" s="17">
         <v>2</v>
       </c>
-      <c r="L23" s="17">
-        <v>3000</v>
-      </c>
-      <c r="M23" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="N23" s="17">
-        <v>0</v>
-      </c>
       <c r="O23" s="17">
-        <v>30</v>
+        <v>10000</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="Q23" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23" s="17">
-        <v>0</v>
+        <v>5000001</v>
       </c>
       <c r="T23" s="17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="U23" s="17">
-        <v>-1</v>
+        <v>4000</v>
       </c>
       <c r="V23" s="17" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="W23" s="17">
         <v>10000</v>
@@ -3997,10 +4541,10 @@
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A24" s="17">
-        <v>55050001</v>
+        <v>55030001</v>
       </c>
       <c r="B24" s="17">
-        <v>5505</v>
+        <v>5503</v>
       </c>
       <c r="C24" s="17">
         <v>1</v>
@@ -4009,55 +4553,55 @@
         <v>0</v>
       </c>
       <c r="E24" s="17">
-        <v>3551100</v>
+        <v>3550700</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="K24" s="17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" s="17">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="N24" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="17">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>374</v>
+        <v>84</v>
       </c>
       <c r="Q24" s="17">
         <v>1</v>
       </c>
       <c r="R24" s="17">
-        <v>2000</v>
+        <v>1</v>
       </c>
       <c r="S24" s="17">
-        <v>0</v>
+        <v>5000001</v>
       </c>
       <c r="T24" s="17" t="s">
         <v>43</v>
       </c>
       <c r="U24" s="17">
-        <v>-1</v>
+        <v>4000</v>
       </c>
       <c r="V24" s="17" t="s">
         <v>43</v>
@@ -4086,10 +4630,10 @@
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A25" s="17">
-        <v>55060001</v>
+        <v>55040001</v>
       </c>
       <c r="B25" s="17">
-        <v>5506</v>
+        <v>5504</v>
       </c>
       <c r="C25" s="17">
         <v>1</v>
@@ -4098,37 +4642,37 @@
         <v>0</v>
       </c>
       <c r="E25" s="17">
-        <v>3551300</v>
+        <v>3550900</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>357</v>
+        <v>74</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K25" s="17">
         <v>2</v>
       </c>
       <c r="L25" s="17">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="N25" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" s="17">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="P25" s="17" t="s">
         <v>43</v>
@@ -4175,10 +4719,10 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A26" s="17">
-        <v>55070001</v>
+        <v>55050001</v>
       </c>
       <c r="B26" s="17">
-        <v>5507</v>
+        <v>5505</v>
       </c>
       <c r="C26" s="17">
         <v>1</v>
@@ -4187,265 +4731,265 @@
         <v>0</v>
       </c>
       <c r="E26" s="17">
-        <v>3551500</v>
+        <v>3551100</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>185</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>157</v>
+        <v>355</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="K26" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L26" s="17">
+        <v>100000</v>
+      </c>
+      <c r="M26" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="N26" s="17">
+        <v>1</v>
+      </c>
+      <c r="O26" s="17">
+        <v>0</v>
+      </c>
+      <c r="P26" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q26" s="17">
+        <v>1</v>
+      </c>
+      <c r="R26" s="17">
         <v>2000</v>
       </c>
-      <c r="M26" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="N26" s="17">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17">
-        <v>0</v>
-      </c>
-      <c r="P26" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q26" s="17">
-        <v>0</v>
-      </c>
-      <c r="R26" s="17">
-        <v>0</v>
-      </c>
       <c r="S26" s="17">
         <v>0</v>
       </c>
       <c r="T26" s="17" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="U26" s="17">
         <v>-1</v>
       </c>
       <c r="V26" s="17" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="W26" s="17">
         <v>10000</v>
       </c>
       <c r="X26" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y26" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB26" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A27" s="17">
+        <v>55060001</v>
+      </c>
+      <c r="B27" s="17">
+        <v>5506</v>
+      </c>
+      <c r="C27" s="17">
+        <v>1</v>
+      </c>
+      <c r="D27" s="17">
+        <v>0</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3551300</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="K27" s="17">
+        <v>2</v>
+      </c>
+      <c r="L27" s="17">
+        <v>5000</v>
+      </c>
+      <c r="M27" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="N27" s="17">
+        <v>1</v>
+      </c>
+      <c r="O27" s="17">
+        <v>50</v>
+      </c>
+      <c r="P27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="17">
+        <v>0</v>
+      </c>
+      <c r="R27" s="17">
+        <v>0</v>
+      </c>
+      <c r="S27" s="17">
+        <v>0</v>
+      </c>
+      <c r="T27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="U27" s="17">
+        <v>-1</v>
+      </c>
+      <c r="V27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W27" s="17">
+        <v>10000</v>
+      </c>
+      <c r="X27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y27" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB27" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A28" s="17">
+        <v>55070001</v>
+      </c>
+      <c r="B28" s="17">
+        <v>5507</v>
+      </c>
+      <c r="C28" s="17">
+        <v>1</v>
+      </c>
+      <c r="D28" s="17">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3551500</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="K28" s="17">
+        <v>2</v>
+      </c>
+      <c r="L28" s="17">
+        <v>2000</v>
+      </c>
+      <c r="M28" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="Y26" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="17">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB26" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A27" s="18">
-        <v>56010001</v>
-      </c>
-      <c r="B27" s="18">
-        <v>5601</v>
-      </c>
-      <c r="C27" s="18">
-        <v>1</v>
-      </c>
-      <c r="D27" s="18">
-        <v>0</v>
-      </c>
-      <c r="E27" s="18">
-        <v>3560200</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="K27" s="18">
-        <v>2</v>
-      </c>
-      <c r="L27" s="18">
-        <v>5000</v>
-      </c>
-      <c r="M27" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="N27" s="18">
-        <v>1</v>
-      </c>
-      <c r="O27" s="18">
-        <v>50</v>
-      </c>
-      <c r="P27" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q27" s="18">
-        <v>0</v>
-      </c>
-      <c r="R27" s="18">
-        <v>0</v>
-      </c>
-      <c r="S27" s="18">
-        <v>0</v>
-      </c>
-      <c r="T27" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="U27" s="18">
-        <v>4000</v>
-      </c>
-      <c r="V27" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="W27" s="18">
-        <v>1500</v>
-      </c>
-      <c r="X27" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y27" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="18">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB27" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="18">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A28" s="18">
-        <v>56020001</v>
-      </c>
-      <c r="B28" s="18">
-        <v>5602</v>
-      </c>
-      <c r="C28" s="18">
-        <v>1</v>
-      </c>
-      <c r="D28" s="18">
-        <v>0</v>
-      </c>
-      <c r="E28" s="18">
-        <v>3560500</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="K28" s="18">
-        <v>1</v>
-      </c>
-      <c r="L28" s="18">
-        <v>8</v>
-      </c>
-      <c r="M28" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="N28" s="18">
-        <v>1</v>
-      </c>
-      <c r="O28" s="18">
+      <c r="N28" s="17">
+        <v>0</v>
+      </c>
+      <c r="O28" s="17">
+        <v>0</v>
+      </c>
+      <c r="P28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q28" s="17">
+        <v>0</v>
+      </c>
+      <c r="R28" s="17">
+        <v>0</v>
+      </c>
+      <c r="S28" s="17">
+        <v>0</v>
+      </c>
+      <c r="T28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="U28" s="17">
+        <v>-1</v>
+      </c>
+      <c r="V28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="W28" s="17">
         <v>10000</v>
       </c>
-      <c r="P28" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q28" s="18">
-        <v>1</v>
-      </c>
-      <c r="R28" s="18">
-        <v>1</v>
-      </c>
-      <c r="S28" s="18">
-        <v>0</v>
-      </c>
-      <c r="T28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="U28" s="18">
-        <v>0</v>
-      </c>
-      <c r="V28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="W28" s="18">
-        <v>10000</v>
-      </c>
-      <c r="X28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y28" s="18">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="18">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB28" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="18">
+      <c r="X28" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y28" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="17">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB28" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A29" s="18">
-        <v>56030001</v>
+        <v>56010001</v>
       </c>
       <c r="B29" s="18">
-        <v>5603</v>
+        <v>5601</v>
       </c>
       <c r="C29" s="18">
         <v>1</v>
@@ -4454,37 +4998,37 @@
         <v>0</v>
       </c>
       <c r="E29" s="18">
-        <v>3560700</v>
+        <v>3560200</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>236</v>
+        <v>334</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="K29" s="18">
         <v>2</v>
       </c>
       <c r="L29" s="18">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="N29" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P29" s="18" t="s">
         <v>43</v>
@@ -4499,16 +5043,16 @@
         <v>0</v>
       </c>
       <c r="T29" s="18" t="s">
-        <v>43</v>
+        <v>206</v>
       </c>
       <c r="U29" s="18">
-        <v>-1</v>
+        <v>4000</v>
       </c>
       <c r="V29" s="18" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="W29" s="18">
-        <v>10000</v>
+        <v>1500</v>
       </c>
       <c r="X29" s="18" t="s">
         <v>43</v>
@@ -4520,21 +5064,21 @@
         <v>1</v>
       </c>
       <c r="AA29" s="18" t="s">
-        <v>43</v>
+        <v>339</v>
       </c>
       <c r="AB29" s="18">
         <v>1</v>
       </c>
       <c r="AC29" s="18">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A30" s="18">
-        <v>56040001</v>
+        <v>56020001</v>
       </c>
       <c r="B30" s="18">
-        <v>5604</v>
+        <v>5602</v>
       </c>
       <c r="C30" s="18">
         <v>1</v>
@@ -4543,46 +5087,46 @@
         <v>0</v>
       </c>
       <c r="E30" s="18">
-        <v>3560900</v>
+        <v>3560500</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K30" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L30" s="18">
+        <v>8</v>
+      </c>
+      <c r="M30" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="N30" s="18">
+        <v>1</v>
+      </c>
+      <c r="O30" s="18">
         <v>10000</v>
       </c>
-      <c r="M30" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="N30" s="18">
-        <v>0</v>
-      </c>
-      <c r="O30" s="18">
-        <v>0</v>
-      </c>
       <c r="P30" s="18" t="s">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="Q30" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" s="18">
         <v>0</v>
@@ -4591,7 +5135,7 @@
         <v>43</v>
       </c>
       <c r="U30" s="18">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V30" s="18" t="s">
         <v>43</v>
@@ -4620,10 +5164,10 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A31" s="18">
-        <v>56050001</v>
+        <v>56030001</v>
       </c>
       <c r="B31" s="18">
-        <v>5605</v>
+        <v>5603</v>
       </c>
       <c r="C31" s="18">
         <v>1</v>
@@ -4632,46 +5176,46 @@
         <v>0</v>
       </c>
       <c r="E31" s="18">
-        <v>3561100</v>
+        <v>3560700</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>43</v>
+        <v>211</v>
       </c>
       <c r="K31" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" s="18">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="M31" s="18" t="s">
-        <v>233</v>
+        <v>43</v>
       </c>
       <c r="N31" s="18">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O31" s="18">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P31" s="18" t="s">
-        <v>234</v>
+        <v>43</v>
       </c>
       <c r="Q31" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31" s="18">
         <v>0</v>
@@ -4680,7 +5224,7 @@
         <v>43</v>
       </c>
       <c r="U31" s="18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V31" s="18" t="s">
         <v>43</v>
@@ -4709,10 +5253,10 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A32" s="18">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B32" s="18">
-        <v>5606</v>
+        <v>5604</v>
       </c>
       <c r="C32" s="18">
         <v>1</v>
@@ -4721,37 +5265,37 @@
         <v>0</v>
       </c>
       <c r="E32" s="18">
-        <v>3561400</v>
+        <v>3560900</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>344</v>
+        <v>195</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>345</v>
+        <v>195</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>366</v>
+        <v>237</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>363</v>
+        <v>212</v>
       </c>
       <c r="K32" s="18">
         <v>2</v>
       </c>
       <c r="L32" s="18">
-        <v>3500</v>
+        <v>10000</v>
       </c>
       <c r="M32" s="18" t="s">
-        <v>364</v>
+        <v>43</v>
       </c>
       <c r="N32" s="18">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O32" s="18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="18" t="s">
         <v>43</v>
@@ -4769,7 +5313,7 @@
         <v>43</v>
       </c>
       <c r="U32" s="18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V32" s="18" t="s">
         <v>43</v>
@@ -4787,199 +5331,199 @@
         <v>1</v>
       </c>
       <c r="AA32" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB32" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A33" s="18">
+        <v>56050001</v>
+      </c>
+      <c r="B33" s="18">
+        <v>5605</v>
+      </c>
+      <c r="C33" s="18">
+        <v>1</v>
+      </c>
+      <c r="D33" s="18">
+        <v>0</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3561100</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="J33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="K33" s="18">
+        <v>0</v>
+      </c>
+      <c r="L33" s="18">
+        <v>0</v>
+      </c>
+      <c r="M33" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="N33" s="18">
+        <v>2</v>
+      </c>
+      <c r="O33" s="18">
+        <v>10000</v>
+      </c>
+      <c r="P33" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q33" s="18">
+        <v>1</v>
+      </c>
+      <c r="R33" s="18">
+        <v>1</v>
+      </c>
+      <c r="S33" s="18">
+        <v>0</v>
+      </c>
+      <c r="T33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="U33" s="18">
+        <v>0</v>
+      </c>
+      <c r="V33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W33" s="18">
+        <v>10000</v>
+      </c>
+      <c r="X33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y33" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="18">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB33" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A34" s="18">
+        <v>56060001</v>
+      </c>
+      <c r="B34" s="18">
+        <v>5606</v>
+      </c>
+      <c r="C34" s="18">
+        <v>1</v>
+      </c>
+      <c r="D34" s="18">
+        <v>0</v>
+      </c>
+      <c r="E34" s="18">
+        <v>3561400</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>366</v>
+      </c>
+      <c r="J34" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="K34" s="18">
+        <v>2</v>
+      </c>
+      <c r="L34" s="18">
+        <v>3500</v>
+      </c>
+      <c r="M34" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="N34" s="18">
+        <v>35</v>
+      </c>
+      <c r="O34" s="18">
+        <v>1</v>
+      </c>
+      <c r="P34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q34" s="18">
+        <v>0</v>
+      </c>
+      <c r="R34" s="18">
+        <v>0</v>
+      </c>
+      <c r="S34" s="18">
+        <v>0</v>
+      </c>
+      <c r="T34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="U34" s="18">
+        <v>0</v>
+      </c>
+      <c r="V34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="W34" s="18">
+        <v>10000</v>
+      </c>
+      <c r="X34" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y34" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="18">
+        <v>1</v>
+      </c>
+      <c r="AA34" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="AB32" s="18">
-        <v>1</v>
-      </c>
-      <c r="AC32" s="18">
+      <c r="AB34" s="18">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="18">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A33" s="19">
-        <v>57010001</v>
-      </c>
-      <c r="B33" s="19">
-        <v>5701</v>
-      </c>
-      <c r="C33" s="19">
-        <v>1</v>
-      </c>
-      <c r="D33" s="19">
-        <v>0</v>
-      </c>
-      <c r="E33" s="19">
-        <v>3570200</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G33" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="K33" s="19">
-        <v>2</v>
-      </c>
-      <c r="L33" s="19">
-        <v>4000</v>
-      </c>
-      <c r="M33" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="19">
-        <v>1</v>
-      </c>
-      <c r="O33" s="19">
-        <v>3</v>
-      </c>
-      <c r="P33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q33" s="19">
-        <v>0</v>
-      </c>
-      <c r="R33" s="19">
-        <v>0</v>
-      </c>
-      <c r="S33" s="19">
-        <v>0</v>
-      </c>
-      <c r="T33" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="U33" s="19">
-        <v>4000</v>
-      </c>
-      <c r="V33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="W33" s="19">
-        <v>10000</v>
-      </c>
-      <c r="X33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y33" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z33" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA33" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB33" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC33" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A34" s="19">
-        <v>57020001</v>
-      </c>
-      <c r="B34" s="19">
-        <v>5702</v>
-      </c>
-      <c r="C34" s="19">
-        <v>1</v>
-      </c>
-      <c r="D34" s="19">
-        <v>0</v>
-      </c>
-      <c r="E34" s="19">
-        <v>3570500</v>
-      </c>
-      <c r="F34" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="J34" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="K34" s="19">
-        <v>1</v>
-      </c>
-      <c r="L34" s="19">
-        <v>3</v>
-      </c>
-      <c r="M34" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="N34" s="19">
-        <v>1</v>
-      </c>
-      <c r="O34" s="19">
-        <v>1</v>
-      </c>
-      <c r="P34" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q34" s="19">
-        <v>2</v>
-      </c>
-      <c r="R34" s="19">
-        <v>2500</v>
-      </c>
-      <c r="S34" s="19">
-        <v>0</v>
-      </c>
-      <c r="T34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="U34" s="19">
-        <v>-1</v>
-      </c>
-      <c r="V34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="W34" s="19">
-        <v>10000</v>
-      </c>
-      <c r="X34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y34" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z34" s="19">
-        <v>1</v>
-      </c>
-      <c r="AA34" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB34" s="19">
-        <v>1</v>
-      </c>
-      <c r="AC34" s="19">
-        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35" s="19">
-        <v>57030001</v>
+        <v>57010001</v>
       </c>
       <c r="B35" s="19">
-        <v>5703</v>
+        <v>5701</v>
       </c>
       <c r="C35" s="19">
         <v>1</v>
@@ -4988,55 +5532,55 @@
         <v>0</v>
       </c>
       <c r="E35" s="19">
-        <v>3570700</v>
+        <v>3570200</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G35" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="K35" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="19">
-        <v>8</v>
+        <v>4000</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N35" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O35" s="19">
-        <v>10000</v>
+        <v>3</v>
       </c>
       <c r="P35" s="19" t="s">
-        <v>219</v>
+        <v>43</v>
       </c>
       <c r="Q35" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" s="19">
         <v>0</v>
       </c>
       <c r="T35" s="19" t="s">
-        <v>43</v>
+        <v>367</v>
       </c>
       <c r="U35" s="19">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V35" s="19" t="s">
         <v>43</v>
@@ -5065,10 +5609,10 @@
     </row>
     <row r="36" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A36" s="19">
-        <v>57040001</v>
+        <v>57020001</v>
       </c>
       <c r="B36" s="19">
-        <v>5704</v>
+        <v>5702</v>
       </c>
       <c r="C36" s="19">
         <v>1</v>
@@ -5077,46 +5621,46 @@
         <v>0</v>
       </c>
       <c r="E36" s="19">
-        <v>3570900</v>
+        <v>3570500</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>347</v>
+        <v>198</v>
       </c>
       <c r="G36" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>346</v>
+        <v>240</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="K36" s="19">
+        <v>1</v>
+      </c>
+      <c r="L36" s="19">
+        <v>3</v>
+      </c>
+      <c r="M36" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N36" s="19">
+        <v>1</v>
+      </c>
+      <c r="O36" s="19">
+        <v>1</v>
+      </c>
+      <c r="P36" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q36" s="19">
         <v>2</v>
       </c>
-      <c r="L36" s="19">
-        <v>2000</v>
-      </c>
-      <c r="M36" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="N36" s="19">
-        <v>1</v>
-      </c>
-      <c r="O36" s="19">
-        <v>20</v>
-      </c>
-      <c r="P36" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q36" s="19">
-        <v>0</v>
-      </c>
       <c r="R36" s="19">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="S36" s="19">
         <v>0</v>
@@ -5154,10 +5698,10 @@
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A37" s="19">
-        <v>57050001</v>
+        <v>57030001</v>
       </c>
       <c r="B37" s="19">
-        <v>5705</v>
+        <v>5703</v>
       </c>
       <c r="C37" s="19">
         <v>1</v>
@@ -5166,46 +5710,46 @@
         <v>0</v>
       </c>
       <c r="E37" s="19">
-        <v>3571100</v>
+        <v>3570700</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>350</v>
+        <v>199</v>
       </c>
       <c r="G37" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>349</v>
+        <v>199</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>349</v>
+        <v>235</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="K37" s="19">
+        <v>1</v>
+      </c>
+      <c r="L37" s="19">
+        <v>8</v>
+      </c>
+      <c r="M37" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="N37" s="19">
         <v>2</v>
       </c>
-      <c r="L37" s="19">
+      <c r="O37" s="19">
         <v>10000</v>
       </c>
-      <c r="M37" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="N37" s="19">
-        <v>1</v>
-      </c>
-      <c r="O37" s="19">
-        <v>1</v>
-      </c>
       <c r="P37" s="19" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Q37" s="19">
         <v>1</v>
       </c>
       <c r="R37" s="19">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="S37" s="19">
         <v>0</v>
@@ -5214,7 +5758,7 @@
         <v>43</v>
       </c>
       <c r="U37" s="19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="19" t="s">
         <v>43</v>
@@ -5243,10 +5787,10 @@
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A38" s="19">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B38" s="19">
-        <v>5706</v>
+        <v>5704</v>
       </c>
       <c r="C38" s="19">
         <v>1</v>
@@ -5255,46 +5799,46 @@
         <v>0</v>
       </c>
       <c r="E38" s="19">
-        <v>3571300</v>
+        <v>3570900</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>201</v>
+        <v>347</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>43</v>
+        <v>220</v>
       </c>
       <c r="K38" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="19">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="N38" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" s="19">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="P38" s="19" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="Q38" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="19">
         <v>0</v>
@@ -5331,189 +5875,189 @@
       </c>
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A39" s="20">
-        <v>58010001</v>
-      </c>
-      <c r="B39" s="20">
-        <v>5801</v>
-      </c>
-      <c r="C39" s="20">
-        <v>1</v>
-      </c>
-      <c r="D39" s="20">
-        <v>0</v>
-      </c>
-      <c r="E39" s="20">
-        <v>3580200</v>
+      <c r="A39" s="19">
+        <v>57050001</v>
+      </c>
+      <c r="B39" s="19">
+        <v>5705</v>
+      </c>
+      <c r="C39" s="19">
+        <v>1</v>
+      </c>
+      <c r="D39" s="19">
+        <v>0</v>
+      </c>
+      <c r="E39" s="19">
+        <v>3571100</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>202</v>
+        <v>350</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>202</v>
+        <v>349</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="J39" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="K39" s="20">
+        <v>349</v>
+      </c>
+      <c r="J39" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="K39" s="19">
         <v>2</v>
       </c>
-      <c r="L39" s="20">
-        <v>3000</v>
-      </c>
-      <c r="M39" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="N39" s="20">
-        <v>1</v>
-      </c>
-      <c r="O39" s="20">
-        <v>30</v>
-      </c>
-      <c r="P39" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q39" s="20">
-        <v>1</v>
-      </c>
-      <c r="R39" s="20">
-        <v>0</v>
-      </c>
-      <c r="S39" s="20">
-        <v>0</v>
-      </c>
-      <c r="T39" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="U39" s="20">
-        <v>4000</v>
-      </c>
-      <c r="V39" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="W39" s="20">
+      <c r="L39" s="19">
         <v>10000</v>
       </c>
-      <c r="X39" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y39" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="20">
-        <v>1</v>
-      </c>
-      <c r="AA39" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="AB39" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC39" s="20">
-        <v>1000</v>
+      <c r="M39" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="N39" s="19">
+        <v>1</v>
+      </c>
+      <c r="O39" s="19">
+        <v>1</v>
+      </c>
+      <c r="P39" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q39" s="19">
+        <v>1</v>
+      </c>
+      <c r="R39" s="19">
+        <v>100</v>
+      </c>
+      <c r="S39" s="19">
+        <v>0</v>
+      </c>
+      <c r="T39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="U39" s="19">
+        <v>-1</v>
+      </c>
+      <c r="V39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W39" s="19">
+        <v>10000</v>
+      </c>
+      <c r="X39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y39" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB39" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="19">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A40" s="20">
-        <v>58020001</v>
-      </c>
-      <c r="B40" s="20">
-        <v>5802</v>
-      </c>
-      <c r="C40" s="20">
-        <v>1</v>
-      </c>
-      <c r="D40" s="20">
-        <v>0</v>
-      </c>
-      <c r="E40" s="20">
-        <v>3580500</v>
+      <c r="A40" s="19">
+        <v>57060001</v>
+      </c>
+      <c r="B40" s="19">
+        <v>5706</v>
+      </c>
+      <c r="C40" s="19">
+        <v>1</v>
+      </c>
+      <c r="D40" s="19">
+        <v>0</v>
+      </c>
+      <c r="E40" s="19">
+        <v>3571300</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="J40" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="K40" s="20">
-        <v>1</v>
-      </c>
-      <c r="L40" s="20">
-        <v>8</v>
-      </c>
-      <c r="M40" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="N40" s="20">
+        <v>241</v>
+      </c>
+      <c r="J40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="K40" s="19">
+        <v>0</v>
+      </c>
+      <c r="L40" s="19">
+        <v>0</v>
+      </c>
+      <c r="M40" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="N40" s="19">
         <v>2</v>
       </c>
-      <c r="O40" s="20">
+      <c r="O40" s="19">
         <v>10000</v>
       </c>
-      <c r="P40" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="Q40" s="20">
-        <v>1</v>
-      </c>
-      <c r="R40" s="20">
-        <v>1</v>
-      </c>
-      <c r="S40" s="20">
-        <v>0</v>
-      </c>
-      <c r="T40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="U40" s="20">
+      <c r="P40" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q40" s="19">
+        <v>1</v>
+      </c>
+      <c r="R40" s="19">
+        <v>1</v>
+      </c>
+      <c r="S40" s="19">
+        <v>0</v>
+      </c>
+      <c r="T40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="U40" s="19">
         <v>-1</v>
       </c>
-      <c r="V40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="W40" s="20">
+      <c r="V40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="W40" s="19">
         <v>10000</v>
       </c>
-      <c r="X40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y40" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="20">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB40" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="20">
+      <c r="X40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y40" s="19">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="19">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB40" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A41" s="20">
-        <v>58030001</v>
+        <v>58010001</v>
       </c>
       <c r="B41" s="20">
-        <v>5803</v>
+        <v>5801</v>
       </c>
       <c r="C41" s="20">
         <v>1</v>
@@ -5522,43 +6066,43 @@
         <v>0</v>
       </c>
       <c r="E41" s="20">
-        <v>3580700</v>
+        <v>3580200</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>358</v>
+        <v>202</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>358</v>
+        <v>202</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>359</v>
+        <v>335</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="K41" s="20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L41" s="20">
-        <v>5</v>
+        <v>3000</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>360</v>
+        <v>225</v>
       </c>
       <c r="N41" s="20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O41" s="20">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="P41" s="20" t="s">
         <v>43</v>
       </c>
       <c r="Q41" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" s="20">
         <v>0</v>
@@ -5567,10 +6111,10 @@
         <v>0</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>43</v>
+        <v>368</v>
       </c>
       <c r="U41" s="20">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="V41" s="20" t="s">
         <v>43</v>
@@ -5579,7 +6123,7 @@
         <v>10000</v>
       </c>
       <c r="X41" s="20" t="s">
-        <v>43</v>
+        <v>226</v>
       </c>
       <c r="Y41" s="20">
         <v>1</v>
@@ -5588,21 +6132,21 @@
         <v>1</v>
       </c>
       <c r="AA41" s="20" t="s">
-        <v>43</v>
+        <v>340</v>
       </c>
       <c r="AB41" s="20">
         <v>1</v>
       </c>
       <c r="AC41" s="20">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="42" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A42" s="20">
-        <v>58040001</v>
+        <v>58020001</v>
       </c>
       <c r="B42" s="20">
-        <v>5804</v>
+        <v>5802</v>
       </c>
       <c r="C42" s="20">
         <v>1</v>
@@ -5611,31 +6155,31 @@
         <v>0</v>
       </c>
       <c r="E42" s="20">
-        <v>3580900</v>
+        <v>3580500</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>43</v>
+        <v>227</v>
       </c>
       <c r="K42" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="20">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="N42" s="20">
         <v>2</v>
@@ -5644,7 +6188,7 @@
         <v>10000</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q42" s="20">
         <v>1</v>
@@ -5659,7 +6203,7 @@
         <v>43</v>
       </c>
       <c r="U42" s="20">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V42" s="20" t="s">
         <v>43</v>
@@ -5687,50 +6231,50 @@
       </c>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A43" s="23">
-        <v>58050001</v>
-      </c>
-      <c r="B43" s="23">
-        <v>5805</v>
-      </c>
-      <c r="C43" s="23">
-        <v>1</v>
-      </c>
-      <c r="D43" s="23">
-        <v>0</v>
-      </c>
-      <c r="E43" s="23">
-        <v>3581200</v>
+      <c r="A43" s="20">
+        <v>58030001</v>
+      </c>
+      <c r="B43" s="20">
+        <v>5803</v>
+      </c>
+      <c r="C43" s="20">
+        <v>1</v>
+      </c>
+      <c r="D43" s="20">
+        <v>0</v>
+      </c>
+      <c r="E43" s="20">
+        <v>3580700</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>188</v>
+        <v>358</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>191</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>188</v>
+        <v>358</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
       <c r="J43" s="20" t="s">
-        <v>322</v>
+        <v>230</v>
       </c>
       <c r="K43" s="20">
+        <v>1</v>
+      </c>
+      <c r="L43" s="20">
+        <v>5</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="N43" s="20">
         <v>2</v>
       </c>
-      <c r="L43" s="20">
-        <v>3000</v>
-      </c>
-      <c r="M43" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="N43" s="20">
-        <v>0</v>
-      </c>
       <c r="O43" s="20">
-        <v>30</v>
+        <v>10000</v>
       </c>
       <c r="P43" s="20" t="s">
         <v>43</v>
@@ -5745,10 +6289,10 @@
         <v>0</v>
       </c>
       <c r="T43" s="20" t="s">
-        <v>369</v>
+        <v>43</v>
       </c>
       <c r="U43" s="20">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="V43" s="20" t="s">
         <v>43</v>
@@ -5757,200 +6301,208 @@
         <v>10000</v>
       </c>
       <c r="X43" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y43" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB43" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A44" s="20">
+        <v>58040001</v>
+      </c>
+      <c r="B44" s="20">
+        <v>5804</v>
+      </c>
+      <c r="C44" s="20">
+        <v>1</v>
+      </c>
+      <c r="D44" s="20">
+        <v>0</v>
+      </c>
+      <c r="E44" s="20">
+        <v>3580900</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="H44" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="I44" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="K44" s="20">
+        <v>0</v>
+      </c>
+      <c r="L44" s="20">
+        <v>0</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="N44" s="20">
+        <v>2</v>
+      </c>
+      <c r="O44" s="20">
+        <v>10000</v>
+      </c>
+      <c r="P44" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q44" s="20">
+        <v>1</v>
+      </c>
+      <c r="R44" s="20">
+        <v>1</v>
+      </c>
+      <c r="S44" s="20">
+        <v>0</v>
+      </c>
+      <c r="T44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="U44" s="20">
+        <v>0</v>
+      </c>
+      <c r="V44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W44" s="20">
+        <v>10000</v>
+      </c>
+      <c r="X44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y44" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA44" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB44" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A45" s="23">
+        <v>58050001</v>
+      </c>
+      <c r="B45" s="23">
+        <v>5805</v>
+      </c>
+      <c r="C45" s="23">
+        <v>1</v>
+      </c>
+      <c r="D45" s="23">
+        <v>0</v>
+      </c>
+      <c r="E45" s="23">
+        <v>3581200</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="H45" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="I45" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="K45" s="20">
+        <v>2</v>
+      </c>
+      <c r="L45" s="20">
+        <v>3000</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="N45" s="20">
+        <v>0</v>
+      </c>
+      <c r="O45" s="20">
+        <v>30</v>
+      </c>
+      <c r="P45" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q45" s="20">
+        <v>0</v>
+      </c>
+      <c r="R45" s="20">
+        <v>0</v>
+      </c>
+      <c r="S45" s="20">
+        <v>0</v>
+      </c>
+      <c r="T45" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="U45" s="20">
+        <v>4000</v>
+      </c>
+      <c r="V45" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="W45" s="20">
+        <v>10000</v>
+      </c>
+      <c r="X45" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="Y43" s="20">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="20">
+      <c r="Y45" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="20">
         <v>10</v>
       </c>
-      <c r="AA43" s="20" t="s">
+      <c r="AA45" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="AB43" s="20">
-        <v>1</v>
-      </c>
-      <c r="AC43" s="20">
+      <c r="AB45" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="20">
         <v>1000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A44" s="24">
-        <v>59010001</v>
-      </c>
-      <c r="B44" s="24">
-        <v>5901</v>
-      </c>
-      <c r="C44" s="24">
-        <v>1</v>
-      </c>
-      <c r="D44" s="24">
-        <v>0</v>
-      </c>
-      <c r="E44" s="24">
-        <v>3590200</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="24" t="s">
-        <v>279</v>
-      </c>
-      <c r="K44" s="24">
-        <v>3</v>
-      </c>
-      <c r="L44" s="24">
-        <v>200000</v>
-      </c>
-      <c r="M44" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="N44" s="24">
-        <v>2</v>
-      </c>
-      <c r="O44" s="24">
-        <v>10000</v>
-      </c>
-      <c r="P44" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q44" s="24">
-        <v>1</v>
-      </c>
-      <c r="R44" s="24">
-        <v>1</v>
-      </c>
-      <c r="S44" s="24">
-        <v>0</v>
-      </c>
-      <c r="T44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="U44" s="24">
-        <v>0</v>
-      </c>
-      <c r="V44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="W44" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y44" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="24">
-        <v>1</v>
-      </c>
-      <c r="AA44" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB44" s="24">
-        <v>1</v>
-      </c>
-      <c r="AC44" s="24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A45" s="24">
-        <v>59020001</v>
-      </c>
-      <c r="B45" s="24">
-        <v>5902</v>
-      </c>
-      <c r="C45" s="24">
-        <v>1</v>
-      </c>
-      <c r="D45" s="24">
-        <v>0</v>
-      </c>
-      <c r="E45" s="24">
-        <v>3590400</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="K45" s="24">
-        <v>3</v>
-      </c>
-      <c r="L45" s="24">
-        <v>200000</v>
-      </c>
-      <c r="M45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="N45" s="24">
-        <v>0</v>
-      </c>
-      <c r="O45" s="24">
-        <v>0</v>
-      </c>
-      <c r="P45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q45" s="24">
-        <v>0</v>
-      </c>
-      <c r="R45" s="24">
-        <v>0</v>
-      </c>
-      <c r="S45" s="24">
-        <v>59030001</v>
-      </c>
-      <c r="T45" s="24" t="s">
-        <v>370</v>
-      </c>
-      <c r="U45" s="24">
-        <v>-1</v>
-      </c>
-      <c r="V45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="W45" s="24">
-        <v>10000</v>
-      </c>
-      <c r="X45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y45" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="24">
-        <v>1</v>
-      </c>
-      <c r="AA45" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB45" s="24">
-        <v>1</v>
-      </c>
-      <c r="AC45" s="24">
-        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A46" s="24">
-        <v>59030001</v>
+        <v>59010001</v>
       </c>
       <c r="B46" s="24">
-        <v>5903</v>
+        <v>5901</v>
       </c>
       <c r="C46" s="24">
         <v>1</v>
@@ -5959,10 +6511,10 @@
         <v>0</v>
       </c>
       <c r="E46" s="24">
-        <v>3590600</v>
+        <v>3590200</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G46" s="13" t="s">
         <v>245</v>
@@ -5970,16 +6522,16 @@
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="24" t="s">
-        <v>43</v>
+        <v>279</v>
       </c>
       <c r="K46" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="24">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="N46" s="24">
         <v>2</v>
@@ -5988,7 +6540,7 @@
         <v>10000</v>
       </c>
       <c r="P46" s="24" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q46" s="24">
         <v>1</v>
@@ -5997,7 +6549,7 @@
         <v>1</v>
       </c>
       <c r="S46" s="24">
-        <v>59200001</v>
+        <v>0</v>
       </c>
       <c r="T46" s="24" t="s">
         <v>43</v>
@@ -6032,10 +6584,10 @@
     </row>
     <row r="47" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A47" s="24">
-        <v>59040001</v>
+        <v>59020001</v>
       </c>
       <c r="B47" s="24">
-        <v>5904</v>
+        <v>5902</v>
       </c>
       <c r="C47" s="24">
         <v>1</v>
@@ -6044,10 +6596,10 @@
         <v>0</v>
       </c>
       <c r="E47" s="24">
-        <v>3590800</v>
+        <v>3590400</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G47" s="13" t="s">
         <v>245</v>
@@ -6055,37 +6607,37 @@
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="24" t="s">
-        <v>43</v>
+        <v>282</v>
       </c>
       <c r="K47" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" s="24">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M47" s="24" t="s">
-        <v>285</v>
+        <v>43</v>
       </c>
       <c r="N47" s="24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P47" s="24" t="s">
-        <v>286</v>
+        <v>43</v>
       </c>
       <c r="Q47" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" s="24">
-        <v>59090001</v>
+        <v>59030001</v>
       </c>
       <c r="T47" s="24" t="s">
-        <v>43</v>
+        <v>370</v>
       </c>
       <c r="U47" s="24">
         <v>-1</v>
@@ -6117,10 +6669,10 @@
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A48" s="24">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B48" s="24">
-        <v>5905</v>
+        <v>5903</v>
       </c>
       <c r="C48" s="24">
         <v>1</v>
@@ -6129,10 +6681,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="24">
-        <v>3591000</v>
+        <v>3590600</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G48" s="13" t="s">
         <v>245</v>
@@ -6140,40 +6692,40 @@
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
       <c r="J48" s="24" t="s">
-        <v>287</v>
+        <v>43</v>
       </c>
       <c r="K48" s="24">
+        <v>0</v>
+      </c>
+      <c r="L48" s="24">
+        <v>0</v>
+      </c>
+      <c r="M48" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="N48" s="24">
         <v>2</v>
       </c>
-      <c r="L48" s="24">
-        <v>0</v>
-      </c>
-      <c r="M48" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="N48" s="24">
-        <v>1</v>
-      </c>
       <c r="O48" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P48" s="24" t="s">
-        <v>343</v>
+        <v>284</v>
       </c>
       <c r="Q48" s="24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R48" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48" s="24">
-        <v>0</v>
+        <v>59200001</v>
       </c>
       <c r="T48" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U48" s="24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V48" s="24" t="s">
         <v>43</v>
@@ -6202,10 +6754,10 @@
     </row>
     <row r="49" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A49" s="24">
-        <v>59060001</v>
+        <v>59040001</v>
       </c>
       <c r="B49" s="24">
-        <v>5906</v>
+        <v>5904</v>
       </c>
       <c r="C49" s="24">
         <v>1</v>
@@ -6214,10 +6766,10 @@
         <v>0</v>
       </c>
       <c r="E49" s="24">
-        <v>3591200</v>
+        <v>3590800</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G49" s="13" t="s">
         <v>245</v>
@@ -6225,16 +6777,16 @@
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
       <c r="J49" s="24" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="K49" s="24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L49" s="24">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6243,7 +6795,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6252,7 +6804,7 @@
         <v>1</v>
       </c>
       <c r="S49" s="24">
-        <v>0</v>
+        <v>59090001</v>
       </c>
       <c r="T49" s="24" t="s">
         <v>43</v>
@@ -6287,10 +6839,10 @@
     </row>
     <row r="50" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A50" s="24">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B50" s="24">
-        <v>5907</v>
+        <v>5905</v>
       </c>
       <c r="C50" s="24">
         <v>1</v>
@@ -6299,10 +6851,10 @@
         <v>0</v>
       </c>
       <c r="E50" s="24">
-        <v>3591400</v>
+        <v>3591000</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G50" s="13" t="s">
         <v>245</v>
@@ -6310,34 +6862,34 @@
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="K50" s="24">
+        <v>2</v>
+      </c>
+      <c r="L50" s="24">
+        <v>0</v>
+      </c>
+      <c r="M50" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="N50" s="24">
+        <v>1</v>
+      </c>
+      <c r="O50" s="24">
+        <v>0</v>
+      </c>
+      <c r="P50" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="Q50" s="24">
         <v>3</v>
       </c>
-      <c r="L50" s="24">
-        <v>500000</v>
-      </c>
-      <c r="M50" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="N50" s="24">
-        <v>2</v>
-      </c>
-      <c r="O50" s="24">
-        <v>10000</v>
-      </c>
-      <c r="P50" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q50" s="24">
-        <v>1</v>
-      </c>
       <c r="R50" s="24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50" s="24">
-        <v>59200002</v>
+        <v>0</v>
       </c>
       <c r="T50" s="24" t="s">
         <v>43</v>
@@ -6372,10 +6924,10 @@
     </row>
     <row r="51" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A51" s="24">
-        <v>59080001</v>
+        <v>59060001</v>
       </c>
       <c r="B51" s="24">
-        <v>5908</v>
+        <v>5906</v>
       </c>
       <c r="C51" s="24">
         <v>1</v>
@@ -6384,10 +6936,10 @@
         <v>0</v>
       </c>
       <c r="E51" s="24">
-        <v>3591600</v>
+        <v>3591200</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G51" s="13" t="s">
         <v>245</v>
@@ -6395,16 +6947,16 @@
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="24" t="s">
-        <v>43</v>
+        <v>288</v>
       </c>
       <c r="K51" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L51" s="24">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -6413,7 +6965,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -6422,13 +6974,13 @@
         <v>1</v>
       </c>
       <c r="S51" s="24">
-        <v>90000001</v>
+        <v>0</v>
       </c>
       <c r="T51" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U51" s="24">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V51" s="24" t="s">
         <v>43</v>
@@ -6457,10 +7009,10 @@
     </row>
     <row r="52" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A52" s="24">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B52" s="24">
-        <v>5909</v>
+        <v>5907</v>
       </c>
       <c r="C52" s="24">
         <v>1</v>
@@ -6469,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="E52" s="24">
-        <v>3591900</v>
+        <v>3591400</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>361</v>
+        <v>252</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>245</v>
@@ -6480,34 +7032,34 @@
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="24" t="s">
-        <v>43</v>
+        <v>291</v>
       </c>
       <c r="K52" s="24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="24">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="N52" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" s="24">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="P52" s="24" t="s">
-        <v>43</v>
+        <v>293</v>
       </c>
       <c r="Q52" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52" s="24">
-        <v>0</v>
+        <v>59200002</v>
       </c>
       <c r="T52" s="24" t="s">
         <v>43</v>
@@ -6531,21 +7083,21 @@
         <v>1</v>
       </c>
       <c r="AA52" s="24" t="s">
-        <v>362</v>
+        <v>43</v>
       </c>
       <c r="AB52" s="24">
         <v>1</v>
       </c>
       <c r="AC52" s="24">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A53" s="24">
-        <v>59100001</v>
+        <v>59080001</v>
       </c>
       <c r="B53" s="24">
-        <v>5910</v>
+        <v>5908</v>
       </c>
       <c r="C53" s="24">
         <v>1</v>
@@ -6554,10 +7106,10 @@
         <v>0</v>
       </c>
       <c r="E53" s="24">
-        <v>3541800</v>
+        <v>3591600</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>315</v>
+        <v>253</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>245</v>
@@ -6568,37 +7120,37 @@
         <v>43</v>
       </c>
       <c r="K53" s="24">
+        <v>0</v>
+      </c>
+      <c r="L53" s="24">
+        <v>0</v>
+      </c>
+      <c r="M53" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="N53" s="24">
         <v>2</v>
       </c>
-      <c r="L53" s="24">
-        <v>1500</v>
-      </c>
-      <c r="M53" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="N53" s="24">
-        <v>0</v>
-      </c>
       <c r="O53" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P53" s="24" t="s">
-        <v>43</v>
+        <v>295</v>
       </c>
       <c r="Q53" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53" s="24">
-        <v>0</v>
+        <v>90000001</v>
       </c>
       <c r="T53" s="24" t="s">
         <v>43</v>
       </c>
       <c r="U53" s="24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="24" t="s">
         <v>43</v>
@@ -6627,10 +7179,10 @@
     </row>
     <row r="54" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A54" s="24">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B54" s="24">
-        <v>5911</v>
+        <v>5909</v>
       </c>
       <c r="C54" s="24">
         <v>1</v>
@@ -6639,10 +7191,10 @@
         <v>0</v>
       </c>
       <c r="E54" s="24">
-        <v>3541800</v>
+        <v>3591900</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>245</v>
@@ -6653,19 +7205,19 @@
         <v>43</v>
       </c>
       <c r="K54" s="24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="24">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="M54" s="24" t="s">
-        <v>43</v>
+        <v>296</v>
       </c>
       <c r="N54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P54" s="24" t="s">
         <v>43</v>
@@ -6701,21 +7253,21 @@
         <v>1</v>
       </c>
       <c r="AA54" s="24" t="s">
-        <v>43</v>
+        <v>362</v>
       </c>
       <c r="AB54" s="24">
         <v>1</v>
       </c>
       <c r="AC54" s="24">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="55" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A55" s="25">
-        <v>59120001</v>
+      <c r="A55" s="24">
+        <v>59100001</v>
       </c>
       <c r="B55" s="24">
-        <v>5912</v>
+        <v>5910</v>
       </c>
       <c r="C55" s="24">
         <v>1</v>
@@ -6724,10 +7276,10 @@
         <v>0</v>
       </c>
       <c r="E55" s="24">
-        <v>3592100</v>
+        <v>3541800</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>373</v>
+        <v>315</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>245</v>
@@ -6735,13 +7287,13 @@
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
       <c r="J55" s="24" t="s">
-        <v>372</v>
+        <v>43</v>
       </c>
       <c r="K55" s="24">
         <v>2</v>
       </c>
       <c r="L55" s="24">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M55" s="24" t="s">
         <v>43</v>
@@ -6796,181 +7348,181 @@
       </c>
     </row>
     <row r="56" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A56" s="21">
-        <v>60010001</v>
-      </c>
-      <c r="B56" s="21">
-        <v>6001</v>
-      </c>
-      <c r="C56" s="21">
-        <v>1</v>
-      </c>
-      <c r="D56" s="21">
-        <v>0</v>
-      </c>
-      <c r="E56" s="21">
-        <v>3600200</v>
+      <c r="A56" s="24">
+        <v>59110001</v>
+      </c>
+      <c r="B56" s="24">
+        <v>5911</v>
+      </c>
+      <c r="C56" s="24">
+        <v>1</v>
+      </c>
+      <c r="D56" s="24">
+        <v>0</v>
+      </c>
+      <c r="E56" s="24">
+        <v>3541800</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>257</v>
+        <v>316</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
-      <c r="J56" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="K56" s="21">
-        <v>1</v>
-      </c>
-      <c r="L56" s="21">
-        <v>8</v>
-      </c>
-      <c r="M56" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="N56" s="21">
+      <c r="J56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="K56" s="24">
         <v>2</v>
       </c>
-      <c r="O56" s="21">
+      <c r="L56" s="24">
+        <v>5000</v>
+      </c>
+      <c r="M56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N56" s="24">
+        <v>0</v>
+      </c>
+      <c r="O56" s="24">
+        <v>0</v>
+      </c>
+      <c r="P56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q56" s="24">
+        <v>0</v>
+      </c>
+      <c r="R56" s="24">
+        <v>0</v>
+      </c>
+      <c r="S56" s="24">
+        <v>0</v>
+      </c>
+      <c r="T56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U56" s="24">
+        <v>-1</v>
+      </c>
+      <c r="V56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" s="24">
         <v>10000</v>
       </c>
-      <c r="P56" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q56" s="21">
-        <v>1</v>
-      </c>
-      <c r="R56" s="21">
-        <v>1</v>
-      </c>
-      <c r="S56" s="21">
-        <v>0</v>
-      </c>
-      <c r="T56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U56" s="21">
-        <v>0</v>
-      </c>
-      <c r="V56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W56" s="21">
-        <v>10000</v>
-      </c>
-      <c r="X56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y56" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z56" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA56" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB56" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC56" s="21">
+      <c r="X56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y56" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA56" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB56" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A57" s="21">
-        <v>60020001</v>
-      </c>
-      <c r="B57" s="21">
-        <v>6002</v>
-      </c>
-      <c r="C57" s="21">
-        <v>1</v>
-      </c>
-      <c r="D57" s="21">
-        <v>0</v>
-      </c>
-      <c r="E57" s="21">
-        <v>3600400</v>
+      <c r="A57" s="25">
+        <v>59120001</v>
+      </c>
+      <c r="B57" s="24">
+        <v>5912</v>
+      </c>
+      <c r="C57" s="24">
+        <v>1</v>
+      </c>
+      <c r="D57" s="24">
+        <v>0</v>
+      </c>
+      <c r="E57" s="24">
+        <v>3592100</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>258</v>
+        <v>373</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
-      <c r="J57" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="K57" s="21">
-        <v>1</v>
-      </c>
-      <c r="L57" s="21">
-        <v>1</v>
-      </c>
-      <c r="M57" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="N57" s="21">
+      <c r="J57" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="K57" s="24">
         <v>2</v>
       </c>
-      <c r="O57" s="21">
-        <v>15000</v>
-      </c>
-      <c r="P57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q57" s="21">
-        <v>0</v>
-      </c>
-      <c r="R57" s="21">
-        <v>0</v>
-      </c>
-      <c r="S57" s="21">
-        <v>0</v>
-      </c>
-      <c r="T57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U57" s="21">
+      <c r="L57" s="24">
+        <v>0</v>
+      </c>
+      <c r="M57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N57" s="24">
+        <v>0</v>
+      </c>
+      <c r="O57" s="24">
+        <v>0</v>
+      </c>
+      <c r="P57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q57" s="24">
+        <v>0</v>
+      </c>
+      <c r="R57" s="24">
+        <v>0</v>
+      </c>
+      <c r="S57" s="24">
+        <v>0</v>
+      </c>
+      <c r="T57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U57" s="24">
         <v>-1</v>
       </c>
-      <c r="V57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W57" s="21">
+      <c r="V57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" s="24">
         <v>10000</v>
       </c>
-      <c r="X57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y57" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z57" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB57" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC57" s="21">
+      <c r="X57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y57" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB57" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A58" s="21">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B58" s="21">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="C58" s="21">
         <v>1</v>
@@ -6979,10 +7531,10 @@
         <v>0</v>
       </c>
       <c r="E58" s="21">
-        <v>3600700</v>
+        <v>3600200</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>254</v>
@@ -6990,7 +7542,7 @@
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="21" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="K58" s="21">
         <v>1</v>
@@ -6999,7 +7551,7 @@
         <v>8</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="N58" s="21">
         <v>2</v>
@@ -7008,7 +7560,7 @@
         <v>10000</v>
       </c>
       <c r="P58" s="21" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="Q58" s="21">
         <v>1</v>
@@ -7052,10 +7604,10 @@
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A59" s="21">
-        <v>60040001</v>
+        <v>60020001</v>
       </c>
       <c r="B59" s="21">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="C59" s="21">
         <v>1</v>
@@ -7064,10 +7616,10 @@
         <v>0</v>
       </c>
       <c r="E59" s="21">
-        <v>3601000</v>
+        <v>3600400</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>254</v>
@@ -7075,31 +7627,31 @@
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
       <c r="J59" s="21" t="s">
-        <v>43</v>
+        <v>264</v>
       </c>
       <c r="K59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" s="21" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="N59" s="21">
         <v>2</v>
       </c>
       <c r="O59" s="21">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P59" s="21" t="s">
-        <v>269</v>
+        <v>43</v>
       </c>
       <c r="Q59" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59" s="21">
         <v>0</v>
@@ -7108,7 +7660,7 @@
         <v>43</v>
       </c>
       <c r="U59" s="21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V59" s="21" t="s">
         <v>43</v>
@@ -7137,10 +7689,10 @@
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60" s="21">
-        <v>60050001</v>
+        <v>60030001</v>
       </c>
       <c r="B60" s="21">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="C60" s="21">
         <v>1</v>
@@ -7149,10 +7701,10 @@
         <v>0</v>
       </c>
       <c r="E60" s="21">
-        <v>3541600</v>
+        <v>3600700</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>254</v>
@@ -7160,31 +7712,31 @@
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>119</v>
+        <v>297</v>
       </c>
       <c r="K60" s="21">
+        <v>1</v>
+      </c>
+      <c r="L60" s="21">
+        <v>8</v>
+      </c>
+      <c r="M60" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="N60" s="21">
         <v>2</v>
       </c>
-      <c r="L60" s="21">
-        <v>-2000</v>
-      </c>
-      <c r="M60" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N60" s="21">
-        <v>0</v>
-      </c>
       <c r="O60" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P60" s="21" t="s">
-        <v>43</v>
+        <v>267</v>
       </c>
       <c r="Q60" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="21">
         <v>0</v>
@@ -7193,7 +7745,7 @@
         <v>43</v>
       </c>
       <c r="U60" s="21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V60" s="21" t="s">
         <v>43</v>
@@ -7222,10 +7774,10 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A61" s="21">
-        <v>60060001</v>
+        <v>60040001</v>
       </c>
       <c r="B61" s="21">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="C61" s="21">
         <v>1</v>
@@ -7234,10 +7786,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="21">
-        <v>3541800</v>
+        <v>3601000</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>254</v>
@@ -7245,31 +7797,31 @@
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
       <c r="J61" s="21" t="s">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="K61" s="21">
+        <v>0</v>
+      </c>
+      <c r="L61" s="21">
+        <v>0</v>
+      </c>
+      <c r="M61" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="N61" s="21">
         <v>2</v>
       </c>
-      <c r="L61" s="21">
-        <v>2500</v>
-      </c>
-      <c r="M61" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N61" s="21">
-        <v>0</v>
-      </c>
       <c r="O61" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P61" s="21" t="s">
-        <v>43</v>
+        <v>269</v>
       </c>
       <c r="Q61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="21">
         <v>0</v>
@@ -7278,7 +7830,7 @@
         <v>43</v>
       </c>
       <c r="U61" s="21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V61" s="21" t="s">
         <v>43</v>
@@ -7307,10 +7859,10 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A62" s="21">
-        <v>60070001</v>
+        <v>60050001</v>
       </c>
       <c r="B62" s="21">
-        <v>6007</v>
+        <v>6005</v>
       </c>
       <c r="C62" s="21">
         <v>1</v>
@@ -7319,10 +7871,10 @@
         <v>0</v>
       </c>
       <c r="E62" s="21">
-        <v>3601300</v>
+        <v>3541600</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>254</v>
@@ -7330,28 +7882,28 @@
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>270</v>
+        <v>119</v>
       </c>
       <c r="K62" s="21">
         <v>2</v>
       </c>
       <c r="L62" s="21">
-        <v>10000</v>
+        <v>-2000</v>
       </c>
       <c r="M62" s="21" t="s">
-        <v>271</v>
+        <v>43</v>
       </c>
       <c r="N62" s="21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O62" s="21">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P62" s="21" t="s">
-        <v>272</v>
+        <v>43</v>
       </c>
       <c r="Q62" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" s="21">
         <v>0</v>
@@ -7391,181 +7943,181 @@
       </c>
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A63" s="22">
-        <v>61010001</v>
-      </c>
-      <c r="B63" s="22">
-        <v>6101</v>
-      </c>
-      <c r="C63" s="22">
-        <v>1</v>
-      </c>
-      <c r="D63" s="22">
-        <v>0</v>
-      </c>
-      <c r="E63" s="22">
-        <v>3610300</v>
+      <c r="A63" s="21">
+        <v>60060001</v>
+      </c>
+      <c r="B63" s="21">
+        <v>6006</v>
+      </c>
+      <c r="C63" s="21">
+        <v>1</v>
+      </c>
+      <c r="D63" s="21">
+        <v>0</v>
+      </c>
+      <c r="E63" s="21">
+        <v>3541800</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
-      <c r="J63" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="K63" s="22">
-        <v>1</v>
-      </c>
-      <c r="L63" s="22">
-        <v>8</v>
-      </c>
-      <c r="M63" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="N63" s="22">
+      <c r="J63" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="K63" s="21">
         <v>2</v>
       </c>
-      <c r="O63" s="22">
+      <c r="L63" s="21">
+        <v>2500</v>
+      </c>
+      <c r="M63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N63" s="21">
+        <v>0</v>
+      </c>
+      <c r="O63" s="21">
+        <v>0</v>
+      </c>
+      <c r="P63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q63" s="21">
+        <v>0</v>
+      </c>
+      <c r="R63" s="21">
+        <v>0</v>
+      </c>
+      <c r="S63" s="21">
+        <v>0</v>
+      </c>
+      <c r="T63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U63" s="21">
+        <v>-1</v>
+      </c>
+      <c r="V63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" s="21">
         <v>10000</v>
       </c>
-      <c r="P63" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="Q63" s="22">
-        <v>1</v>
-      </c>
-      <c r="R63" s="22">
-        <v>1</v>
-      </c>
-      <c r="S63" s="22">
-        <v>0</v>
-      </c>
-      <c r="T63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U63" s="22">
-        <v>0</v>
-      </c>
-      <c r="V63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W63" s="22">
-        <v>10000</v>
-      </c>
-      <c r="X63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y63" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB63" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC63" s="22">
+      <c r="X63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y63" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB63" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC63" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A64" s="22">
-        <v>61020001</v>
-      </c>
-      <c r="B64" s="22">
-        <v>6102</v>
-      </c>
-      <c r="C64" s="22">
-        <v>1</v>
-      </c>
-      <c r="D64" s="22">
-        <v>0</v>
-      </c>
-      <c r="E64" s="22">
-        <v>3610500</v>
+      <c r="A64" s="21">
+        <v>60070001</v>
+      </c>
+      <c r="B64" s="21">
+        <v>6007</v>
+      </c>
+      <c r="C64" s="21">
+        <v>1</v>
+      </c>
+      <c r="D64" s="21">
+        <v>0</v>
+      </c>
+      <c r="E64" s="21">
+        <v>3601300</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
-      <c r="J64" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="K64" s="22">
+      <c r="J64" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="K64" s="21">
         <v>2</v>
       </c>
-      <c r="L64" s="22">
+      <c r="L64" s="21">
         <v>10000</v>
       </c>
-      <c r="M64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="N64" s="22">
-        <v>0</v>
-      </c>
-      <c r="O64" s="22">
-        <v>0</v>
-      </c>
-      <c r="P64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q64" s="22">
-        <v>0</v>
-      </c>
-      <c r="R64" s="22">
-        <v>0</v>
-      </c>
-      <c r="S64" s="22">
-        <v>0</v>
-      </c>
-      <c r="T64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U64" s="22">
+      <c r="M64" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="N64" s="21">
+        <v>2</v>
+      </c>
+      <c r="O64" s="21">
+        <v>2000</v>
+      </c>
+      <c r="P64" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q64" s="21">
+        <v>1</v>
+      </c>
+      <c r="R64" s="21">
+        <v>0</v>
+      </c>
+      <c r="S64" s="21">
+        <v>0</v>
+      </c>
+      <c r="T64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U64" s="21">
         <v>-1</v>
       </c>
-      <c r="V64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W64" s="22">
+      <c r="V64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W64" s="21">
         <v>10000</v>
       </c>
-      <c r="X64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y64" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z64" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA64" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB64" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC64" s="22">
+      <c r="X64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y64" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB64" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A65" s="22">
-        <v>61030001</v>
+        <v>61010001</v>
       </c>
       <c r="B65" s="22">
-        <v>6103</v>
+        <v>6101</v>
       </c>
       <c r="C65" s="22">
         <v>1</v>
@@ -7574,10 +8126,10 @@
         <v>0</v>
       </c>
       <c r="E65" s="22">
-        <v>3610700</v>
+        <v>3610300</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>255</v>
@@ -7585,16 +8137,16 @@
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
       <c r="J65" s="22" t="s">
-        <v>43</v>
+        <v>273</v>
       </c>
       <c r="K65" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="N65" s="22">
         <v>2</v>
@@ -7603,7 +8155,7 @@
         <v>10000</v>
       </c>
       <c r="P65" s="22" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q65" s="22">
         <v>1</v>
@@ -7647,10 +8199,10 @@
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A66" s="22">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B66" s="22">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="C66" s="22">
         <v>1</v>
@@ -7659,10 +8211,10 @@
         <v>0</v>
       </c>
       <c r="E66" s="22">
-        <v>3541400</v>
+        <v>3610500</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="G66" s="13" t="s">
         <v>255</v>
@@ -7670,13 +8222,13 @@
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="22" t="s">
-        <v>118</v>
+        <v>276</v>
       </c>
       <c r="K66" s="22">
         <v>2</v>
       </c>
       <c r="L66" s="22">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M66" s="22" t="s">
         <v>43</v>
@@ -7732,10 +8284,10 @@
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A67" s="22">
-        <v>61050001</v>
+        <v>61030001</v>
       </c>
       <c r="B67" s="22">
-        <v>6105</v>
+        <v>6103</v>
       </c>
       <c r="C67" s="22">
         <v>1</v>
@@ -7744,10 +8296,10 @@
         <v>0</v>
       </c>
       <c r="E67" s="22">
-        <v>3610900</v>
+        <v>3610700</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G67" s="13" t="s">
         <v>255</v>
@@ -7755,31 +8307,31 @@
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
       <c r="J67" s="22" t="s">
-        <v>305</v>
+        <v>43</v>
       </c>
       <c r="K67" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" s="22" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
       <c r="N67" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O67" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P67" s="22" t="s">
-        <v>43</v>
+        <v>278</v>
       </c>
       <c r="Q67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67" s="22">
         <v>0</v>
@@ -7788,7 +8340,7 @@
         <v>43</v>
       </c>
       <c r="U67" s="22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V67" s="22" t="s">
         <v>43</v>
@@ -7817,10 +8369,10 @@
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B68" s="22">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="C68" s="22">
         <v>1</v>
@@ -7829,10 +8381,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="22">
-        <v>3611100</v>
+        <v>3541400</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>371</v>
+        <v>256</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>255</v>
@@ -7840,13 +8392,13 @@
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="22" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="K68" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="22">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M68" s="22" t="s">
         <v>43</v>
@@ -7902,10 +8454,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
-        <v>61070001</v>
+        <v>61050001</v>
       </c>
       <c r="B69" s="22">
-        <v>6107</v>
+        <v>6105</v>
       </c>
       <c r="C69" s="22">
         <v>1</v>
@@ -7914,10 +8466,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="22">
-        <v>3611300</v>
+        <v>3610900</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>255</v>
@@ -7925,13 +8477,13 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K69" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L69" s="22">
-        <v>300000</v>
+        <v>1</v>
       </c>
       <c r="M69" s="22" t="s">
         <v>43</v>
@@ -7943,13 +8495,13 @@
         <v>0</v>
       </c>
       <c r="P69" s="22" t="s">
-        <v>307</v>
+        <v>43</v>
       </c>
       <c r="Q69" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" s="22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S69" s="22">
         <v>0</v>
@@ -7987,10 +8539,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B70" s="22">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="C70" s="22">
         <v>1</v>
@@ -7999,10 +8551,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="22">
-        <v>3611500</v>
+        <v>3611100</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>255</v>
@@ -8019,22 +8571,22 @@
         <v>0</v>
       </c>
       <c r="M70" s="22" t="s">
-        <v>309</v>
+        <v>43</v>
       </c>
       <c r="N70" s="22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70" s="22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P70" s="22" t="s">
-        <v>310</v>
+        <v>43</v>
       </c>
       <c r="Q70" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70" s="22">
         <v>0</v>
@@ -8043,7 +8595,7 @@
         <v>43</v>
       </c>
       <c r="U70" s="22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V70" s="22" t="s">
         <v>43</v>
@@ -8072,10 +8624,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
-        <v>61090001</v>
+        <v>61070001</v>
       </c>
       <c r="B71" s="22">
-        <v>6109</v>
+        <v>6107</v>
       </c>
       <c r="C71" s="22">
         <v>1</v>
@@ -8084,10 +8636,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="22">
-        <v>3611700</v>
+        <v>3611300</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>255</v>
@@ -8095,7 +8647,7 @@
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K71" s="22">
         <v>3</v>
@@ -8113,13 +8665,13 @@
         <v>0</v>
       </c>
       <c r="P71" s="22" t="s">
-        <v>43</v>
+        <v>307</v>
       </c>
       <c r="Q71" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S71" s="22">
         <v>0</v>
@@ -8157,10 +8709,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B72" s="22">
-        <v>6110</v>
+        <v>6108</v>
       </c>
       <c r="C72" s="22">
         <v>1</v>
@@ -8169,10 +8721,10 @@
         <v>0</v>
       </c>
       <c r="E72" s="22">
-        <v>3590800</v>
+        <v>3611500</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>255</v>
@@ -8189,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="22" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="N72" s="22">
         <v>2</v>
@@ -8198,7 +8750,7 @@
         <v>10000</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>
@@ -8240,8 +8792,178 @@
         <v>0</v>
       </c>
     </row>
+    <row r="73" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A73" s="22">
+        <v>61090001</v>
+      </c>
+      <c r="B73" s="22">
+        <v>6109</v>
+      </c>
+      <c r="C73" s="22">
+        <v>1</v>
+      </c>
+      <c r="D73" s="22">
+        <v>0</v>
+      </c>
+      <c r="E73" s="22">
+        <v>3611700</v>
+      </c>
+      <c r="F73" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="H73" s="13"/>
+      <c r="I73" s="13"/>
+      <c r="J73" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="K73" s="22">
+        <v>3</v>
+      </c>
+      <c r="L73" s="22">
+        <v>300000</v>
+      </c>
+      <c r="M73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N73" s="22">
+        <v>0</v>
+      </c>
+      <c r="O73" s="22">
+        <v>0</v>
+      </c>
+      <c r="P73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q73" s="22">
+        <v>0</v>
+      </c>
+      <c r="R73" s="22">
+        <v>0</v>
+      </c>
+      <c r="S73" s="22">
+        <v>0</v>
+      </c>
+      <c r="T73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U73" s="22">
+        <v>-1</v>
+      </c>
+      <c r="V73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W73" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y73" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z73" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA73" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB73" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC73" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A74" s="22">
+        <v>61100001</v>
+      </c>
+      <c r="B74" s="22">
+        <v>6110</v>
+      </c>
+      <c r="C74" s="22">
+        <v>1</v>
+      </c>
+      <c r="D74" s="22">
+        <v>0</v>
+      </c>
+      <c r="E74" s="22">
+        <v>3590800</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="G74" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="22">
+        <v>0</v>
+      </c>
+      <c r="L74" s="22">
+        <v>0</v>
+      </c>
+      <c r="M74" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="N74" s="22">
+        <v>2</v>
+      </c>
+      <c r="O74" s="22">
+        <v>10000</v>
+      </c>
+      <c r="P74" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q74" s="22">
+        <v>1</v>
+      </c>
+      <c r="R74" s="22">
+        <v>1</v>
+      </c>
+      <c r="S74" s="22">
+        <v>0</v>
+      </c>
+      <c r="T74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U74" s="22">
+        <v>0</v>
+      </c>
+      <c r="V74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W74" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y74" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z74" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB74" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC74" s="22">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:AC72" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AC74" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -8249,6 +8971,1030 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE859F77-6529-4974-B226-877FAEE341A8}">
+  <dimension ref="E7:S71"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="27.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="17.125" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="11" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="12" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="13" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="14" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="15" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="16" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="17" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="18" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="19" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="1" t="str">
+        <f>H19&amp;"-"&amp;I19</f>
+        <v>参数4LIST-触发的技能id</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="20" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="1" t="str">
+        <f t="shared" ref="G20:G71" si="0">H20&amp;"-"&amp;I20</f>
+        <v>参数5-持续时间（毫秒）</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="21" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数6-效果基础命中率（万分比）</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="22" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数7-效果最大叠加层数</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="23" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数8-效果触发间隔（毫秒）</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="24" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G24" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数9-击中回复生命值-固定值</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="25" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G25" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="26" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E26" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数11-击中回复效果提高万分比</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数12-击杀回复生命-固定值</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="28" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G28" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="29" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G30" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数15-击杀回复生命效果提高万分比</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="31" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E31" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G31" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数16-获得护盾-固定值</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="32" spans="5:19" x14ac:dyDescent="0.15">
+      <c r="E32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G32" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数17-获得护盾-自身生命百万分比</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="33" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="E33" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数18-获得护盾-自身已损失生命万分比</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="34" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="E34" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="G34" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数19-获得护盾效果提高万分比</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="35" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="E35" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="G35" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数20-技能增加-固定值</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="36" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G36" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数21-技能增加-万分比</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="37" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G37" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数22-技能增加-普通攻击范围万分比</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="38" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G38" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数25LIST-攻击提高-攻击的元素类型</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="39" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G39" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数25LIST-攻击提高-固定值</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G40" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数25LIST-攻击提高-万分比</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="41" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数28-防御提高-固定值</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="42" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G42" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数29-防御提高-万分比</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="43" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G43" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数30-生命上限提高-固定值</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="44" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数31-生命上限提高-百万分比</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="45" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G45" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数32-攻击速度提高-万分比</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="46" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G46" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数33-移动速度提高-万分比</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="47" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G47" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数34-攻击范围提高-万分比</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="48" spans="5:9" x14ac:dyDescent="0.15">
+      <c r="G48" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数35-攻击目标数量提高-固定值</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="49" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G49" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数36-</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="50" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G50" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数37-</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="51" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G51" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数38-</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="52" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G52" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数39-</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="53" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G53" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数40-</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="54" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G54" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数41-</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="55" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G55" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数42-</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="56" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G56" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数41-</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="57" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G57" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数42-</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="58" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G58" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数43-</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="59" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G59" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数44-</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="60" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G60" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数45-</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="61" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G61" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数46-</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="62" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G62" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数47-</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="63" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G63" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数48-</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="64" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G64" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数49-</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="65" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G65" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数50-</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="66" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G66" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数51-</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="67" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G67" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数52-</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="68" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G68" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数53-</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="69" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G69" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数54-</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="70" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G70" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数55-</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="71" spans="7:8" x14ac:dyDescent="0.15">
+      <c r="G71" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>参数56-</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="D6:F43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E89779E-6FAA-4DF9-B7FD-A79767996087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB399B1-EDCD-44B8-8222-4AA8F516E5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4349,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="Z21" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AA21" s="15" t="s">
         <v>43</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB399B1-EDCD-44B8-8222-4AA8F516E5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776A8CC2-4CF7-4493-B8DB-29542E5A2266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -460,1442 +460,1443 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
+    <t>3540401:1</t>
+  </si>
+  <si>
+    <t>3540402:1</t>
+  </si>
+  <si>
+    <t>3540601:1</t>
+  </si>
+  <si>
+    <t>3540602:1</t>
+  </si>
+  <si>
+    <t>3540801:1</t>
+  </si>
+  <si>
+    <t>3540802:1</t>
+  </si>
+  <si>
+    <t>3541001:1</t>
+  </si>
+  <si>
+    <t>3541002:1</t>
+  </si>
+  <si>
+    <t>3541201:1</t>
+  </si>
+  <si>
+    <t>3541401:1</t>
+  </si>
+  <si>
+    <t>3541601:1</t>
+  </si>
+  <si>
+    <t>3541602:1</t>
+  </si>
+  <si>
+    <t>3541801:1</t>
+  </si>
+  <si>
+    <t>3541802:1</t>
+  </si>
+  <si>
+    <t>3542001:1</t>
+  </si>
+  <si>
+    <t>3542002:1</t>
+  </si>
+  <si>
+    <t>3542201:1</t>
+  </si>
+  <si>
+    <t>3542202:1</t>
+  </si>
+  <si>
+    <t>3542401:1</t>
+  </si>
+  <si>
+    <t>3540205:1</t>
+  </si>
+  <si>
+    <t>3540207:1</t>
+  </si>
+  <si>
+    <t>3540405:1</t>
+  </si>
+  <si>
+    <t>3540407:1</t>
+  </si>
+  <si>
+    <t>3540605:1</t>
+  </si>
+  <si>
+    <t>3540607:1</t>
+  </si>
+  <si>
+    <t>3540805:1</t>
+  </si>
+  <si>
+    <t>3540807:1</t>
+  </si>
+  <si>
+    <t>3541005:1</t>
+  </si>
+  <si>
+    <t>3541007:1</t>
+  </si>
+  <si>
+    <t>3541205:1</t>
+  </si>
+  <si>
+    <t>3541207:1</t>
+  </si>
+  <si>
+    <t>3541405:1</t>
+  </si>
+  <si>
+    <t>3541407:1</t>
+  </si>
+  <si>
+    <t>3541605:1</t>
+  </si>
+  <si>
+    <t>3541607:1</t>
+  </si>
+  <si>
+    <t>3541805:1</t>
+  </si>
+  <si>
+    <t>3541807:1</t>
+  </si>
+  <si>
+    <t>3542005:1</t>
+  </si>
+  <si>
+    <t>3542007:1</t>
+  </si>
+  <si>
+    <t>3542205:1</t>
+  </si>
+  <si>
+    <t>3542207:1</t>
+  </si>
+  <si>
+    <t>3542405:1</t>
+  </si>
+  <si>
+    <t>3542407:1</t>
+  </si>
+  <si>
+    <t>3551302:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3551501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重冰霜新星</t>
+  </si>
+  <si>
+    <t>冰霜新星造成冰冻几率提高</t>
+  </si>
+  <si>
+    <t>冰冻时受到冰元素伤害</t>
+  </si>
+  <si>
+    <t>释放冰霜新星时，对敌人造成的冰冻几率增加【参数1万分比】</t>
+  </si>
+  <si>
+    <t>双重冰冻造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰冻命中造成额外伤害</t>
+  </si>
+  <si>
+    <t>击中冰冻目标造成额外伤害</t>
+  </si>
+  <si>
+    <t>冰霜新星额外冰冻几率</t>
+  </si>
+  <si>
+    <t>攻击次数触发冰霜新星</t>
+  </si>
+  <si>
+    <t>攻击使目标冰冻</t>
+  </si>
+  <si>
+    <t>3550902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>攻击提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>防御提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>生命提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>击中回血效果提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>暴击几率提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>暴击伤害提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>受到伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>受到持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>移动速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>获取护盾提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>全属性伤害提高</t>
+  </si>
+  <si>
+    <t>受到全属性伤害提高</t>
+  </si>
+  <si>
+    <t>全属性持续伤害提高</t>
+  </si>
+  <si>
+    <t>受到全属性持续伤害提高</t>
+  </si>
+  <si>
+    <t>移动速度提高</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+  </si>
+  <si>
+    <t>技能效果-通用</t>
+  </si>
+  <si>
+    <t>技能效果-冰</t>
+  </si>
+  <si>
+    <t>获取护盾提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒死亡释放瘟疫</t>
+  </si>
+  <si>
+    <t>瘟疫状态</t>
+  </si>
+  <si>
+    <t>技能效果-火</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-电</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-毒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动释放陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧状态受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石造成燃烧命中率增加</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时死亡触发死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链弹射效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发触电伤害时释放电磁爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒状态</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560201:1</t>
+  </si>
+  <si>
+    <t>3560202:1</t>
+  </si>
+  <si>
+    <t>3560205:1</t>
+  </si>
+  <si>
+    <t>3560206:1</t>
+  </si>
+  <si>
+    <t>3560501:2</t>
+  </si>
+  <si>
+    <t>3560502:1</t>
+  </si>
+  <si>
+    <t>3560503:1</t>
+  </si>
+  <si>
+    <t>3560701:1</t>
+  </si>
+  <si>
+    <t>3560901:1</t>
+  </si>
+  <si>
+    <t>3570201:1</t>
+  </si>
+  <si>
+    <t>3570202:1</t>
+  </si>
+  <si>
+    <t>3570501:1</t>
+  </si>
+  <si>
+    <t>3570502:1</t>
+  </si>
+  <si>
+    <t>3570701:2</t>
+  </si>
+  <si>
+    <t>3570702:1</t>
+  </si>
+  <si>
+    <t>3570703:1</t>
+  </si>
+  <si>
+    <t>3570901:1</t>
+  </si>
+  <si>
+    <t>3571101:1</t>
+  </si>
+  <si>
+    <t>3571102:1</t>
+  </si>
+  <si>
+    <t>3571103:1</t>
+  </si>
+  <si>
+    <t>3580201:1</t>
+  </si>
+  <si>
+    <t>3580202:1</t>
+  </si>
+  <si>
+    <t>3580207:1</t>
+  </si>
+  <si>
+    <t>3580501:2</t>
+  </si>
+  <si>
+    <t>3580502:1</t>
+  </si>
+  <si>
+    <t>3580503:1</t>
+  </si>
+  <si>
+    <t>3580701:1</t>
+  </si>
+  <si>
+    <t>3580902:1</t>
+  </si>
+  <si>
+    <t>3580903:1</t>
+  </si>
+  <si>
+    <t>3561102:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561103:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>每【参数1】次攻击，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>燃烧时，受到全种类攻击承受伤害提高【参数1万分比】</t>
+  </si>
+  <si>
+    <t>陨石造成伤害时，燃烧效果的命中率提升【参数1万分比】</t>
+  </si>
+  <si>
+    <t>燃烧时，死亡，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>每次受到攻击会额外受到等同于[电元素最终伤害]【参数1万分比】</t>
+  </si>
+  <si>
+    <t>闪电链可弹射【参数1】次，同1个目标最多可被选择【参数2】次，每次弹射造成的伤害降低第1次命中造成伤害的【参数3万分比】</t>
+  </si>
+  <si>
+    <t>触电时，触发触电伤害，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
+  </si>
+  <si>
+    <t>【瘟疫：附近任意目标施加瘟疫状态。】</t>
+  </si>
+  <si>
+    <t>3571302:1</t>
+  </si>
+  <si>
+    <t>3571303:1</t>
+  </si>
+  <si>
+    <t>技能效果-生存</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>损失血量触发获得护盾</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时触发技能受到全属性伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发额外回血</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外回复击回X倍的血量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值大于等于百万分比时触发技能触发全属性伤害提升</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值低于百万分比时触发技能触发受到全属性伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时触发技能复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-范围</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放技能多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击效果，额外造成X次X%的伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击触发释放旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩触发释放半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3600201:2</t>
+  </si>
+  <si>
+    <t>3600202:1</t>
+  </si>
+  <si>
+    <t>3600203:1</t>
+  </si>
+  <si>
+    <t>3600401:1</t>
+  </si>
+  <si>
+    <t>3600402:1</t>
+  </si>
+  <si>
+    <t>3600702:1</t>
+  </si>
+  <si>
+    <t>3600703:1</t>
+  </si>
+  <si>
+    <t>3601002:1</t>
+  </si>
+  <si>
+    <t>3601003:1</t>
+  </si>
+  <si>
+    <t>3601301:1</t>
+  </si>
+  <si>
+    <t>3601302:1</t>
+  </si>
+  <si>
+    <t>3601303:1</t>
+  </si>
+  <si>
+    <t>3610301:1</t>
+  </si>
+  <si>
+    <t>3610302:1</t>
+  </si>
+  <si>
+    <t>3610303:1</t>
+  </si>
+  <si>
+    <t>3610501:1</t>
+  </si>
+  <si>
+    <t>3610702:1</t>
+  </si>
+  <si>
+    <t>3610703:1</t>
+  </si>
+  <si>
+    <t>3590201:1</t>
+  </si>
+  <si>
+    <t>3590202:1</t>
+  </si>
+  <si>
+    <t>3590203:1</t>
+  </si>
+  <si>
+    <t>3590401:1</t>
+  </si>
+  <si>
+    <t>3590602:1</t>
+  </si>
+  <si>
+    <t>3590603:1</t>
+  </si>
+  <si>
+    <t>3590802:1</t>
+  </si>
+  <si>
+    <t>3590803:1</t>
+  </si>
+  <si>
+    <t>3591001:1</t>
+  </si>
+  <si>
+    <t>3591201:1</t>
+  </si>
+  <si>
+    <t>3591202:1</t>
+  </si>
+  <si>
+    <t>3591203:1</t>
+  </si>
+  <si>
+    <t>3591401:1</t>
+  </si>
+  <si>
+    <t>3591402:1</t>
+  </si>
+  <si>
+    <t>3591403:1</t>
+  </si>
+  <si>
+    <t>3591602:1</t>
+  </si>
+  <si>
+    <t>3591603:1</t>
+  </si>
+  <si>
+    <t>3591902:1</t>
+  </si>
+  <si>
+    <t>3600701:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数触发技能重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击技能暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能攻击累计额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀暴击触发斩杀血线变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590802:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3610901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611303:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611502:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611503:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590803:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名称</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数描述</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>低血时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-光环效果影响范围变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标血量低于百万分比触发斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀血线提高效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581202:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581207:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_value_8_variable_id</t>
+  </si>
+  <si>
+    <t>attr_value_8_type</t>
+  </si>
+  <si>
+    <t>attr_value_8</t>
+  </si>
+  <si>
+    <t>参数8关联的变量id</t>
+  </si>
+  <si>
+    <t>参数8数值类型</t>
+  </si>
+  <si>
+    <t>参数8</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>3041108:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591002:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591003:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+  </si>
+  <si>
+    <t>3570503:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
+  </si>
+  <si>
+    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
+  </si>
+  <si>
+    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
+  </si>
+  <si>
+    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时造成额外伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒受到额外中毒伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580702:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活回复血量、触发次数、触发间隔</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591908:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561401:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561402:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561408:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590405:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命暴击状态攻速提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回血效果提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3551103:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数8结算间隔时间</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑属性id</t>
+  </si>
+  <si>
+    <t>技能效果</t>
+  </si>
+  <si>
+    <t>技能名称</t>
+  </si>
+  <si>
+    <t>参数描述</t>
+  </si>
+  <si>
+    <t>效果叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算间隔时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复中buff组的cd时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
+    <t>参数6</t>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果最大叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果基础命中率（万分比）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果触发间隔（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数4LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发的技能id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数9</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数10</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数11</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数12</t>
+  </si>
+  <si>
+    <t>参数13</t>
+  </si>
+  <si>
+    <t>击中回复生命值-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中回复效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数14</t>
+  </si>
+  <si>
+    <t>参数15</t>
+  </si>
+  <si>
+    <t>参数16</t>
+  </si>
+  <si>
+    <t>击中回复生命值-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-目标最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数17</t>
+  </si>
+  <si>
+    <t>参数18</t>
+  </si>
+  <si>
+    <t>参数19</t>
+  </si>
+  <si>
+    <t>参数20</t>
+  </si>
+  <si>
+    <t>参数21</t>
+  </si>
+  <si>
+    <t>参数22</t>
+  </si>
+  <si>
+    <t>参数28</t>
+  </si>
+  <si>
+    <t>参数29</t>
+  </si>
+  <si>
+    <t>获得护盾-自身生命百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-自身已损失生命万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发自动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数30</t>
+  </si>
+  <si>
+    <t>参数31</t>
+  </si>
+  <si>
+    <t>参数32</t>
+  </si>
+  <si>
+    <t>参数33</t>
+  </si>
+  <si>
+    <t>参数34</t>
+  </si>
+  <si>
+    <t>参数35</t>
+  </si>
+  <si>
+    <t>参数36</t>
+  </si>
+  <si>
+    <t>参数37</t>
+  </si>
+  <si>
+    <t>参数38</t>
+  </si>
+  <si>
+    <t>参数39</t>
+  </si>
+  <si>
+    <t>参数40</t>
+  </si>
+  <si>
+    <t>参数41</t>
+  </si>
+  <si>
+    <t>参数42</t>
+  </si>
+  <si>
+    <t>参数43</t>
+  </si>
+  <si>
+    <t>参数44</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复生命</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中目标</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘟疫</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>电磁爆发</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-万分比</t>
+  </si>
+  <si>
+    <t>技能增加-普通攻击范围万分比</t>
+  </si>
+  <si>
+    <t>攻击提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-攻击的元素类型</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数25LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数45</t>
+  </si>
+  <si>
+    <t>参数46</t>
+  </si>
+  <si>
+    <t>参数47</t>
+  </si>
+  <si>
+    <t>参数48</t>
+  </si>
+  <si>
+    <t>参数49</t>
+  </si>
+  <si>
+    <t>参数50</t>
+  </si>
+  <si>
+    <t>参数51</t>
+  </si>
+  <si>
+    <t>参数52</t>
+  </si>
+  <si>
+    <t>参数53</t>
+  </si>
+  <si>
+    <t>参数54</t>
+  </si>
+  <si>
+    <t>参数55</t>
+  </si>
+  <si>
+    <t>参数56</t>
+  </si>
+  <si>
+    <t>生命上限提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命上限提高-百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击范围提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击目标数量提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+  </si>
+  <si>
+    <t>auto_cd</t>
+  </si>
+  <si>
+    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
+  </si>
+  <si>
+    <t>release_ratio</t>
+  </si>
+  <si>
+    <t>参数-释放几率</t>
+  </si>
+  <si>
+    <t>release_num</t>
+  </si>
+  <si>
+    <t>参数-释放次数</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>参数-释放的技能id</t>
+  </si>
+  <si>
+    <t>total_attack_num</t>
+  </si>
+  <si>
+    <t>参数-累计发起攻击次数时</t>
+  </si>
+  <si>
+    <t>lose_hp_ratio</t>
+  </si>
+  <si>
+    <t>参数-损失自身生命最大值百万分比时</t>
+  </si>
+  <si>
+    <t>kill_target_after</t>
+  </si>
+  <si>
+    <t>参数-击杀目标后</t>
+  </si>
+  <si>
+    <t>after_attack_crit</t>
+  </si>
+  <si>
+    <t>参数-攻击暴击后</t>
+  </si>
+  <si>
+    <t>after_use_skill</t>
+  </si>
+  <si>
+    <t>参数-释放【技能id】后</t>
+  </si>
+  <si>
+    <t>cycle_time</t>
+  </si>
+  <si>
+    <t>参数-每过固定时间（毫秒）时</t>
+  </si>
+  <si>
+    <t>after_skill_hit</t>
+  </si>
+  <si>
+    <t>参数-【技能id】命中后</t>
+  </si>
+  <si>
+    <t>after_self_death</t>
+  </si>
+  <si>
+    <t>参数-自身死亡后释放</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+  </si>
+  <si>
+    <t>self_have_effect</t>
+  </si>
+  <si>
+    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_have_effect</t>
+  </si>
+  <si>
+    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_over</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_under</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>to_target_effect_hit</t>
+  </si>
+  <si>
+    <t>参数-对目标施加【效果id】命中时</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542801:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542601:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543001:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542607:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542807:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543007:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542605:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542805:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543005:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
     <t>3540201:1</t>
-  </si>
-  <si>
-    <t>3540401:1</t>
-  </si>
-  <si>
-    <t>3540402:1</t>
-  </si>
-  <si>
-    <t>3540601:1</t>
-  </si>
-  <si>
-    <t>3540602:1</t>
-  </si>
-  <si>
-    <t>3540801:1</t>
-  </si>
-  <si>
-    <t>3540802:1</t>
-  </si>
-  <si>
-    <t>3541001:1</t>
-  </si>
-  <si>
-    <t>3541002:1</t>
-  </si>
-  <si>
-    <t>3541201:1</t>
-  </si>
-  <si>
-    <t>3541401:1</t>
-  </si>
-  <si>
-    <t>3541601:1</t>
-  </si>
-  <si>
-    <t>3541602:1</t>
-  </si>
-  <si>
-    <t>3541801:1</t>
-  </si>
-  <si>
-    <t>3541802:1</t>
-  </si>
-  <si>
-    <t>3542001:1</t>
-  </si>
-  <si>
-    <t>3542002:1</t>
-  </si>
-  <si>
-    <t>3542201:1</t>
-  </si>
-  <si>
-    <t>3542202:1</t>
-  </si>
-  <si>
-    <t>3542401:1</t>
-  </si>
-  <si>
-    <t>3540205:1</t>
-  </si>
-  <si>
-    <t>3540207:1</t>
-  </si>
-  <si>
-    <t>3540405:1</t>
-  </si>
-  <si>
-    <t>3540407:1</t>
-  </si>
-  <si>
-    <t>3540605:1</t>
-  </si>
-  <si>
-    <t>3540607:1</t>
-  </si>
-  <si>
-    <t>3540805:1</t>
-  </si>
-  <si>
-    <t>3540807:1</t>
-  </si>
-  <si>
-    <t>3541005:1</t>
-  </si>
-  <si>
-    <t>3541007:1</t>
-  </si>
-  <si>
-    <t>3541205:1</t>
-  </si>
-  <si>
-    <t>3541207:1</t>
-  </si>
-  <si>
-    <t>3541405:1</t>
-  </si>
-  <si>
-    <t>3541407:1</t>
-  </si>
-  <si>
-    <t>3541605:1</t>
-  </si>
-  <si>
-    <t>3541607:1</t>
-  </si>
-  <si>
-    <t>3541805:1</t>
-  </si>
-  <si>
-    <t>3541807:1</t>
-  </si>
-  <si>
-    <t>3542005:1</t>
-  </si>
-  <si>
-    <t>3542007:1</t>
-  </si>
-  <si>
-    <t>3542205:1</t>
-  </si>
-  <si>
-    <t>3542207:1</t>
-  </si>
-  <si>
-    <t>3542405:1</t>
-  </si>
-  <si>
-    <t>3542407:1</t>
-  </si>
-  <si>
-    <t>3551302:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3551501:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重冰霜新星</t>
-  </si>
-  <si>
-    <t>冰霜新星造成冰冻几率提高</t>
-  </si>
-  <si>
-    <t>冰冻时受到冰元素伤害</t>
-  </si>
-  <si>
-    <t>释放冰霜新星时，对敌人造成的冰冻几率增加【参数1万分比】</t>
-  </si>
-  <si>
-    <t>双重冰冻造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰冻命中造成额外伤害</t>
-  </si>
-  <si>
-    <t>击中冰冻目标造成额外伤害</t>
-  </si>
-  <si>
-    <t>冰霜新星额外冰冻几率</t>
-  </si>
-  <si>
-    <t>攻击次数触发冰霜新星</t>
-  </si>
-  <si>
-    <t>攻击使目标冰冻</t>
-  </si>
-  <si>
-    <t>3550902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>攻击提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>防御提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>生命提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>击中回血效果提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>暴击几率提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>暴击伤害提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>受到伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>受到持续伤害提高【参数1万分比】+【参数2固定值】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>移动速度提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>获取护盾提高【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>全属性伤害提高</t>
-  </si>
-  <si>
-    <t>受到全属性伤害提高</t>
-  </si>
-  <si>
-    <t>全属性持续伤害提高</t>
-  </si>
-  <si>
-    <t>受到全属性持续伤害提高</t>
-  </si>
-  <si>
-    <t>移动速度提高</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-  </si>
-  <si>
-    <t>技能效果-通用</t>
-  </si>
-  <si>
-    <t>技能效果-冰</t>
-  </si>
-  <si>
-    <t>获取护盾提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒死亡释放瘟疫</t>
-  </si>
-  <si>
-    <t>瘟疫状态</t>
-  </si>
-  <si>
-    <t>技能效果-火</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-电</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-毒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动释放陨石</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧状态受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石造成燃烧命中率增加</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时死亡触发死亡爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链弹射效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放闪电链</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发触电伤害时释放电磁爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>中毒状态</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发传染</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560201:1</t>
-  </si>
-  <si>
-    <t>3560202:1</t>
-  </si>
-  <si>
-    <t>3560205:1</t>
-  </si>
-  <si>
-    <t>3560206:1</t>
-  </si>
-  <si>
-    <t>3560501:2</t>
-  </si>
-  <si>
-    <t>3560502:1</t>
-  </si>
-  <si>
-    <t>3560503:1</t>
-  </si>
-  <si>
-    <t>3560701:1</t>
-  </si>
-  <si>
-    <t>3560901:1</t>
-  </si>
-  <si>
-    <t>3570201:1</t>
-  </si>
-  <si>
-    <t>3570202:1</t>
-  </si>
-  <si>
-    <t>3570501:1</t>
-  </si>
-  <si>
-    <t>3570502:1</t>
-  </si>
-  <si>
-    <t>3570701:2</t>
-  </si>
-  <si>
-    <t>3570702:1</t>
-  </si>
-  <si>
-    <t>3570703:1</t>
-  </si>
-  <si>
-    <t>3570901:1</t>
-  </si>
-  <si>
-    <t>3571101:1</t>
-  </si>
-  <si>
-    <t>3571102:1</t>
-  </si>
-  <si>
-    <t>3571103:1</t>
-  </si>
-  <si>
-    <t>3580201:1</t>
-  </si>
-  <si>
-    <t>3580202:1</t>
-  </si>
-  <si>
-    <t>3580207:1</t>
-  </si>
-  <si>
-    <t>3580501:2</t>
-  </si>
-  <si>
-    <t>3580502:1</t>
-  </si>
-  <si>
-    <t>3580503:1</t>
-  </si>
-  <si>
-    <t>3580701:1</t>
-  </si>
-  <si>
-    <t>3580902:1</t>
-  </si>
-  <si>
-    <t>3580903:1</t>
-  </si>
-  <si>
-    <t>3561102:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561103:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>每【参数1】次攻击，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>燃烧时，受到全种类攻击承受伤害提高【参数1万分比】</t>
-  </si>
-  <si>
-    <t>陨石造成伤害时，燃烧效果的命中率提升【参数1万分比】</t>
-  </si>
-  <si>
-    <t>燃烧时，死亡，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>每次受到攻击会额外受到等同于[电元素最终伤害]【参数1万分比】</t>
-  </si>
-  <si>
-    <t>闪电链可弹射【参数1】次，同1个目标最多可被选择【参数2】次，每次弹射造成的伤害降低第1次命中造成伤害的【参数3万分比】</t>
-  </si>
-  <si>
-    <t>触电时，触发触电伤害，有【参数2万分比】的几率触发【参数3】次【参数4技能id】</t>
-  </si>
-  <si>
-    <t>【瘟疫：附近任意目标施加瘟疫状态。】</t>
-  </si>
-  <si>
-    <t>3571302:1</t>
-  </si>
-  <si>
-    <t>3571303:1</t>
-  </si>
-  <si>
-    <t>技能效果-生存</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>损失血量触发获得护盾</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时触发技能受到全属性伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发额外回血</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外回复击回X倍的血量</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值大于等于百万分比时触发技能触发全属性伤害提升</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命值低于百万分比时触发技能触发受到全属性伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡时触发技能复活</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-范围</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果-伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放技能多重打击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重打击效果，额外造成X次X%的伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击触发释放旋风斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋风斩触发释放半月斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3600201:2</t>
-  </si>
-  <si>
-    <t>3600202:1</t>
-  </si>
-  <si>
-    <t>3600203:1</t>
-  </si>
-  <si>
-    <t>3600401:1</t>
-  </si>
-  <si>
-    <t>3600402:1</t>
-  </si>
-  <si>
-    <t>3600702:1</t>
-  </si>
-  <si>
-    <t>3600703:1</t>
-  </si>
-  <si>
-    <t>3601002:1</t>
-  </si>
-  <si>
-    <t>3601003:1</t>
-  </si>
-  <si>
-    <t>3601301:1</t>
-  </si>
-  <si>
-    <t>3601302:1</t>
-  </si>
-  <si>
-    <t>3601303:1</t>
-  </si>
-  <si>
-    <t>3610301:1</t>
-  </si>
-  <si>
-    <t>3610302:1</t>
-  </si>
-  <si>
-    <t>3610303:1</t>
-  </si>
-  <si>
-    <t>3610501:1</t>
-  </si>
-  <si>
-    <t>3610702:1</t>
-  </si>
-  <si>
-    <t>3610703:1</t>
-  </si>
-  <si>
-    <t>3590201:1</t>
-  </si>
-  <si>
-    <t>3590202:1</t>
-  </si>
-  <si>
-    <t>3590203:1</t>
-  </si>
-  <si>
-    <t>3590401:1</t>
-  </si>
-  <si>
-    <t>3590602:1</t>
-  </si>
-  <si>
-    <t>3590603:1</t>
-  </si>
-  <si>
-    <t>3590802:1</t>
-  </si>
-  <si>
-    <t>3590803:1</t>
-  </si>
-  <si>
-    <t>3591001:1</t>
-  </si>
-  <si>
-    <t>3591201:1</t>
-  </si>
-  <si>
-    <t>3591202:1</t>
-  </si>
-  <si>
-    <t>3591203:1</t>
-  </si>
-  <si>
-    <t>3591401:1</t>
-  </si>
-  <si>
-    <t>3591402:1</t>
-  </si>
-  <si>
-    <t>3591403:1</t>
-  </si>
-  <si>
-    <t>3591602:1</t>
-  </si>
-  <si>
-    <t>3591603:1</t>
-  </si>
-  <si>
-    <t>3591902:1</t>
-  </si>
-  <si>
-    <t>3600701:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数触发技能重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击技能暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能攻击累计额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀暴击触发斩杀血线变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590802:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3610901:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611301:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611303:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611701:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611502:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611503:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590803:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名称</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数描述</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>低血时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-光环效果影响范围变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标血量低于百万分比触发斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀血线提高效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581201:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581202:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581207:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>attr_value_8_variable_id</t>
-  </si>
-  <si>
-    <t>attr_value_8_type</t>
-  </si>
-  <si>
-    <t>attr_value_8</t>
-  </si>
-  <si>
-    <t>参数8关联的变量id</t>
-  </si>
-  <si>
-    <t>参数8数值类型</t>
-  </si>
-  <si>
-    <t>参数8</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>3041108:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591002:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591003:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-  </si>
-  <si>
-    <t>3570503:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
-  </si>
-  <si>
-    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
-  </si>
-  <si>
-    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
-  </si>
-  <si>
-    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时造成额外伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒受到额外中毒伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580702:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活回复血量、触发次数、触发间隔</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591908:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561401:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561402:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561408:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590405:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命暴击状态攻速提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3592101:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回血效果提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3551103:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数8结算间隔时间</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>逻辑属性id</t>
-  </si>
-  <si>
-    <t>技能效果</t>
-  </si>
-  <si>
-    <t>技能名称</t>
-  </si>
-  <si>
-    <t>参数描述</t>
-  </si>
-  <si>
-    <t>效果叠加层数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>结算间隔时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复中buff组的cd时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数5</t>
-  </si>
-  <si>
-    <t>参数6</t>
-  </si>
-  <si>
-    <t>持续时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果最大叠加层数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果基础命中率（万分比）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果触发间隔（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数4LIST</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发的技能id</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数9</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数10</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数11</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数12</t>
-  </si>
-  <si>
-    <t>参数13</t>
-  </si>
-  <si>
-    <t>击中回复生命值-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击中回复效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数14</t>
-  </si>
-  <si>
-    <t>参数15</t>
-  </si>
-  <si>
-    <t>参数16</t>
-  </si>
-  <si>
-    <t>击中回复生命值-自身最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-自身最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-目标最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数17</t>
-  </si>
-  <si>
-    <t>参数18</t>
-  </si>
-  <si>
-    <t>参数19</t>
-  </si>
-  <si>
-    <t>参数20</t>
-  </si>
-  <si>
-    <t>参数21</t>
-  </si>
-  <si>
-    <t>参数22</t>
-  </si>
-  <si>
-    <t>参数28</t>
-  </si>
-  <si>
-    <t>参数29</t>
-  </si>
-  <si>
-    <t>获得护盾-自身生命百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾-自身已损失生命万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发自动技能</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数30</t>
-  </si>
-  <si>
-    <t>参数31</t>
-  </si>
-  <si>
-    <t>参数32</t>
-  </si>
-  <si>
-    <t>参数33</t>
-  </si>
-  <si>
-    <t>参数34</t>
-  </si>
-  <si>
-    <t>参数35</t>
-  </si>
-  <si>
-    <t>参数36</t>
-  </si>
-  <si>
-    <t>参数37</t>
-  </si>
-  <si>
-    <t>参数38</t>
-  </si>
-  <si>
-    <t>参数39</t>
-  </si>
-  <si>
-    <t>参数40</t>
-  </si>
-  <si>
-    <t>参数41</t>
-  </si>
-  <si>
-    <t>参数42</t>
-  </si>
-  <si>
-    <t>参数43</t>
-  </si>
-  <si>
-    <t>参数44</t>
-  </si>
-  <si>
-    <t>主动技能</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复生命</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击中目标</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰霜新星</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>传染</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>瘟疫</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重打击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋风斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>半月斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>电磁爆发</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能增加-万分比</t>
-  </si>
-  <si>
-    <t>技能增加-普通攻击范围万分比</t>
-  </si>
-  <si>
-    <t>攻击提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击提高-攻击的元素类型</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数25LIST</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数45</t>
-  </si>
-  <si>
-    <t>参数46</t>
-  </si>
-  <si>
-    <t>参数47</t>
-  </si>
-  <si>
-    <t>参数48</t>
-  </si>
-  <si>
-    <t>参数49</t>
-  </si>
-  <si>
-    <t>参数50</t>
-  </si>
-  <si>
-    <t>参数51</t>
-  </si>
-  <si>
-    <t>参数52</t>
-  </si>
-  <si>
-    <t>参数53</t>
-  </si>
-  <si>
-    <t>参数54</t>
-  </si>
-  <si>
-    <t>参数55</t>
-  </si>
-  <si>
-    <t>参数56</t>
-  </si>
-  <si>
-    <t>生命上限提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命上限提高-百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击范围提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击目标数量提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能增加-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-  </si>
-  <si>
-    <t>auto_cd</t>
-  </si>
-  <si>
-    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
-  </si>
-  <si>
-    <t>release_ratio</t>
-  </si>
-  <si>
-    <t>参数-释放几率</t>
-  </si>
-  <si>
-    <t>release_num</t>
-  </si>
-  <si>
-    <t>参数-释放次数</t>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S</t>
-  </si>
-  <si>
-    <t>skill_id</t>
-  </si>
-  <si>
-    <t>参数-释放的技能id</t>
-  </si>
-  <si>
-    <t>total_attack_num</t>
-  </si>
-  <si>
-    <t>参数-累计发起攻击次数时</t>
-  </si>
-  <si>
-    <t>lose_hp_ratio</t>
-  </si>
-  <si>
-    <t>参数-损失自身生命最大值百万分比时</t>
-  </si>
-  <si>
-    <t>kill_target_after</t>
-  </si>
-  <si>
-    <t>参数-击杀目标后</t>
-  </si>
-  <si>
-    <t>after_attack_crit</t>
-  </si>
-  <si>
-    <t>参数-攻击暴击后</t>
-  </si>
-  <si>
-    <t>after_use_skill</t>
-  </si>
-  <si>
-    <t>参数-释放【技能id】后</t>
-  </si>
-  <si>
-    <t>cycle_time</t>
-  </si>
-  <si>
-    <t>参数-每过固定时间（毫秒）时</t>
-  </si>
-  <si>
-    <t>after_skill_hit</t>
-  </si>
-  <si>
-    <t>参数-【技能id】命中后</t>
-  </si>
-  <si>
-    <t>after_self_death</t>
-  </si>
-  <si>
-    <t>参数-自身死亡后释放</t>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-  </si>
-  <si>
-    <t>self_have_effect</t>
-  </si>
-  <si>
-    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>target_have_effect</t>
-  </si>
-  <si>
-    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_over</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_under</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>to_target_effect_hit</t>
-  </si>
-  <si>
-    <t>参数-对目标施加【效果id】命中时</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>自动</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542801:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542601:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543001:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542607:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542807:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543007:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542605:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542805:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543005:1</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -2661,13 +2662,13 @@
         <v>65</v>
       </c>
       <c r="AA2" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="AB2" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>327</v>
-      </c>
       <c r="AC2" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
@@ -2750,13 +2751,13 @@
         <v>103</v>
       </c>
       <c r="AA3" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="AB3" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>329</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
@@ -2776,16 +2777,16 @@
         <v>64</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>30</v>
@@ -2839,13 +2840,13 @@
         <v>106</v>
       </c>
       <c r="AA4" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="AB4" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="AB4" s="7" t="s">
-        <v>332</v>
-      </c>
       <c r="AC4" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
@@ -2883,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="5">
-        <v>600000</v>
+        <v>300000</v>
       </c>
       <c r="M5" s="11" t="s">
         <v>43</v>
@@ -2963,7 +2964,7 @@
         <v>47</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>89</v>
@@ -3017,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AB6" s="6">
         <v>1</v>
@@ -3046,22 +3047,22 @@
         <v>90</v>
       </c>
       <c r="G7" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H7" s="16" t="s">
         <v>90</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>108</v>
+        <v>532</v>
       </c>
       <c r="K7" s="15">
         <v>2</v>
       </c>
       <c r="L7" s="15">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>43</v>
@@ -3085,10 +3086,10 @@
         <v>0</v>
       </c>
       <c r="T7" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U7" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V7" s="15" t="s">
         <v>43</v>
@@ -3097,7 +3098,7 @@
         <v>10000</v>
       </c>
       <c r="X7" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y7" s="15">
         <v>1</v>
@@ -3135,25 +3136,25 @@
         <v>91</v>
       </c>
       <c r="G8" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H8" s="16" t="s">
         <v>91</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K8" s="15">
         <v>2</v>
       </c>
       <c r="L8" s="15">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N8" s="15">
         <v>1</v>
@@ -3174,10 +3175,10 @@
         <v>0</v>
       </c>
       <c r="T8" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="U8" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V8" s="15" t="s">
         <v>43</v>
@@ -3186,7 +3187,7 @@
         <v>10000</v>
       </c>
       <c r="X8" s="15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Y8" s="15">
         <v>1</v>
@@ -3224,25 +3225,25 @@
         <v>92</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>92</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K9" s="15">
         <v>2</v>
       </c>
       <c r="L9" s="15">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="M9" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N9" s="15">
         <v>1</v>
@@ -3263,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="T9" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U9" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V9" s="15" t="s">
         <v>43</v>
@@ -3275,7 +3276,7 @@
         <v>10000</v>
       </c>
       <c r="X9" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Y9" s="15">
         <v>1</v>
@@ -3313,25 +3314,25 @@
         <v>93</v>
       </c>
       <c r="G10" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>93</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K10" s="15">
         <v>3</v>
       </c>
       <c r="L10" s="15">
-        <v>50000</v>
+        <v>150000</v>
       </c>
       <c r="M10" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N10" s="15">
         <v>1</v>
@@ -3352,10 +3353,10 @@
         <v>0</v>
       </c>
       <c r="T10" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="U10" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V10" s="15" t="s">
         <v>43</v>
@@ -3364,7 +3365,7 @@
         <v>10000</v>
       </c>
       <c r="X10" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y10" s="15">
         <v>1</v>
@@ -3402,16 +3403,16 @@
         <v>94</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>94</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K11" s="15">
         <v>2</v>
@@ -3420,7 +3421,7 @@
         <v>500</v>
       </c>
       <c r="M11" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N11" s="15">
         <v>1</v>
@@ -3441,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="T11" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="U11" s="15">
         <v>4000</v>
@@ -3453,7 +3454,7 @@
         <v>10000</v>
       </c>
       <c r="X11" s="15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Y11" s="15">
         <v>1</v>
@@ -3491,22 +3492,22 @@
         <v>95</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>95</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K12" s="15">
         <v>2</v>
       </c>
       <c r="L12" s="15">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="M12" s="15" t="s">
         <v>43</v>
@@ -3530,10 +3531,10 @@
         <v>0</v>
       </c>
       <c r="T12" s="15" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="U12" s="15">
-        <v>4000</v>
+        <v>60000</v>
       </c>
       <c r="V12" s="15" t="s">
         <v>43</v>
@@ -3542,7 +3543,7 @@
         <v>10000</v>
       </c>
       <c r="X12" s="15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Y12" s="15">
         <v>1</v>
@@ -3580,16 +3581,16 @@
         <v>96</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H13" s="16" t="s">
         <v>96</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J13" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K13" s="15">
         <v>2</v>
@@ -3619,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="15" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U13" s="15">
         <v>4000</v>
@@ -3631,7 +3632,7 @@
         <v>10000</v>
       </c>
       <c r="X13" s="15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Y13" s="15">
         <v>1</v>
@@ -3669,16 +3670,16 @@
         <v>97</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K14" s="15">
         <v>2</v>
@@ -3687,7 +3688,7 @@
         <v>500</v>
       </c>
       <c r="M14" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N14" s="15">
         <v>1</v>
@@ -3708,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U14" s="15">
         <v>4000</v>
@@ -3720,7 +3721,7 @@
         <v>10000</v>
       </c>
       <c r="X14" s="15" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Y14" s="15">
         <v>1</v>
@@ -3758,16 +3759,16 @@
         <v>98</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K15" s="15">
         <v>2</v>
@@ -3776,7 +3777,7 @@
         <v>500</v>
       </c>
       <c r="M15" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N15" s="15">
         <v>1</v>
@@ -3797,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="T15" s="15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="U15" s="15">
         <v>4000</v>
@@ -3809,7 +3810,7 @@
         <v>10000</v>
       </c>
       <c r="X15" s="15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y15" s="15">
         <v>1</v>
@@ -3847,16 +3848,16 @@
         <v>99</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K16" s="15">
         <v>2</v>
@@ -3865,7 +3866,7 @@
         <v>500</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N16" s="15">
         <v>1</v>
@@ -3886,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="T16" s="15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U16" s="15">
         <v>4000</v>
@@ -3898,7 +3899,7 @@
         <v>10000</v>
       </c>
       <c r="X16" s="15" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y16" s="15">
         <v>1</v>
@@ -3936,16 +3937,16 @@
         <v>100</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K17" s="15">
         <v>2</v>
@@ -3954,7 +3955,7 @@
         <v>500</v>
       </c>
       <c r="M17" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N17" s="15">
         <v>1</v>
@@ -3975,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="15" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="U17" s="15">
         <v>4000</v>
@@ -3987,7 +3988,7 @@
         <v>10000</v>
       </c>
       <c r="X17" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Y17" s="15">
         <v>1</v>
@@ -4025,16 +4026,16 @@
         <v>107</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K18" s="15">
         <v>2</v>
@@ -4064,7 +4065,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="15" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U18" s="15">
         <v>4000</v>
@@ -4076,7 +4077,7 @@
         <v>10000</v>
       </c>
       <c r="X18" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Y18" s="15">
         <v>1</v>
@@ -4111,19 +4112,19 @@
         <v>3542600</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -4153,7 +4154,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -4165,7 +4166,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -4200,19 +4201,19 @@
         <v>3542800</v>
       </c>
       <c r="F20" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="I20" s="16" t="s">
         <v>521</v>
       </c>
-      <c r="G20" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>522</v>
-      </c>
       <c r="J20" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K20" s="15">
         <v>2</v>
@@ -4242,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="U20" s="15">
         <v>-1</v>
@@ -4254,7 +4255,7 @@
         <v>10000</v>
       </c>
       <c r="X20" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y20" s="15">
         <v>1</v>
@@ -4289,25 +4290,25 @@
         <v>3543000</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="K21" s="15">
         <v>2</v>
       </c>
       <c r="L21" s="15">
-        <v>10000</v>
+        <v>3500</v>
       </c>
       <c r="M21" s="15" t="s">
         <v>43</v>
@@ -4331,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="U21" s="15">
         <v>-1</v>
@@ -4343,7 +4344,7 @@
         <v>10000</v>
       </c>
       <c r="X21" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="Y21" s="15">
         <v>1</v>
@@ -4381,13 +4382,13 @@
         <v>69</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -4470,13 +4471,13 @@
         <v>71</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>80</v>
@@ -4559,13 +4560,13 @@
         <v>72</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>43</v>
@@ -4648,13 +4649,13 @@
         <v>74</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>85</v>
@@ -4666,7 +4667,7 @@
         <v>3000</v>
       </c>
       <c r="M25" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N25" s="17">
         <v>0</v>
@@ -4734,16 +4735,16 @@
         <v>3551100</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>86</v>
@@ -4764,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Q26" s="17">
         <v>1</v>
@@ -4823,16 +4824,16 @@
         <v>3551300</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>88</v>
@@ -4844,7 +4845,7 @@
         <v>5000</v>
       </c>
       <c r="M27" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N27" s="17">
         <v>1</v>
@@ -4912,19 +4913,19 @@
         <v>3551500</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K28" s="17">
         <v>2</v>
@@ -5001,19 +5002,19 @@
         <v>3560200</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J29" s="18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K29" s="18">
         <v>2</v>
@@ -5022,7 +5023,7 @@
         <v>5000</v>
       </c>
       <c r="M29" s="18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="N29" s="18">
         <v>1</v>
@@ -5043,13 +5044,13 @@
         <v>0</v>
       </c>
       <c r="T29" s="18" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U29" s="18">
         <v>4000</v>
       </c>
       <c r="V29" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="W29" s="18">
         <v>1500</v>
@@ -5064,7 +5065,7 @@
         <v>1</v>
       </c>
       <c r="AA29" s="18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AB29" s="18">
         <v>1</v>
@@ -5090,19 +5091,19 @@
         <v>3560500</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J30" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K30" s="18">
         <v>1</v>
@@ -5111,7 +5112,7 @@
         <v>8</v>
       </c>
       <c r="M30" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N30" s="18">
         <v>1</v>
@@ -5120,7 +5121,7 @@
         <v>10000</v>
       </c>
       <c r="P30" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q30" s="18">
         <v>1</v>
@@ -5179,19 +5180,19 @@
         <v>3560700</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J31" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K31" s="18">
         <v>2</v>
@@ -5268,19 +5269,19 @@
         <v>3560900</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="J32" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K32" s="18">
         <v>2</v>
@@ -5357,16 +5358,16 @@
         <v>3561100</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J33" s="18" t="s">
         <v>43</v>
@@ -5378,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="N33" s="18">
         <v>2</v>
@@ -5387,7 +5388,7 @@
         <v>10000</v>
       </c>
       <c r="P33" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q33" s="18">
         <v>1</v>
@@ -5446,19 +5447,19 @@
         <v>3561400</v>
       </c>
       <c r="F34" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="H34" s="13" t="s">
         <v>344</v>
       </c>
-      <c r="G34" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>345</v>
-      </c>
       <c r="I34" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K34" s="18">
         <v>2</v>
@@ -5467,7 +5468,7 @@
         <v>3500</v>
       </c>
       <c r="M34" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="N34" s="18">
         <v>35</v>
@@ -5509,7 +5510,7 @@
         <v>1</v>
       </c>
       <c r="AA34" s="18" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AB34" s="18">
         <v>1</v>
@@ -5535,19 +5536,19 @@
         <v>3570200</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K35" s="19">
         <v>2</v>
@@ -5556,7 +5557,7 @@
         <v>4000</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N35" s="19">
         <v>1</v>
@@ -5577,7 +5578,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U35" s="19">
         <v>4000</v>
@@ -5624,19 +5625,19 @@
         <v>3570500</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K36" s="19">
         <v>1</v>
@@ -5645,7 +5646,7 @@
         <v>3</v>
       </c>
       <c r="M36" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N36" s="19">
         <v>1</v>
@@ -5654,7 +5655,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q36" s="19">
         <v>2</v>
@@ -5713,19 +5714,19 @@
         <v>3570700</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J37" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K37" s="19">
         <v>1</v>
@@ -5734,7 +5735,7 @@
         <v>8</v>
       </c>
       <c r="M37" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="N37" s="19">
         <v>2</v>
@@ -5743,7 +5744,7 @@
         <v>10000</v>
       </c>
       <c r="P37" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Q37" s="19">
         <v>1</v>
@@ -5802,19 +5803,19 @@
         <v>3570900</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K38" s="19">
         <v>2</v>
@@ -5823,7 +5824,7 @@
         <v>2000</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="N38" s="19">
         <v>1</v>
@@ -5891,19 +5892,19 @@
         <v>3571100</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J39" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K39" s="19">
         <v>2</v>
@@ -5912,16 +5913,16 @@
         <v>10000</v>
       </c>
       <c r="M39" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="N39" s="19">
+        <v>1</v>
+      </c>
+      <c r="O39" s="19">
+        <v>1</v>
+      </c>
+      <c r="P39" s="19" t="s">
         <v>222</v>
-      </c>
-      <c r="N39" s="19">
-        <v>1</v>
-      </c>
-      <c r="O39" s="19">
-        <v>1</v>
-      </c>
-      <c r="P39" s="19" t="s">
-        <v>223</v>
       </c>
       <c r="Q39" s="19">
         <v>1</v>
@@ -5980,16 +5981,16 @@
         <v>3571300</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J40" s="19" t="s">
         <v>43</v>
@@ -6001,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="N40" s="19">
         <v>2</v>
@@ -6010,7 +6011,7 @@
         <v>10000</v>
       </c>
       <c r="P40" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="Q40" s="19">
         <v>1</v>
@@ -6069,19 +6070,19 @@
         <v>3580200</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J41" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K41" s="20">
         <v>2</v>
@@ -6090,7 +6091,7 @@
         <v>3000</v>
       </c>
       <c r="M41" s="20" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N41" s="20">
         <v>1</v>
@@ -6111,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U41" s="20">
         <v>4000</v>
@@ -6123,7 +6124,7 @@
         <v>10000</v>
       </c>
       <c r="X41" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="Y41" s="20">
         <v>1</v>
@@ -6132,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="AA41" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AB41" s="20">
         <v>1</v>
@@ -6158,19 +6159,19 @@
         <v>3580500</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J42" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K42" s="20">
         <v>1</v>
@@ -6179,7 +6180,7 @@
         <v>8</v>
       </c>
       <c r="M42" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N42" s="20">
         <v>2</v>
@@ -6188,7 +6189,7 @@
         <v>10000</v>
       </c>
       <c r="P42" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Q42" s="20">
         <v>1</v>
@@ -6247,19 +6248,19 @@
         <v>3580700</v>
       </c>
       <c r="F43" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="G43" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>359</v>
-      </c>
       <c r="J43" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K43" s="20">
         <v>1</v>
@@ -6268,7 +6269,7 @@
         <v>5</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="N43" s="20">
         <v>2</v>
@@ -6336,16 +6337,16 @@
         <v>3580900</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J44" s="20" t="s">
         <v>43</v>
@@ -6357,7 +6358,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="N44" s="20">
         <v>2</v>
@@ -6366,7 +6367,7 @@
         <v>10000</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q44" s="20">
         <v>1</v>
@@ -6425,19 +6426,19 @@
         <v>3581200</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K45" s="20">
         <v>2</v>
@@ -6446,7 +6447,7 @@
         <v>3000</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N45" s="20">
         <v>0</v>
@@ -6467,7 +6468,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U45" s="20">
         <v>4000</v>
@@ -6479,7 +6480,7 @@
         <v>10000</v>
       </c>
       <c r="X45" s="20" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Y45" s="20">
         <v>1</v>
@@ -6488,7 +6489,7 @@
         <v>10</v>
       </c>
       <c r="AA45" s="20" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AB45" s="20">
         <v>1</v>
@@ -6514,15 +6515,15 @@
         <v>3590200</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H46" s="13"/>
       <c r="I46" s="13"/>
       <c r="J46" s="24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K46" s="24">
         <v>3</v>
@@ -6531,7 +6532,7 @@
         <v>200000</v>
       </c>
       <c r="M46" s="24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="N46" s="24">
         <v>2</v>
@@ -6540,7 +6541,7 @@
         <v>10000</v>
       </c>
       <c r="P46" s="24" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q46" s="24">
         <v>1</v>
@@ -6599,15 +6600,15 @@
         <v>3590400</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="13"/>
       <c r="J47" s="24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K47" s="24">
         <v>3</v>
@@ -6637,7 +6638,7 @@
         <v>59030001</v>
       </c>
       <c r="T47" s="24" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="U47" s="24">
         <v>-1</v>
@@ -6684,10 +6685,10 @@
         <v>3590600</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H48" s="13"/>
       <c r="I48" s="13"/>
@@ -6701,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N48" s="24">
         <v>2</v>
@@ -6710,7 +6711,7 @@
         <v>10000</v>
       </c>
       <c r="P48" s="24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q48" s="24">
         <v>1</v>
@@ -6769,10 +6770,10 @@
         <v>3590800</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H49" s="13"/>
       <c r="I49" s="13"/>
@@ -6786,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6795,7 +6796,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6854,15 +6855,15 @@
         <v>3591000</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K50" s="24">
         <v>2</v>
@@ -6871,16 +6872,16 @@
         <v>0</v>
       </c>
       <c r="M50" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="N50" s="24">
+        <v>1</v>
+      </c>
+      <c r="O50" s="24">
+        <v>0</v>
+      </c>
+      <c r="P50" s="24" t="s">
         <v>342</v>
-      </c>
-      <c r="N50" s="24">
-        <v>1</v>
-      </c>
-      <c r="O50" s="24">
-        <v>0</v>
-      </c>
-      <c r="P50" s="24" t="s">
-        <v>343</v>
       </c>
       <c r="Q50" s="24">
         <v>3</v>
@@ -6939,15 +6940,15 @@
         <v>3591200</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K51" s="24">
         <v>3</v>
@@ -6956,7 +6957,7 @@
         <v>1000000</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -6965,7 +6966,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -7024,15 +7025,15 @@
         <v>3591400</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="K52" s="24">
         <v>3</v>
@@ -7041,7 +7042,7 @@
         <v>500000</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N52" s="24">
         <v>2</v>
@@ -7050,7 +7051,7 @@
         <v>10000</v>
       </c>
       <c r="P52" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="Q52" s="24">
         <v>1</v>
@@ -7109,10 +7110,10 @@
         <v>3591600</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H53" s="13"/>
       <c r="I53" s="13"/>
@@ -7126,7 +7127,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="N53" s="24">
         <v>2</v>
@@ -7135,7 +7136,7 @@
         <v>10000</v>
       </c>
       <c r="P53" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q53" s="24">
         <v>1</v>
@@ -7194,10 +7195,10 @@
         <v>3591900</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="13"/>
@@ -7211,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="24" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N54" s="24">
         <v>1</v>
@@ -7253,7 +7254,7 @@
         <v>1</v>
       </c>
       <c r="AA54" s="24" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AB54" s="24">
         <v>1</v>
@@ -7279,10 +7280,10 @@
         <v>3541800</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="13"/>
@@ -7364,10 +7365,10 @@
         <v>3541800</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="13"/>
@@ -7449,15 +7450,15 @@
         <v>3592100</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
       <c r="J57" s="24" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K57" s="24">
         <v>2</v>
@@ -7534,15 +7535,15 @@
         <v>3600200</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
       <c r="J58" s="21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="K58" s="21">
         <v>1</v>
@@ -7551,7 +7552,7 @@
         <v>8</v>
       </c>
       <c r="M58" s="21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N58" s="21">
         <v>2</v>
@@ -7560,7 +7561,7 @@
         <v>10000</v>
       </c>
       <c r="P58" s="21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q58" s="21">
         <v>1</v>
@@ -7619,24 +7620,24 @@
         <v>3600400</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
       <c r="J59" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="K59" s="21">
+        <v>1</v>
+      </c>
+      <c r="L59" s="21">
+        <v>1</v>
+      </c>
+      <c r="M59" s="21" t="s">
         <v>264</v>
-      </c>
-      <c r="K59" s="21">
-        <v>1</v>
-      </c>
-      <c r="L59" s="21">
-        <v>1</v>
-      </c>
-      <c r="M59" s="21" t="s">
-        <v>265</v>
       </c>
       <c r="N59" s="21">
         <v>2</v>
@@ -7704,15 +7705,15 @@
         <v>3600700</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K60" s="21">
         <v>1</v>
@@ -7721,7 +7722,7 @@
         <v>8</v>
       </c>
       <c r="M60" s="21" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="N60" s="21">
         <v>2</v>
@@ -7730,7 +7731,7 @@
         <v>10000</v>
       </c>
       <c r="P60" s="21" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q60" s="21">
         <v>1</v>
@@ -7789,10 +7790,10 @@
         <v>3601000</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
@@ -7806,7 +7807,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N61" s="21">
         <v>2</v>
@@ -7815,7 +7816,7 @@
         <v>10000</v>
       </c>
       <c r="P61" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Q61" s="21">
         <v>1</v>
@@ -7874,15 +7875,15 @@
         <v>3541600</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K62" s="21">
         <v>2</v>
@@ -7959,15 +7960,15 @@
         <v>3541800</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
       <c r="J63" s="21" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K63" s="21">
         <v>2</v>
@@ -8044,15 +8045,15 @@
         <v>3601300</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
       <c r="J64" s="21" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K64" s="21">
         <v>2</v>
@@ -8061,7 +8062,7 @@
         <v>10000</v>
       </c>
       <c r="M64" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N64" s="21">
         <v>2</v>
@@ -8070,7 +8071,7 @@
         <v>2000</v>
       </c>
       <c r="P64" s="21" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q64" s="21">
         <v>1</v>
@@ -8129,15 +8130,15 @@
         <v>3610300</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
       <c r="J65" s="22" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K65" s="22">
         <v>1</v>
@@ -8146,7 +8147,7 @@
         <v>8</v>
       </c>
       <c r="M65" s="22" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N65" s="22">
         <v>2</v>
@@ -8155,7 +8156,7 @@
         <v>10000</v>
       </c>
       <c r="P65" s="22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="Q65" s="22">
         <v>1</v>
@@ -8214,15 +8215,15 @@
         <v>3610500</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
       <c r="J66" s="22" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K66" s="22">
         <v>2</v>
@@ -8299,10 +8300,10 @@
         <v>3610700</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
@@ -8316,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N67" s="22">
         <v>2</v>
@@ -8325,7 +8326,7 @@
         <v>10000</v>
       </c>
       <c r="P67" s="22" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q67" s="22">
         <v>1</v>
@@ -8384,15 +8385,15 @@
         <v>3541400</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G68" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K68" s="22">
         <v>2</v>
@@ -8469,15 +8470,15 @@
         <v>3610900</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G69" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K69" s="22">
         <v>1</v>
@@ -8554,10 +8555,10 @@
         <v>3611100</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G70" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="13"/>
@@ -8639,15 +8640,15 @@
         <v>3611300</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G71" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K71" s="22">
         <v>3</v>
@@ -8665,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q71" s="22">
         <v>1</v>
@@ -8724,10 +8725,10 @@
         <v>3611500</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G72" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
@@ -8741,7 +8742,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N72" s="22">
         <v>2</v>
@@ -8750,7 +8751,7 @@
         <v>10000</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>
@@ -8809,15 +8810,15 @@
         <v>3611700</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G73" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="13"/>
       <c r="J73" s="22" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K73" s="22">
         <v>3</v>
@@ -8894,10 +8895,10 @@
         <v>3590800</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G74" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H74" s="13"/>
       <c r="I74" s="13"/>
@@ -8911,7 +8912,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N74" s="22">
         <v>2</v>
@@ -8920,7 +8921,7 @@
         <v>10000</v>
       </c>
       <c r="P74" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q74" s="22">
         <v>1</v>
@@ -9015,7 +9016,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" spans="5:19" x14ac:dyDescent="0.15">
@@ -9023,7 +9024,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="5:19" x14ac:dyDescent="0.15">
@@ -9031,7 +9032,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" spans="5:19" x14ac:dyDescent="0.15">
@@ -9042,10 +9043,10 @@
         <v>29</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14" spans="5:19" x14ac:dyDescent="0.15">
@@ -9053,19 +9054,19 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="15" spans="5:19" x14ac:dyDescent="0.15">
@@ -9073,19 +9074,19 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>519</v>
-      </c>
       <c r="S15" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="5:19" x14ac:dyDescent="0.15">
@@ -9096,19 +9097,19 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>481</v>
-      </c>
       <c r="S16" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="17" spans="5:19" x14ac:dyDescent="0.15">
@@ -9119,19 +9120,19 @@
         <v>31</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>483</v>
-      </c>
       <c r="S17" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="18" spans="5:19" x14ac:dyDescent="0.15">
@@ -9145,16 +9146,16 @@
         <v>38</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="S18" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" spans="5:19" x14ac:dyDescent="0.15">
@@ -9169,22 +9170,22 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>391</v>
-      </c>
       <c r="J19" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="S19" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="20" spans="5:19" x14ac:dyDescent="0.15">
@@ -9199,22 +9200,22 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="S20" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="21" spans="5:19" x14ac:dyDescent="0.15">
@@ -9229,22 +9230,22 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="S21" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="22" spans="5:19" x14ac:dyDescent="0.15">
@@ -9262,19 +9263,19 @@
         <v>106</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="S22" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="23" spans="5:19" x14ac:dyDescent="0.15">
@@ -9289,22 +9290,22 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="S23" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="5:19" x14ac:dyDescent="0.15">
@@ -9319,22 +9320,22 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="S24" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="25" spans="5:19" x14ac:dyDescent="0.15">
@@ -9349,22 +9350,22 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="S25" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26" spans="5:19" x14ac:dyDescent="0.15">
@@ -9379,22 +9380,22 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="S26" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="27" spans="5:19" x14ac:dyDescent="0.15">
@@ -9409,22 +9410,22 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>504</v>
-      </c>
       <c r="S27" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28" spans="5:19" x14ac:dyDescent="0.15">
@@ -9439,19 +9440,19 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>506</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="29" spans="5:19" x14ac:dyDescent="0.15">
@@ -9466,22 +9467,22 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K29" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="S29" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="5:19" x14ac:dyDescent="0.15">
@@ -9496,22 +9497,22 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="S30" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="31" spans="5:19" x14ac:dyDescent="0.15">
@@ -9526,22 +9527,22 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="S31" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" spans="5:19" x14ac:dyDescent="0.15">
@@ -9549,80 +9550,80 @@
         <v>103</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="33" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E33" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E34" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E35" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="36" spans="5:9" x14ac:dyDescent="0.15">
@@ -9631,10 +9632,10 @@
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="37" spans="5:9" x14ac:dyDescent="0.15">
@@ -9643,10 +9644,10 @@
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="38" spans="5:9" x14ac:dyDescent="0.15">
@@ -9655,10 +9656,10 @@
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="39" spans="5:9" x14ac:dyDescent="0.15">
@@ -9667,10 +9668,10 @@
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="40" spans="5:9" x14ac:dyDescent="0.15">
@@ -9679,10 +9680,10 @@
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="41" spans="5:9" x14ac:dyDescent="0.15">
@@ -9691,10 +9692,10 @@
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" spans="5:9" x14ac:dyDescent="0.15">
@@ -9703,10 +9704,10 @@
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="43" spans="5:9" x14ac:dyDescent="0.15">
@@ -9715,10 +9716,10 @@
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="44" spans="5:9" x14ac:dyDescent="0.15">
@@ -9727,10 +9728,10 @@
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="45" spans="5:9" x14ac:dyDescent="0.15">
@@ -9739,10 +9740,10 @@
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="46" spans="5:9" x14ac:dyDescent="0.15">
@@ -9751,10 +9752,10 @@
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="47" spans="5:9" x14ac:dyDescent="0.15">
@@ -9763,10 +9764,10 @@
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="48" spans="5:9" x14ac:dyDescent="0.15">
@@ -9775,10 +9776,10 @@
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49" spans="7:8" x14ac:dyDescent="0.15">
@@ -9787,7 +9788,7 @@
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="50" spans="7:8" x14ac:dyDescent="0.15">
@@ -9796,7 +9797,7 @@
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.15">
@@ -9805,7 +9806,7 @@
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.15">
@@ -9814,7 +9815,7 @@
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.15">
@@ -9823,7 +9824,7 @@
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.15">
@@ -9832,7 +9833,7 @@
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55" spans="7:8" x14ac:dyDescent="0.15">
@@ -9841,7 +9842,7 @@
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="56" spans="7:8" x14ac:dyDescent="0.15">
@@ -9850,7 +9851,7 @@
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="57" spans="7:8" x14ac:dyDescent="0.15">
@@ -9859,7 +9860,7 @@
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="58" spans="7:8" x14ac:dyDescent="0.15">
@@ -9868,7 +9869,7 @@
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="59" spans="7:8" x14ac:dyDescent="0.15">
@@ -9877,7 +9878,7 @@
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="60" spans="7:8" x14ac:dyDescent="0.15">
@@ -9886,7 +9887,7 @@
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="61" spans="7:8" x14ac:dyDescent="0.15">
@@ -9895,7 +9896,7 @@
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="62" spans="7:8" x14ac:dyDescent="0.15">
@@ -9904,7 +9905,7 @@
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="63" spans="7:8" x14ac:dyDescent="0.15">
@@ -9913,7 +9914,7 @@
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="64" spans="7:8" x14ac:dyDescent="0.15">
@@ -9922,7 +9923,7 @@
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="65" spans="7:8" x14ac:dyDescent="0.15">
@@ -9931,7 +9932,7 @@
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="66" spans="7:8" x14ac:dyDescent="0.15">
@@ -9940,7 +9941,7 @@
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="67" spans="7:8" x14ac:dyDescent="0.15">
@@ -9949,7 +9950,7 @@
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="68" spans="7:8" x14ac:dyDescent="0.15">
@@ -9958,7 +9959,7 @@
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="69" spans="7:8" x14ac:dyDescent="0.15">
@@ -9967,7 +9968,7 @@
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="70" spans="7:8" x14ac:dyDescent="0.15">
@@ -9976,7 +9977,7 @@
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="71" spans="7:8" x14ac:dyDescent="0.15">
@@ -9985,7 +9986,7 @@
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776A8CC2-4CF7-4493-B8DB-29542E5A2266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BE97C8-F66C-42DD-B22F-E998273E3B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -2881,7 +2881,7 @@
         <v>43</v>
       </c>
       <c r="K5" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="5">
         <v>300000</v>
@@ -2979,7 +2979,7 @@
         <v>43</v>
       </c>
       <c r="N6" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" s="6">
         <v>0</v>
@@ -2988,7 +2988,7 @@
         <v>43</v>
       </c>
       <c r="Q6" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="6">
         <v>0</v>
@@ -3068,7 +3068,7 @@
         <v>43</v>
       </c>
       <c r="N7" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" s="15">
         <v>0</v>
@@ -3077,7 +3077,7 @@
         <v>43</v>
       </c>
       <c r="Q7" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" s="15">
         <v>0</v>
@@ -3166,7 +3166,7 @@
         <v>43</v>
       </c>
       <c r="Q8" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="15">
         <v>0</v>
@@ -3255,7 +3255,7 @@
         <v>43</v>
       </c>
       <c r="Q9" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="15">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         <v>112</v>
       </c>
       <c r="K10" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" s="15">
-        <v>150000</v>
+        <v>1500</v>
       </c>
       <c r="M10" s="15" t="s">
         <v>113</v>
@@ -3344,7 +3344,7 @@
         <v>43</v>
       </c>
       <c r="Q10" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="15">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         <v>43</v>
       </c>
       <c r="Q11" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="15">
         <v>0</v>
@@ -3513,7 +3513,7 @@
         <v>43</v>
       </c>
       <c r="N12" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="15">
         <v>0</v>
@@ -3522,7 +3522,7 @@
         <v>43</v>
       </c>
       <c r="Q12" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="15">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>43</v>
       </c>
       <c r="N13" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="15">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>43</v>
       </c>
       <c r="Q13" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" s="15">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>43</v>
       </c>
       <c r="Q14" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="15">
         <v>0</v>
@@ -3789,7 +3789,7 @@
         <v>43</v>
       </c>
       <c r="Q15" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="15">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>43</v>
       </c>
       <c r="Q16" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="15">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>43</v>
       </c>
       <c r="Q17" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="15">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>43</v>
       </c>
       <c r="N18" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="15">
         <v>0</v>
@@ -4056,7 +4056,7 @@
         <v>43</v>
       </c>
       <c r="Q18" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="15">
         <v>0</v>
@@ -4136,7 +4136,7 @@
         <v>43</v>
       </c>
       <c r="N19" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="15">
         <v>0</v>
@@ -4145,7 +4145,7 @@
         <v>43</v>
       </c>
       <c r="Q19" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="15">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>43</v>
       </c>
       <c r="N20" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" s="15">
         <v>0</v>
@@ -4234,7 +4234,7 @@
         <v>43</v>
       </c>
       <c r="Q20" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="15">
         <v>0</v>
@@ -4314,7 +4314,7 @@
         <v>43</v>
       </c>
       <c r="N21" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="15">
         <v>0</v>
@@ -4323,7 +4323,7 @@
         <v>43</v>
       </c>
       <c r="Q21" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="15">
         <v>0</v>
@@ -4394,7 +4394,7 @@
         <v>43</v>
       </c>
       <c r="K22" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="17">
         <v>0</v>
@@ -4403,7 +4403,7 @@
         <v>43</v>
       </c>
       <c r="N22" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" s="17">
         <v>0</v>
@@ -4412,7 +4412,7 @@
         <v>43</v>
       </c>
       <c r="Q22" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="17">
         <v>0</v>
@@ -4572,7 +4572,7 @@
         <v>43</v>
       </c>
       <c r="K24" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="17">
         <v>1000</v>
@@ -4670,7 +4670,7 @@
         <v>163</v>
       </c>
       <c r="N25" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" s="17">
         <v>30</v>
@@ -4679,7 +4679,7 @@
         <v>43</v>
       </c>
       <c r="Q25" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" s="17">
         <v>0</v>
@@ -4857,7 +4857,7 @@
         <v>43</v>
       </c>
       <c r="Q27" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="17">
         <v>0</v>
@@ -4937,7 +4937,7 @@
         <v>70</v>
       </c>
       <c r="N28" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O28" s="17">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>70</v>
       </c>
       <c r="Q28" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="17">
         <v>0</v>
@@ -5035,7 +5035,7 @@
         <v>43</v>
       </c>
       <c r="Q29" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" s="18">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>43</v>
       </c>
       <c r="N31" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="18">
         <v>0</v>
@@ -5213,7 +5213,7 @@
         <v>43</v>
       </c>
       <c r="Q31" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" s="18">
         <v>0</v>
@@ -5293,7 +5293,7 @@
         <v>43</v>
       </c>
       <c r="N32" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="18">
         <v>0</v>
@@ -5302,7 +5302,7 @@
         <v>43</v>
       </c>
       <c r="Q32" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" s="18">
         <v>0</v>
@@ -5373,7 +5373,7 @@
         <v>43</v>
       </c>
       <c r="K33" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="18">
         <v>0</v>
@@ -5480,7 +5480,7 @@
         <v>43</v>
       </c>
       <c r="Q34" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="18">
         <v>0</v>
@@ -5569,7 +5569,7 @@
         <v>43</v>
       </c>
       <c r="Q35" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" s="19">
         <v>0</v>
@@ -5836,7 +5836,7 @@
         <v>43</v>
       </c>
       <c r="Q38" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" s="19">
         <v>0</v>
@@ -5996,7 +5996,7 @@
         <v>43</v>
       </c>
       <c r="K40" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="19">
         <v>0</v>
@@ -6281,7 +6281,7 @@
         <v>43</v>
       </c>
       <c r="Q43" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="20">
         <v>0</v>
@@ -6352,7 +6352,7 @@
         <v>43</v>
       </c>
       <c r="K44" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="20">
         <v>0</v>
@@ -6450,7 +6450,7 @@
         <v>322</v>
       </c>
       <c r="N45" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O45" s="20">
         <v>30</v>
@@ -6459,7 +6459,7 @@
         <v>43</v>
       </c>
       <c r="Q45" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" s="20">
         <v>0</v>
@@ -6620,7 +6620,7 @@
         <v>43</v>
       </c>
       <c r="N47" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O47" s="24">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>43</v>
       </c>
       <c r="Q47" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" s="24">
         <v>0</v>
@@ -6696,7 +6696,7 @@
         <v>43</v>
       </c>
       <c r="K48" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" s="24">
         <v>0</v>
@@ -6781,7 +6781,7 @@
         <v>43</v>
       </c>
       <c r="K49" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="24">
         <v>0</v>
@@ -7121,7 +7121,7 @@
         <v>43</v>
       </c>
       <c r="K53" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="24">
         <v>0</v>
@@ -7206,7 +7206,7 @@
         <v>43</v>
       </c>
       <c r="K54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="24">
         <v>0</v>
@@ -7224,7 +7224,7 @@
         <v>43</v>
       </c>
       <c r="Q54" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="24">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>43</v>
       </c>
       <c r="N55" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="24">
         <v>0</v>
@@ -7309,7 +7309,7 @@
         <v>43</v>
       </c>
       <c r="Q55" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="24">
         <v>0</v>
@@ -7385,7 +7385,7 @@
         <v>43</v>
       </c>
       <c r="N56" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="24">
         <v>0</v>
@@ -7394,7 +7394,7 @@
         <v>43</v>
       </c>
       <c r="Q56" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="24">
         <v>0</v>
@@ -7470,7 +7470,7 @@
         <v>43</v>
       </c>
       <c r="N57" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="24">
         <v>0</v>
@@ -7479,7 +7479,7 @@
         <v>43</v>
       </c>
       <c r="Q57" s="24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" s="24">
         <v>0</v>
@@ -7649,7 +7649,7 @@
         <v>43</v>
       </c>
       <c r="Q59" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" s="21">
         <v>0</v>
@@ -7801,7 +7801,7 @@
         <v>43</v>
       </c>
       <c r="K61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="21">
         <v>0</v>
@@ -7895,7 +7895,7 @@
         <v>43</v>
       </c>
       <c r="N62" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62" s="21">
         <v>0</v>
@@ -7904,7 +7904,7 @@
         <v>43</v>
       </c>
       <c r="Q62" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="21">
         <v>0</v>
@@ -7980,7 +7980,7 @@
         <v>43</v>
       </c>
       <c r="N63" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" s="21">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>43</v>
       </c>
       <c r="Q63" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" s="21">
         <v>0</v>
@@ -8235,7 +8235,7 @@
         <v>43</v>
       </c>
       <c r="N66" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" s="22">
         <v>0</v>
@@ -8244,7 +8244,7 @@
         <v>43</v>
       </c>
       <c r="Q66" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" s="22">
         <v>0</v>
@@ -8311,7 +8311,7 @@
         <v>43</v>
       </c>
       <c r="K67" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="22">
         <v>0</v>
@@ -8405,7 +8405,7 @@
         <v>43</v>
       </c>
       <c r="N68" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" s="22">
         <v>0</v>
@@ -8414,7 +8414,7 @@
         <v>43</v>
       </c>
       <c r="Q68" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" s="22">
         <v>0</v>
@@ -8490,7 +8490,7 @@
         <v>43</v>
       </c>
       <c r="N69" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69" s="22">
         <v>0</v>
@@ -8499,7 +8499,7 @@
         <v>43</v>
       </c>
       <c r="Q69" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69" s="22">
         <v>0</v>
@@ -8566,7 +8566,7 @@
         <v>43</v>
       </c>
       <c r="K70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="22">
         <v>0</v>
@@ -8575,7 +8575,7 @@
         <v>43</v>
       </c>
       <c r="N70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70" s="22">
         <v>0</v>
@@ -8584,7 +8584,7 @@
         <v>43</v>
       </c>
       <c r="Q70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70" s="22">
         <v>0</v>
@@ -8660,7 +8660,7 @@
         <v>43</v>
       </c>
       <c r="N71" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" s="22">
         <v>0</v>
@@ -8736,7 +8736,7 @@
         <v>43</v>
       </c>
       <c r="K72" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="22">
         <v>0</v>
@@ -8830,7 +8830,7 @@
         <v>43</v>
       </c>
       <c r="N73" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" s="22">
         <v>0</v>
@@ -8839,7 +8839,7 @@
         <v>43</v>
       </c>
       <c r="Q73" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="22">
         <v>0</v>
@@ -8906,7 +8906,7 @@
         <v>43</v>
       </c>
       <c r="K74" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="22">
         <v>0</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_effect_v8【迷宫-技能-技能效果】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935FAF2D-F3C5-430F-AC51-F5F33F5307F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB2C580-3D04-4F60-A750-008935FB9DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skilleffect_v8" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="备注" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skilleffect_v8!$A$4:$AC$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1047" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="592">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1025,67 +1025,907 @@
     <t>3590603:1</t>
   </si>
   <si>
+    <t>3590803:1</t>
+  </si>
+  <si>
+    <t>3591001:1</t>
+  </si>
+  <si>
+    <t>3591201:1</t>
+  </si>
+  <si>
+    <t>3591202:1</t>
+  </si>
+  <si>
+    <t>3591203:1</t>
+  </si>
+  <si>
+    <t>3591401:1</t>
+  </si>
+  <si>
+    <t>3591402:1</t>
+  </si>
+  <si>
+    <t>3591403:1</t>
+  </si>
+  <si>
+    <t>3591602:1</t>
+  </si>
+  <si>
+    <t>3591603:1</t>
+  </si>
+  <si>
+    <t>3591902:1</t>
+  </si>
+  <si>
+    <t>3600701:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击次数触发技能重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击技能暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能攻击累计额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀暴击触发斩杀血线变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀触发暴击率提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
     <t>3590802:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3610901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611303:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611502:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3611503:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
     <t>3590803:1</t>
-  </si>
-  <si>
-    <t>3591001:1</t>
-  </si>
-  <si>
-    <t>3591201:1</t>
-  </si>
-  <si>
-    <t>3591202:1</t>
-  </si>
-  <si>
-    <t>3591203:1</t>
-  </si>
-  <si>
-    <t>3591401:1</t>
-  </si>
-  <si>
-    <t>3591402:1</t>
-  </si>
-  <si>
-    <t>3591403:1</t>
-  </si>
-  <si>
-    <t>3591602:1</t>
-  </si>
-  <si>
-    <t>3591603:1</t>
-  </si>
-  <si>
-    <t>3591902:1</t>
-  </si>
-  <si>
-    <t>3600701:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击次数触发技能重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击技能暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能攻击累计额外次数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀暴击触发斩杀血线变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀触发暴击率提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击触发技能暴击伤害提高、致命暴击、额外次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能名称</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数描述</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>有护盾时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>低血时受到伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人伤害降低</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-敌人受到伤害提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能效果-光环效果影响范围变化</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标血量低于百万分比触发斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀血线提高效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581202:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581207:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>attr_value_8_variable_id</t>
+  </si>
+  <si>
+    <t>attr_value_8_type</t>
+  </si>
+  <si>
+    <t>attr_value_8</t>
+  </si>
+  <si>
+    <t>参数8关联的变量id</t>
+  </si>
+  <si>
+    <t>参数8数值类型</t>
+  </si>
+  <si>
+    <t>参数8</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
+  </si>
+  <si>
+    <t>3041108:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3560208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581208:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591002:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591003:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时被攻击受到额外伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
+  </si>
+  <si>
+    <t>触电时受到伤害提高</t>
+  </si>
+  <si>
+    <t>3570503:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+  </si>
+  <si>
+    <t>使目标触电时，造成1次触电伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
+  </si>
+  <si>
+    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
+  </si>
+  <si>
+    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
+  </si>
+  <si>
+    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
+  </si>
+  <si>
+    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+  </si>
+  <si>
+    <t>攻击冰冻目标时造成额外伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒受到额外中毒伤害</t>
+  </si>
+  <si>
+    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580702:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活回复血量、触发次数、触发间隔</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3591908:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561401:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561402:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3561408:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3570205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3580205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3581205:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3590405:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>致命暴击状态攻速提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回血效果提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3551103:2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数8结算间隔时间</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>逻辑属性id</t>
+  </si>
+  <si>
+    <t>技能效果</t>
+  </si>
+  <si>
+    <t>技能名称</t>
+  </si>
+  <si>
+    <t>参数描述</t>
+  </si>
+  <si>
+    <t>效果叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>结算间隔时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复中buff组的cd时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数5</t>
+  </si>
+  <si>
+    <t>参数6</t>
+  </si>
+  <si>
+    <t>持续时间（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果最大叠加层数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果基础命中率（万分比）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果触发间隔（毫秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数4LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发的技能id</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数9</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数2</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数10</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数11</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数12</t>
+  </si>
+  <si>
+    <t>参数13</t>
+  </si>
+  <si>
+    <t>击中回复生命值-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中回复效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数14</t>
+  </si>
+  <si>
+    <t>参数15</t>
+  </si>
+  <si>
+    <t>参数16</t>
+  </si>
+  <si>
+    <t>击中回复生命值-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-自身最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命-目标最大生命值百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数17</t>
+  </si>
+  <si>
+    <t>参数18</t>
+  </si>
+  <si>
+    <t>参数19</t>
+  </si>
+  <si>
+    <t>参数20</t>
+  </si>
+  <si>
+    <t>参数21</t>
+  </si>
+  <si>
+    <t>参数22</t>
+  </si>
+  <si>
+    <t>参数28</t>
+  </si>
+  <si>
+    <t>参数29</t>
+  </si>
+  <si>
+    <t>获得护盾-自身生命百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀回复生命效果提高万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾-自身已损失生命万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>复活</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>触发自动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数30</t>
+  </si>
+  <si>
+    <t>参数31</t>
+  </si>
+  <si>
+    <t>参数32</t>
+  </si>
+  <si>
+    <t>参数33</t>
+  </si>
+  <si>
+    <t>参数34</t>
+  </si>
+  <si>
+    <t>参数35</t>
+  </si>
+  <si>
+    <t>参数36</t>
+  </si>
+  <si>
+    <t>参数37</t>
+  </si>
+  <si>
+    <t>参数38</t>
+  </si>
+  <si>
+    <t>参数39</t>
+  </si>
+  <si>
+    <t>参数40</t>
+  </si>
+  <si>
+    <t>参数41</t>
+  </si>
+  <si>
+    <t>参数42</t>
+  </si>
+  <si>
+    <t>参数43</t>
+  </si>
+  <si>
+    <t>参数44</t>
+  </si>
+  <si>
+    <t>主动技能</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>回复生命</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>击中目标</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰霜新星</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪电链</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>传染</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>瘟疫</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>多重打击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>旋风斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>斩杀</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>半月斩</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡爆炸</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>电磁爆发</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-万分比</t>
+  </si>
+  <si>
+    <t>技能增加-普通攻击范围万分比</t>
+  </si>
+  <si>
+    <t>攻击提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提高-攻击的元素类型</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数25LIST</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数45</t>
+  </si>
+  <si>
+    <t>参数46</t>
+  </si>
+  <si>
+    <t>参数47</t>
+  </si>
+  <si>
+    <t>参数48</t>
+  </si>
+  <si>
+    <t>参数49</t>
+  </si>
+  <si>
+    <t>参数50</t>
+  </si>
+  <si>
+    <t>参数51</t>
+  </si>
+  <si>
+    <t>参数52</t>
+  </si>
+  <si>
+    <t>参数53</t>
+  </si>
+  <si>
+    <t>参数54</t>
+  </si>
+  <si>
+    <t>参数55</t>
+  </si>
+  <si>
+    <t>参数56</t>
+  </si>
+  <si>
+    <t>生命上限提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命上限提高-百万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击范围提高-万分比</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击目标数量提高-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能增加-固定值</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S</t>
+  </si>
+  <si>
+    <t>auto_cd</t>
+  </si>
+  <si>
+    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
+  </si>
+  <si>
+    <t>release_ratio</t>
+  </si>
+  <si>
+    <t>参数-释放几率</t>
+  </si>
+  <si>
+    <t>release_num</t>
+  </si>
+  <si>
+    <t>参数-释放次数</t>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>参数-释放的技能id</t>
+  </si>
+  <si>
+    <t>total_attack_num</t>
+  </si>
+  <si>
+    <t>参数-累计发起攻击次数时</t>
+  </si>
+  <si>
+    <t>lose_hp_ratio</t>
+  </si>
+  <si>
+    <t>参数-损失自身生命最大值百万分比时</t>
+  </si>
+  <si>
+    <t>kill_target_after</t>
+  </si>
+  <si>
+    <t>参数-击杀目标后</t>
+  </si>
+  <si>
+    <t>after_attack_crit</t>
+  </si>
+  <si>
+    <t>参数-攻击暴击后</t>
+  </si>
+  <si>
+    <t>after_use_skill</t>
+  </si>
+  <si>
+    <t>参数-释放【技能id】后</t>
+  </si>
+  <si>
+    <t>cycle_time</t>
+  </si>
+  <si>
+    <t>参数-每过固定时间（毫秒）时</t>
+  </si>
+  <si>
+    <t>after_skill_hit</t>
+  </si>
+  <si>
+    <t>参数-【技能id】命中后</t>
+  </si>
+  <si>
+    <t>after_self_death</t>
+  </si>
+  <si>
+    <t>参数-自身死亡后释放</t>
+  </si>
+  <si>
+    <t>MAP&lt;INT:INT&gt;_S</t>
+  </si>
+  <si>
+    <t>self_have_effect</t>
+  </si>
+  <si>
+    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_have_effect</t>
+  </si>
+  <si>
+    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_over</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>target_hp_ratio_under</t>
+  </si>
+  <si>
+    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
+  </si>
+  <si>
+    <t>to_target_effect_hit</t>
+  </si>
+  <si>
+    <t>参数-对目标施加【效果id】命中时</t>
+  </si>
+  <si>
+    <t>order</t>
+  </si>
+  <si>
+    <t>自动</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害总加成</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542801:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542601:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543001:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542607:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542807:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543007:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542605:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3542805:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3543005:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3540201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-正义光环</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>60120001,60130000</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>护盾技能-每X秒获得最大生命值的护盾</t>
+  </si>
+  <si>
+    <t>955001002</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得护盾</t>
+  </si>
+  <si>
+    <t>3590405:1</t>
+  </si>
+  <si>
+    <t>（获得）雷击</t>
+  </si>
+  <si>
+    <t>（获得）冰弹</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>（获得）陨石</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
@@ -1093,818 +1933,193 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
-    <t>3610901:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611301:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611303:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611701:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611502:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3611503:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590803:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能名称</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数描述</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>有护盾时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>低血时受到伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人伤害降低</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-敌人受到伤害提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能效果-光环效果影响范围变化</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>目标血量低于百万分比触发斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀血线提高效果</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581201:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581202:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581207:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570902:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>attr_value_8_variable_id</t>
-  </si>
-  <si>
-    <t>attr_value_8_type</t>
-  </si>
-  <si>
-    <t>attr_value_8</t>
-  </si>
-  <si>
-    <t>参数8关联的变量id</t>
-  </si>
-  <si>
-    <t>参数8数值类型</t>
-  </si>
-  <si>
-    <t>参数8</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，造成{[火元素直接伤害]【参数1万分比】}，【参数2】的[额外火元素持续伤害]，效果持续【参数5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，效果持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，触发等同于[毒元素直接伤害]*【参数1万分比毒持续buff系数】+【参数2】的[额外毒持续伤害]，状态持续【持续5】毫秒，最大可叠加【参数7】层</t>
-  </si>
-  <si>
-    <t>3041108:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>拥有这个技能效果时，命中敌人时，攻击者回复固定值【参数1固定值】的血量，触发冷却时间【参数8】毫秒</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3560208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581208:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591002:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591003:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时被攻击受到额外伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触电时，[受到所有类型伤害提高]【参数1万分比】+【参数2】受到[受到所有类型额外伤害固定值]</t>
-  </si>
-  <si>
-    <t>触电时受到伤害提高</t>
-  </si>
-  <si>
-    <t>3570503:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-  </si>
-  <si>
-    <t>使目标触电时，造成1次触电伤害</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冻状态，持续时间【参数5】，冰冻状态命中率【参数6命中率】</t>
-  </si>
-  <si>
-    <t>每攻击【参数1】次，有【参数2】几率触发【参数3】次指定技能【参数4】</t>
-  </si>
-  <si>
-    <t>每【参数8】毫秒，在释放冰霜新星时有【参数2】几率，触发【参数3】次数，技能id【参数4】</t>
-  </si>
-  <si>
-    <t>对冰冻有配置标再次触发冰冻效果时，造成{[最终冰元素伤害]【参数1万分比】+【参数2固定值】}的[最终冰元素伤害</t>
-  </si>
-  <si>
-    <t>使目标冰冻时，触发目标{生命最大值【参数1百万分比】}的[冰元素基础伤害]+{【参数2固定值】}的[额外冰元素伤害固定值]</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时，造成{[冰元素最终伤害]【参数1万分比】+【参数2固定值】}的[额外最终冰元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-  </si>
-  <si>
-    <t>攻击冰冻目标时造成额外伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒受到额外中毒伤害</t>
-  </si>
-  <si>
-    <t>中毒目标再次中毒时，造成每次中毒结算伤害*【参数1】次数*【参数2万分比】的[最终毒元素伤害]</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580702:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活回复血量、触发次数、触发间隔</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3591908:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561401:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561402:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3561408:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>燃烧时，被攻击会额外受到1次[最终火元素伤害]【参数1万分比】+【参数2固定值】的[额外最终火元素伤害]，该效果每【参数8】毫秒触发1次。</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3570205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3580205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3581205:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3590405:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>致命暴击状态攻速提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3592101:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回血效果提高</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3551103:2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数8结算间隔时间</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>逻辑属性id</t>
-  </si>
-  <si>
-    <t>技能效果</t>
-  </si>
-  <si>
-    <t>技能名称</t>
-  </si>
-  <si>
-    <t>参数描述</t>
-  </si>
-  <si>
-    <t>效果叠加层数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>结算间隔时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重复中buff组的cd时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数5</t>
-  </si>
-  <si>
-    <t>参数6</t>
-  </si>
-  <si>
-    <t>持续时间（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果最大叠加层数</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果基础命中率（万分比）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>效果触发间隔（毫秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数4LIST</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发的技能id</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数9</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数2</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数10</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数11</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数12</t>
-  </si>
-  <si>
-    <t>参数13</t>
-  </si>
-  <si>
-    <t>击中回复生命值-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击中回复效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数14</t>
-  </si>
-  <si>
-    <t>参数15</t>
-  </si>
-  <si>
-    <t>参数16</t>
-  </si>
-  <si>
-    <t>击中回复生命值-自身最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-自身最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命-目标最大生命值百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数17</t>
-  </si>
-  <si>
-    <t>参数18</t>
-  </si>
-  <si>
-    <t>参数19</t>
-  </si>
-  <si>
-    <t>参数20</t>
-  </si>
-  <si>
-    <t>参数21</t>
-  </si>
-  <si>
-    <t>参数22</t>
-  </si>
-  <si>
-    <t>参数28</t>
-  </si>
-  <si>
-    <t>参数29</t>
-  </si>
-  <si>
-    <t>获得护盾-自身生命百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击杀回复生命效果提高万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>获得护盾-自身已损失生命万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>复活</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>触发自动技能</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数30</t>
-  </si>
-  <si>
-    <t>参数31</t>
-  </si>
-  <si>
-    <t>参数32</t>
-  </si>
-  <si>
-    <t>参数33</t>
-  </si>
-  <si>
-    <t>参数34</t>
-  </si>
-  <si>
-    <t>参数35</t>
-  </si>
-  <si>
-    <t>参数36</t>
-  </si>
-  <si>
-    <t>参数37</t>
-  </si>
-  <si>
-    <t>参数38</t>
-  </si>
-  <si>
-    <t>参数39</t>
-  </si>
-  <si>
-    <t>参数40</t>
-  </si>
-  <si>
-    <t>参数41</t>
-  </si>
-  <si>
-    <t>参数42</t>
-  </si>
-  <si>
-    <t>参数43</t>
-  </si>
-  <si>
-    <t>参数44</t>
-  </si>
-  <si>
-    <t>主动技能</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>回复生命</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>击中目标</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰霜新星</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>陨石</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>闪电链</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>传染</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>瘟疫</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>多重打击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>旋风斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>斩杀</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>半月斩</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>死亡爆炸</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>电磁爆发</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>重击</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能增加-万分比</t>
-  </si>
-  <si>
-    <t>技能增加-普通攻击范围万分比</t>
-  </si>
-  <si>
-    <t>攻击提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>防御提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击提高-攻击的元素类型</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数25LIST</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>参数45</t>
-  </si>
-  <si>
-    <t>参数46</t>
-  </si>
-  <si>
-    <t>参数47</t>
-  </si>
-  <si>
-    <t>参数48</t>
-  </si>
-  <si>
-    <t>参数49</t>
-  </si>
-  <si>
-    <t>参数50</t>
-  </si>
-  <si>
-    <t>参数51</t>
-  </si>
-  <si>
-    <t>参数52</t>
-  </si>
-  <si>
-    <t>参数53</t>
-  </si>
-  <si>
-    <t>参数54</t>
-  </si>
-  <si>
-    <t>参数55</t>
-  </si>
-  <si>
-    <t>参数56</t>
-  </si>
-  <si>
-    <t>生命上限提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>生命上限提高-百万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击速度提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>移动速度提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击范围提高-万分比</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击目标数量提高-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能增加-固定值</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-  </si>
-  <si>
-    <t>auto_cd</t>
-  </si>
-  <si>
-    <t>参数-重复触发自动释放冷却时间（毫秒）</t>
-  </si>
-  <si>
-    <t>release_ratio</t>
-  </si>
-  <si>
-    <t>参数-释放几率</t>
-  </si>
-  <si>
-    <t>release_num</t>
-  </si>
-  <si>
-    <t>参数-释放次数</t>
-  </si>
-  <si>
-    <t>LIST&lt;INT&gt;_S</t>
-  </si>
-  <si>
-    <t>skill_id</t>
-  </si>
-  <si>
-    <t>参数-释放的技能id</t>
-  </si>
-  <si>
-    <t>total_attack_num</t>
-  </si>
-  <si>
-    <t>参数-累计发起攻击次数时</t>
-  </si>
-  <si>
-    <t>lose_hp_ratio</t>
-  </si>
-  <si>
-    <t>参数-损失自身生命最大值百万分比时</t>
-  </si>
-  <si>
-    <t>kill_target_after</t>
-  </si>
-  <si>
-    <t>参数-击杀目标后</t>
-  </si>
-  <si>
-    <t>after_attack_crit</t>
-  </si>
-  <si>
-    <t>参数-攻击暴击后</t>
-  </si>
-  <si>
-    <t>after_use_skill</t>
-  </si>
-  <si>
-    <t>参数-释放【技能id】后</t>
-  </si>
-  <si>
-    <t>cycle_time</t>
-  </si>
-  <si>
-    <t>参数-每过固定时间（毫秒）时</t>
-  </si>
-  <si>
-    <t>after_skill_hit</t>
-  </si>
-  <si>
-    <t>参数-【技能id】命中后</t>
-  </si>
-  <si>
-    <t>after_self_death</t>
-  </si>
-  <si>
-    <t>参数-自身死亡后释放</t>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S</t>
-  </si>
-  <si>
-    <t>self_have_effect</t>
-  </si>
-  <si>
-    <t>参数-自身拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>target_have_effect</t>
-  </si>
-  <si>
-    <t>参数-目标拥有【效果id：&gt;=层数】时</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_over</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&gt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>target_hp_ratio_under</t>
-  </si>
-  <si>
-    <t>参数-目标当前生命值&lt;=最大生命值的百万分之X时</t>
-  </si>
-  <si>
-    <t>to_target_effect_hit</t>
-  </si>
-  <si>
-    <t>参数-对目标施加【效果id】命中时</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>自动</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>受到的伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成伤害总加成</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>造成的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>受到的伤害总加成【参数1万分比】，持续时间【参数5持续时间】，最大可叠加【参数7】层</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542801:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542601:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543001:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542607:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542807:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543007:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542605:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3542805:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3543005:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>3540201:1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>光环技能-正义光环</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>60120001,60130000</t>
+    <t>普攻击中回血效果提高</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中回血</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592401:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592201:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>3592202:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击目标数量</t>
+  </si>
+  <si>
+    <t>雷击伤害</t>
+  </si>
+  <si>
+    <t>技能效果-数量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹数量</t>
+  </si>
+  <si>
+    <t>冰弹伤害</t>
+  </si>
+  <si>
+    <t>冰弹范围</t>
+  </si>
+  <si>
+    <t>5000301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5000903:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加冰弹次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>追加冰弹伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能效果-追加次数</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5001101:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰弹命中后产生冰爆</t>
+  </si>
+  <si>
+    <t>5001301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】额外冰弹数量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】冰弹伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】追加冰弹次数，【参数3】释放冰弹延迟时间后追加冰弹</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数2】追加冰弹调整伤害，如果0则和原冰弹伤害相等</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻痹状态（无法攻击和移动），持续时间【参数5】，状态命中率【参数6】</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>雷击概率附加麻痹</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5200702:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石额外范围</t>
+  </si>
+  <si>
+    <t>陨石伤害</t>
+  </si>
+  <si>
+    <t>陨石数量</t>
+  </si>
+  <si>
+    <t>陨石落地后产生冲击波</t>
+  </si>
+  <si>
+    <t>技能效果-额外效果</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100301:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100501:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100701:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100901:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>5100902:1</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】陨石伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】陨石数量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】冰弹额外范围（度数）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】陨石额外范围（半径）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】雷击目标数量</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数1】雷击伤害</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>陨石落地后产生冲击波，【参数1】冲击波相对于陨石的额外范围（半径），【参数2】冲击波调整伤害，如果0则和原陨石伤害相等</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>【参数2】冰爆调整伤害，如果0则和原冰弹伤害相等；默认值-60%</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -1912,7 +2127,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2042,8 +2257,16 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2105,6 +2328,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2176,7 +2405,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
@@ -2190,8 +2419,11 @@
     <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2229,9 +2461,12 @@
     <xf numFmtId="0" fontId="15" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="6">
     <cellStyle name="差" xfId="4" builtinId="27"/>
+    <cellStyle name="差 2" xfId="5" xr:uid="{4CD9D8B4-CD25-459C-86C6-6BA0747D60BF}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="适中" xfId="2" builtinId="28"/>
     <cellStyle name="输入" xfId="1" builtinId="20"/>
@@ -2528,7 +2763,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
@@ -2539,7 +2774,7 @@
     <col min="6" max="6" width="29.75" customWidth="1"/>
     <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="9" max="9" width="30.125" customWidth="1"/>
     <col min="10" max="11" width="15.125" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="14" width="15.125" customWidth="1"/>
@@ -2671,13 +2906,13 @@
         <v>65</v>
       </c>
       <c r="AA2" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="AB2" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="AB2" s="7" t="s">
-        <v>326</v>
-      </c>
       <c r="AC2" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.2">
@@ -2760,13 +2995,13 @@
         <v>103</v>
       </c>
       <c r="AA3" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="AB3" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="AB3" s="7" t="s">
+      <c r="AC3" s="7" t="s">
         <v>328</v>
-      </c>
-      <c r="AC3" s="7" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.2">
@@ -2786,16 +3021,16 @@
         <v>64</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>30</v>
@@ -2849,13 +3084,13 @@
         <v>106</v>
       </c>
       <c r="AA4" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="AB4" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="AB4" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="AC4" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.2">
@@ -2973,7 +3208,7 @@
         <v>47</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>89</v>
@@ -3027,7 +3262,7 @@
         <v>0</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AB6" s="6">
         <v>1</v>
@@ -3065,7 +3300,7 @@
         <v>164</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K7" s="15">
         <v>2</v>
@@ -4133,7 +4368,7 @@
         <v>176</v>
       </c>
       <c r="J19" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K19" s="15">
         <v>2</v>
@@ -4163,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="U19" s="15">
         <v>4000</v>
@@ -4175,7 +4410,7 @@
         <v>10000</v>
       </c>
       <c r="X19" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="Y19" s="15">
         <v>1</v>
@@ -4210,7 +4445,7 @@
         <v>3542800</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>183</v>
@@ -4219,10 +4454,10 @@
         <v>182</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="K20" s="15">
         <v>2</v>
@@ -4252,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="T20" s="15" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="U20" s="15">
         <v>-1</v>
@@ -4264,7 +4499,7 @@
         <v>10000</v>
       </c>
       <c r="X20" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="Y20" s="15">
         <v>1</v>
@@ -4299,7 +4534,7 @@
         <v>3543000</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>183</v>
@@ -4308,10 +4543,10 @@
         <v>182</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="J21" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="K21" s="15">
         <v>2</v>
@@ -4341,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="T21" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="U21" s="15">
         <v>-1</v>
@@ -4353,7 +4588,7 @@
         <v>10000</v>
       </c>
       <c r="X21" s="15" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="Y21" s="15">
         <v>1</v>
@@ -4397,7 +4632,7 @@
         <v>162</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>43</v>
@@ -4486,7 +4721,7 @@
         <v>161</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J23" s="17" t="s">
         <v>80</v>
@@ -4575,7 +4810,7 @@
         <v>153</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J24" s="17" t="s">
         <v>43</v>
@@ -4664,7 +4899,7 @@
         <v>157</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="J25" s="17" t="s">
         <v>85</v>
@@ -4753,7 +4988,7 @@
         <v>158</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J26" s="17" t="s">
         <v>86</v>
@@ -4774,7 +5009,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="17" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q26" s="17">
         <v>1</v>
@@ -4833,7 +5068,7 @@
         <v>3551300</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>184</v>
@@ -4842,7 +5077,7 @@
         <v>159</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J27" s="17" t="s">
         <v>88</v>
@@ -5020,7 +5255,7 @@
         <v>191</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J29" s="18" t="s">
         <v>203</v>
@@ -5074,7 +5309,7 @@
         <v>1</v>
       </c>
       <c r="AA29" s="18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AB29" s="18">
         <v>1</v>
@@ -5456,19 +5691,19 @@
         <v>3561400</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G34" s="13" t="s">
         <v>188</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J34" s="18" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K34" s="18">
         <v>2</v>
@@ -5477,7 +5712,7 @@
         <v>3500</v>
       </c>
       <c r="M34" s="18" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N34" s="18">
         <v>35</v>
@@ -5519,7 +5754,7 @@
         <v>1</v>
       </c>
       <c r="AA34" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AB34" s="18">
         <v>1</v>
@@ -5587,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="U35" s="19">
         <v>4000</v>
@@ -5664,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="P36" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q36" s="19">
         <v>2</v>
@@ -5812,7 +6047,7 @@
         <v>3570900</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G38" s="13" t="s">
         <v>189</v>
@@ -5821,7 +6056,7 @@
         <v>199</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J38" s="19" t="s">
         <v>219</v>
@@ -5833,7 +6068,7 @@
         <v>2000</v>
       </c>
       <c r="M38" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="N38" s="19">
         <v>1</v>
@@ -5901,16 +6136,16 @@
         <v>3571100</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>189</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="J39" s="19" t="s">
         <v>220</v>
@@ -6088,7 +6323,7 @@
         <v>201</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J41" s="20" t="s">
         <v>223</v>
@@ -6121,7 +6356,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="20" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U41" s="20">
         <v>4000</v>
@@ -6142,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="AA41" s="20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AB41" s="20">
         <v>1</v>
@@ -6257,16 +6492,16 @@
         <v>3580700</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>190</v>
       </c>
       <c r="H43" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>357</v>
-      </c>
-      <c r="I43" s="13" t="s">
-        <v>358</v>
       </c>
       <c r="J43" s="20" t="s">
         <v>229</v>
@@ -6278,7 +6513,7 @@
         <v>5</v>
       </c>
       <c r="M43" s="20" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N43" s="20">
         <v>2</v>
@@ -6444,10 +6679,10 @@
         <v>187</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J45" s="20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K45" s="20">
         <v>2</v>
@@ -6456,7 +6691,7 @@
         <v>3000</v>
       </c>
       <c r="M45" s="20" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="N45" s="20">
         <v>1</v>
@@ -6477,7 +6712,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="20" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U45" s="20">
         <v>4000</v>
@@ -6489,7 +6724,7 @@
         <v>10000</v>
       </c>
       <c r="X45" s="20" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Y45" s="20">
         <v>1</v>
@@ -6498,7 +6733,7 @@
         <v>10</v>
       </c>
       <c r="AA45" s="20" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AB45" s="20">
         <v>1</v>
@@ -6647,7 +6882,7 @@
         <v>59030001</v>
       </c>
       <c r="T47" s="24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U47" s="24">
         <v>-1</v>
@@ -6796,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="24" t="s">
-        <v>284</v>
+        <v>541</v>
       </c>
       <c r="N49" s="24">
         <v>2</v>
@@ -6805,7 +7040,7 @@
         <v>10000</v>
       </c>
       <c r="P49" s="24" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q49" s="24">
         <v>1</v>
@@ -6872,7 +7107,7 @@
       <c r="H50" s="13"/>
       <c r="I50" s="13"/>
       <c r="J50" s="24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K50" s="24">
         <v>2</v>
@@ -6881,16 +7116,16 @@
         <v>0</v>
       </c>
       <c r="M50" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="N50" s="24">
+        <v>1</v>
+      </c>
+      <c r="O50" s="24">
+        <v>0</v>
+      </c>
+      <c r="P50" s="24" t="s">
         <v>341</v>
-      </c>
-      <c r="N50" s="24">
-        <v>1</v>
-      </c>
-      <c r="O50" s="24">
-        <v>0</v>
-      </c>
-      <c r="P50" s="24" t="s">
-        <v>342</v>
       </c>
       <c r="Q50" s="24">
         <v>3</v>
@@ -6957,7 +7192,7 @@
       <c r="H51" s="13"/>
       <c r="I51" s="13"/>
       <c r="J51" s="24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K51" s="24">
         <v>3</v>
@@ -6966,7 +7201,7 @@
         <v>1000000</v>
       </c>
       <c r="M51" s="24" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="N51" s="24">
         <v>2</v>
@@ -6975,7 +7210,7 @@
         <v>10000</v>
       </c>
       <c r="P51" s="24" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Q51" s="24">
         <v>1</v>
@@ -7042,7 +7277,7 @@
       <c r="H52" s="13"/>
       <c r="I52" s="13"/>
       <c r="J52" s="24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="K52" s="24">
         <v>3</v>
@@ -7051,7 +7286,7 @@
         <v>500000</v>
       </c>
       <c r="M52" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N52" s="24">
         <v>2</v>
@@ -7060,7 +7295,7 @@
         <v>10000</v>
       </c>
       <c r="P52" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q52" s="24">
         <v>1</v>
@@ -7136,7 +7371,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="24" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="N53" s="24">
         <v>2</v>
@@ -7145,7 +7380,7 @@
         <v>10000</v>
       </c>
       <c r="P53" s="24" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Q53" s="24">
         <v>1</v>
@@ -7204,7 +7439,7 @@
         <v>3591900</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>244</v>
@@ -7221,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="24" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N54" s="24">
         <v>1</v>
@@ -7263,7 +7498,7 @@
         <v>1</v>
       </c>
       <c r="AA54" s="24" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AB54" s="24">
         <v>1</v>
@@ -7289,7 +7524,7 @@
         <v>3541800</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>244</v>
@@ -7374,7 +7609,7 @@
         <v>3541800</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>244</v>
@@ -7459,7 +7694,7 @@
         <v>3592100</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>244</v>
@@ -7467,7 +7702,7 @@
       <c r="H57" s="13"/>
       <c r="I57" s="13"/>
       <c r="J57" s="24" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K57" s="24">
         <v>2</v>
@@ -7528,181 +7763,181 @@
       </c>
     </row>
     <row r="58" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A58" s="21">
-        <v>60010001</v>
-      </c>
-      <c r="B58" s="21">
-        <v>6001</v>
-      </c>
-      <c r="C58" s="21">
-        <v>1</v>
-      </c>
-      <c r="D58" s="21">
-        <v>0</v>
-      </c>
-      <c r="E58" s="21">
-        <v>3600200</v>
+      <c r="A58" s="25">
+        <v>59130001</v>
+      </c>
+      <c r="B58" s="24">
+        <v>5913</v>
+      </c>
+      <c r="C58" s="24">
+        <v>1</v>
+      </c>
+      <c r="D58" s="24">
+        <v>0</v>
+      </c>
+      <c r="E58" s="24">
+        <v>3591000</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>256</v>
+        <v>543</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="13"/>
-      <c r="J58" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="K58" s="21">
-        <v>1</v>
-      </c>
-      <c r="L58" s="21">
-        <v>8</v>
-      </c>
-      <c r="M58" s="21" t="s">
-        <v>261</v>
-      </c>
-      <c r="N58" s="21">
-        <v>2</v>
-      </c>
-      <c r="O58" s="21">
+      <c r="J58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="K58" s="24">
+        <v>1</v>
+      </c>
+      <c r="L58" s="24">
+        <v>0</v>
+      </c>
+      <c r="M58" s="24" t="s">
+        <v>545</v>
+      </c>
+      <c r="N58" s="24">
+        <v>1</v>
+      </c>
+      <c r="O58" s="24">
+        <v>0</v>
+      </c>
+      <c r="P58" s="24" t="s">
+        <v>546</v>
+      </c>
+      <c r="Q58" s="24">
+        <v>3</v>
+      </c>
+      <c r="R58" s="24">
+        <v>0</v>
+      </c>
+      <c r="S58" s="24">
+        <v>0</v>
+      </c>
+      <c r="T58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U58" s="24">
+        <v>-1</v>
+      </c>
+      <c r="V58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W58" s="24">
         <v>10000</v>
       </c>
-      <c r="P58" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q58" s="21">
-        <v>1</v>
-      </c>
-      <c r="R58" s="21">
-        <v>1</v>
-      </c>
-      <c r="S58" s="21">
-        <v>0</v>
-      </c>
-      <c r="T58" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U58" s="21">
-        <v>0</v>
-      </c>
-      <c r="V58" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W58" s="21">
-        <v>10000</v>
-      </c>
-      <c r="X58" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y58" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z58" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA58" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB58" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC58" s="21">
+      <c r="X58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y58" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z58" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA58" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB58" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A59" s="21">
-        <v>60020001</v>
-      </c>
-      <c r="B59" s="21">
-        <v>6002</v>
-      </c>
-      <c r="C59" s="21">
-        <v>1</v>
-      </c>
-      <c r="D59" s="21">
-        <v>0</v>
-      </c>
-      <c r="E59" s="21">
-        <v>3600400</v>
+      <c r="A59" s="25">
+        <v>59140001</v>
+      </c>
+      <c r="B59" s="24">
+        <v>5914</v>
+      </c>
+      <c r="C59" s="24">
+        <v>1</v>
+      </c>
+      <c r="D59" s="24">
+        <v>0</v>
+      </c>
+      <c r="E59" s="24">
+        <v>3592400</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>257</v>
+        <v>542</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="13"/>
-      <c r="J59" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="K59" s="21">
-        <v>1</v>
-      </c>
-      <c r="L59" s="21">
-        <v>1</v>
-      </c>
-      <c r="M59" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="N59" s="21">
+      <c r="J59" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="K59" s="24">
         <v>2</v>
       </c>
-      <c r="O59" s="21">
-        <v>15000</v>
-      </c>
-      <c r="P59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q59" s="21">
-        <v>1</v>
-      </c>
-      <c r="R59" s="21">
-        <v>0</v>
-      </c>
-      <c r="S59" s="21">
-        <v>0</v>
-      </c>
-      <c r="T59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="U59" s="21">
+      <c r="L59" s="24">
+        <v>0</v>
+      </c>
+      <c r="M59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="N59" s="24">
+        <v>1</v>
+      </c>
+      <c r="O59" s="24">
+        <v>0</v>
+      </c>
+      <c r="P59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q59" s="24">
+        <v>1</v>
+      </c>
+      <c r="R59" s="24">
+        <v>0</v>
+      </c>
+      <c r="S59" s="24">
+        <v>0</v>
+      </c>
+      <c r="T59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="U59" s="24">
         <v>-1</v>
       </c>
-      <c r="V59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="W59" s="21">
+      <c r="V59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="W59" s="24">
         <v>10000</v>
       </c>
-      <c r="X59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y59" s="21">
-        <v>1</v>
-      </c>
-      <c r="Z59" s="21">
-        <v>1</v>
-      </c>
-      <c r="AA59" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB59" s="21">
-        <v>1</v>
-      </c>
-      <c r="AC59" s="21">
+      <c r="X59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y59" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z59" s="24">
+        <v>1</v>
+      </c>
+      <c r="AA59" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB59" s="24">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A60" s="21">
-        <v>60030001</v>
+        <v>60010001</v>
       </c>
       <c r="B60" s="21">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="C60" s="21">
         <v>1</v>
@@ -7711,10 +7946,10 @@
         <v>0</v>
       </c>
       <c r="E60" s="21">
-        <v>3600700</v>
+        <v>3600200</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>253</v>
@@ -7722,7 +7957,7 @@
       <c r="H60" s="13"/>
       <c r="I60" s="13"/>
       <c r="J60" s="21" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="K60" s="21">
         <v>1</v>
@@ -7731,7 +7966,7 @@
         <v>8</v>
       </c>
       <c r="M60" s="21" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="N60" s="21">
         <v>2</v>
@@ -7740,7 +7975,7 @@
         <v>10000</v>
       </c>
       <c r="P60" s="21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Q60" s="21">
         <v>1</v>
@@ -7784,10 +8019,10 @@
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A61" s="21">
-        <v>60040001</v>
+        <v>60020001</v>
       </c>
       <c r="B61" s="21">
-        <v>6004</v>
+        <v>6002</v>
       </c>
       <c r="C61" s="21">
         <v>1</v>
@@ -7796,10 +8031,10 @@
         <v>0</v>
       </c>
       <c r="E61" s="21">
-        <v>3601000</v>
+        <v>3600400</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>253</v>
@@ -7807,31 +8042,31 @@
       <c r="H61" s="13"/>
       <c r="I61" s="13"/>
       <c r="J61" s="21" t="s">
-        <v>43</v>
+        <v>263</v>
       </c>
       <c r="K61" s="21">
         <v>1</v>
       </c>
       <c r="L61" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" s="21" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="N61" s="21">
         <v>2</v>
       </c>
       <c r="O61" s="21">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="P61" s="21" t="s">
-        <v>268</v>
+        <v>43</v>
       </c>
       <c r="Q61" s="21">
         <v>1</v>
       </c>
       <c r="R61" s="21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" s="21">
         <v>0</v>
@@ -7840,7 +8075,7 @@
         <v>43</v>
       </c>
       <c r="U61" s="21">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V61" s="21" t="s">
         <v>43</v>
@@ -7869,10 +8104,10 @@
     </row>
     <row r="62" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A62" s="21">
-        <v>60050001</v>
+        <v>60030001</v>
       </c>
       <c r="B62" s="21">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="C62" s="21">
         <v>1</v>
@@ -7881,10 +8116,10 @@
         <v>0</v>
       </c>
       <c r="E62" s="21">
-        <v>3541600</v>
+        <v>3600700</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>316</v>
+        <v>258</v>
       </c>
       <c r="G62" s="13" t="s">
         <v>253</v>
@@ -7892,31 +8127,31 @@
       <c r="H62" s="13"/>
       <c r="I62" s="13"/>
       <c r="J62" s="21" t="s">
-        <v>118</v>
+        <v>295</v>
       </c>
       <c r="K62" s="21">
+        <v>1</v>
+      </c>
+      <c r="L62" s="21">
+        <v>8</v>
+      </c>
+      <c r="M62" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="N62" s="21">
         <v>2</v>
       </c>
-      <c r="L62" s="21">
-        <v>-2000</v>
-      </c>
-      <c r="M62" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N62" s="21">
-        <v>1</v>
-      </c>
       <c r="O62" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P62" s="21" t="s">
-        <v>43</v>
+        <v>266</v>
       </c>
       <c r="Q62" s="21">
         <v>1</v>
       </c>
       <c r="R62" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="21">
         <v>0</v>
@@ -7925,7 +8160,7 @@
         <v>43</v>
       </c>
       <c r="U62" s="21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V62" s="21" t="s">
         <v>43</v>
@@ -7954,10 +8189,10 @@
     </row>
     <row r="63" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A63" s="21">
-        <v>60060001</v>
+        <v>60040001</v>
       </c>
       <c r="B63" s="21">
-        <v>6006</v>
+        <v>6004</v>
       </c>
       <c r="C63" s="21">
         <v>1</v>
@@ -7966,10 +8201,10 @@
         <v>0</v>
       </c>
       <c r="E63" s="21">
-        <v>3541800</v>
+        <v>3601000</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="G63" s="13" t="s">
         <v>253</v>
@@ -7977,31 +8212,31 @@
       <c r="H63" s="13"/>
       <c r="I63" s="13"/>
       <c r="J63" s="21" t="s">
-        <v>120</v>
+        <v>43</v>
       </c>
       <c r="K63" s="21">
+        <v>1</v>
+      </c>
+      <c r="L63" s="21">
+        <v>0</v>
+      </c>
+      <c r="M63" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="N63" s="21">
         <v>2</v>
       </c>
-      <c r="L63" s="21">
-        <v>2500</v>
-      </c>
-      <c r="M63" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="N63" s="21">
-        <v>1</v>
-      </c>
       <c r="O63" s="21">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P63" s="21" t="s">
-        <v>43</v>
+        <v>268</v>
       </c>
       <c r="Q63" s="21">
         <v>1</v>
       </c>
       <c r="R63" s="21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" s="21">
         <v>0</v>
@@ -8010,7 +8245,7 @@
         <v>43</v>
       </c>
       <c r="U63" s="21">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="V63" s="21" t="s">
         <v>43</v>
@@ -8039,10 +8274,10 @@
     </row>
     <row r="64" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A64" s="21">
-        <v>60070001</v>
+        <v>60050001</v>
       </c>
       <c r="B64" s="21">
-        <v>6007</v>
+        <v>6005</v>
       </c>
       <c r="C64" s="21">
         <v>1</v>
@@ -8051,10 +8286,10 @@
         <v>0</v>
       </c>
       <c r="E64" s="21">
-        <v>3601300</v>
+        <v>3541600</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G64" s="13" t="s">
         <v>253</v>
@@ -8062,25 +8297,25 @@
       <c r="H64" s="13"/>
       <c r="I64" s="13"/>
       <c r="J64" s="21" t="s">
-        <v>269</v>
+        <v>118</v>
       </c>
       <c r="K64" s="21">
         <v>2</v>
       </c>
       <c r="L64" s="21">
-        <v>10000</v>
+        <v>-2000</v>
       </c>
       <c r="M64" s="21" t="s">
-        <v>270</v>
+        <v>43</v>
       </c>
       <c r="N64" s="21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O64" s="21">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P64" s="21" t="s">
-        <v>271</v>
+        <v>43</v>
       </c>
       <c r="Q64" s="21">
         <v>1</v>
@@ -8124,10 +8359,10 @@
     </row>
     <row r="65" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A65" s="21">
-        <v>60080001</v>
+        <v>60060001</v>
       </c>
       <c r="B65" s="21">
-        <v>6008</v>
+        <v>6006</v>
       </c>
       <c r="C65" s="21">
         <v>1</v>
@@ -8136,10 +8371,10 @@
         <v>0</v>
       </c>
       <c r="E65" s="21">
-        <v>3541600</v>
+        <v>3541800</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>533</v>
+        <v>316</v>
       </c>
       <c r="G65" s="13" t="s">
         <v>253</v>
@@ -8147,13 +8382,13 @@
       <c r="H65" s="13"/>
       <c r="I65" s="13"/>
       <c r="J65" s="21" t="s">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="K65" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" s="21">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="M65" s="21" t="s">
         <v>43</v>
@@ -8173,14 +8408,14 @@
       <c r="R65" s="21">
         <v>0</v>
       </c>
-      <c r="S65" s="26" t="s">
-        <v>534</v>
+      <c r="S65" s="21">
+        <v>0</v>
       </c>
       <c r="T65" s="21" t="s">
         <v>43</v>
       </c>
       <c r="U65" s="21">
-        <v>-1</v>
+        <v>1000</v>
       </c>
       <c r="V65" s="21" t="s">
         <v>43</v>
@@ -8204,185 +8439,185 @@
         <v>1</v>
       </c>
       <c r="AC65" s="21">
-        <v>1000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A66" s="22">
-        <v>61010001</v>
-      </c>
-      <c r="B66" s="22">
-        <v>6101</v>
-      </c>
-      <c r="C66" s="22">
-        <v>1</v>
-      </c>
-      <c r="D66" s="22">
-        <v>0</v>
-      </c>
-      <c r="E66" s="22">
-        <v>3610300</v>
+      <c r="A66" s="21">
+        <v>60070001</v>
+      </c>
+      <c r="B66" s="21">
+        <v>6007</v>
+      </c>
+      <c r="C66" s="21">
+        <v>1</v>
+      </c>
+      <c r="D66" s="21">
+        <v>0</v>
+      </c>
+      <c r="E66" s="21">
+        <v>3601300</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="13"/>
-      <c r="J66" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="K66" s="22">
-        <v>1</v>
-      </c>
-      <c r="L66" s="22">
-        <v>8</v>
-      </c>
-      <c r="M66" s="22" t="s">
-        <v>273</v>
-      </c>
-      <c r="N66" s="22">
+      <c r="J66" s="21" t="s">
+        <v>269</v>
+      </c>
+      <c r="K66" s="21">
         <v>2</v>
       </c>
-      <c r="O66" s="22">
+      <c r="L66" s="21">
         <v>10000</v>
       </c>
-      <c r="P66" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q66" s="22">
-        <v>1</v>
-      </c>
-      <c r="R66" s="22">
-        <v>1</v>
-      </c>
-      <c r="S66" s="22">
-        <v>0</v>
-      </c>
-      <c r="T66" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U66" s="22">
-        <v>0</v>
-      </c>
-      <c r="V66" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W66" s="22">
+      <c r="M66" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="N66" s="21">
+        <v>2</v>
+      </c>
+      <c r="O66" s="21">
+        <v>2000</v>
+      </c>
+      <c r="P66" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q66" s="21">
+        <v>1</v>
+      </c>
+      <c r="R66" s="21">
+        <v>0</v>
+      </c>
+      <c r="S66" s="21">
+        <v>0</v>
+      </c>
+      <c r="T66" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U66" s="21">
+        <v>1000</v>
+      </c>
+      <c r="V66" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" s="21">
         <v>10000</v>
       </c>
-      <c r="X66" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y66" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z66" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA66" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB66" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC66" s="22">
+      <c r="X66" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y66" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA66" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB66" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC66" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A67" s="22">
-        <v>61020001</v>
-      </c>
-      <c r="B67" s="22">
-        <v>6102</v>
-      </c>
-      <c r="C67" s="22">
-        <v>1</v>
-      </c>
-      <c r="D67" s="22">
-        <v>0</v>
-      </c>
-      <c r="E67" s="22">
-        <v>3610500</v>
+      <c r="A67" s="21">
+        <v>60080001</v>
+      </c>
+      <c r="B67" s="21">
+        <v>6008</v>
+      </c>
+      <c r="C67" s="21">
+        <v>1</v>
+      </c>
+      <c r="D67" s="21">
+        <v>0</v>
+      </c>
+      <c r="E67" s="21">
+        <v>3541600</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>298</v>
+        <v>532</v>
       </c>
       <c r="G67" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="13"/>
-      <c r="J67" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="K67" s="22">
-        <v>2</v>
-      </c>
-      <c r="L67" s="22">
+      <c r="J67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="K67" s="21">
+        <v>1</v>
+      </c>
+      <c r="L67" s="21">
+        <v>0</v>
+      </c>
+      <c r="M67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N67" s="21">
+        <v>1</v>
+      </c>
+      <c r="O67" s="21">
+        <v>0</v>
+      </c>
+      <c r="P67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q67" s="21">
+        <v>1</v>
+      </c>
+      <c r="R67" s="21">
+        <v>0</v>
+      </c>
+      <c r="S67" s="26" t="s">
+        <v>533</v>
+      </c>
+      <c r="T67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U67" s="21">
+        <v>-1</v>
+      </c>
+      <c r="V67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W67" s="21">
         <v>10000</v>
       </c>
-      <c r="M67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="N67" s="22">
-        <v>1</v>
-      </c>
-      <c r="O67" s="22">
-        <v>0</v>
-      </c>
-      <c r="P67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q67" s="22">
-        <v>1</v>
-      </c>
-      <c r="R67" s="22">
-        <v>0</v>
-      </c>
-      <c r="S67" s="22">
-        <v>0</v>
-      </c>
-      <c r="T67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="U67" s="22">
-        <v>-1</v>
-      </c>
-      <c r="V67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="W67" s="22">
-        <v>10000</v>
-      </c>
-      <c r="X67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y67" s="22">
-        <v>1</v>
-      </c>
-      <c r="Z67" s="22">
-        <v>1</v>
-      </c>
-      <c r="AA67" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB67" s="22">
-        <v>1</v>
-      </c>
-      <c r="AC67" s="22">
-        <v>0</v>
+      <c r="X67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y67" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z67" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA67" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB67" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC67" s="21">
+        <v>1000</v>
       </c>
     </row>
     <row r="68" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A68" s="22">
-        <v>61030001</v>
+        <v>61010001</v>
       </c>
       <c r="B68" s="22">
-        <v>6103</v>
+        <v>6101</v>
       </c>
       <c r="C68" s="22">
         <v>1</v>
@@ -8391,10 +8626,10 @@
         <v>0</v>
       </c>
       <c r="E68" s="22">
-        <v>3610700</v>
+        <v>3610300</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="G68" s="13" t="s">
         <v>254</v>
@@ -8402,16 +8637,16 @@
       <c r="H68" s="13"/>
       <c r="I68" s="13"/>
       <c r="J68" s="22" t="s">
-        <v>43</v>
+        <v>272</v>
       </c>
       <c r="K68" s="22">
         <v>1</v>
       </c>
       <c r="L68" s="22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M68" s="22" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="N68" s="22">
         <v>2</v>
@@ -8420,7 +8655,7 @@
         <v>10000</v>
       </c>
       <c r="P68" s="22" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="Q68" s="22">
         <v>1</v>
@@ -8464,10 +8699,10 @@
     </row>
     <row r="69" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A69" s="22">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="B69" s="22">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="C69" s="22">
         <v>1</v>
@@ -8476,10 +8711,10 @@
         <v>0</v>
       </c>
       <c r="E69" s="22">
-        <v>3541400</v>
+        <v>3610500</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>255</v>
+        <v>297</v>
       </c>
       <c r="G69" s="13" t="s">
         <v>254</v>
@@ -8487,13 +8722,13 @@
       <c r="H69" s="13"/>
       <c r="I69" s="13"/>
       <c r="J69" s="22" t="s">
-        <v>117</v>
+        <v>275</v>
       </c>
       <c r="K69" s="22">
         <v>2</v>
       </c>
       <c r="L69" s="22">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="M69" s="22" t="s">
         <v>43</v>
@@ -8549,10 +8784,10 @@
     </row>
     <row r="70" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A70" s="22">
-        <v>61050001</v>
+        <v>61030001</v>
       </c>
       <c r="B70" s="22">
-        <v>6105</v>
+        <v>6103</v>
       </c>
       <c r="C70" s="22">
         <v>1</v>
@@ -8561,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="22">
-        <v>3610900</v>
+        <v>3610700</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G70" s="13" t="s">
         <v>254</v>
@@ -8572,31 +8807,31 @@
       <c r="H70" s="13"/>
       <c r="I70" s="13"/>
       <c r="J70" s="22" t="s">
-        <v>304</v>
+        <v>43</v>
       </c>
       <c r="K70" s="22">
         <v>1</v>
       </c>
       <c r="L70" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="22" t="s">
-        <v>43</v>
+        <v>276</v>
       </c>
       <c r="N70" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O70" s="22">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="P70" s="22" t="s">
-        <v>43</v>
+        <v>277</v>
       </c>
       <c r="Q70" s="22">
         <v>1</v>
       </c>
       <c r="R70" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" s="22">
         <v>0</v>
@@ -8605,7 +8840,7 @@
         <v>43</v>
       </c>
       <c r="U70" s="22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V70" s="22" t="s">
         <v>43</v>
@@ -8634,10 +8869,10 @@
     </row>
     <row r="71" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A71" s="22">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B71" s="22">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="C71" s="22">
         <v>1</v>
@@ -8646,10 +8881,10 @@
         <v>0</v>
       </c>
       <c r="E71" s="22">
-        <v>3611100</v>
+        <v>3541400</v>
       </c>
       <c r="F71" s="13" t="s">
-        <v>370</v>
+        <v>255</v>
       </c>
       <c r="G71" s="13" t="s">
         <v>254</v>
@@ -8657,13 +8892,13 @@
       <c r="H71" s="13"/>
       <c r="I71" s="13"/>
       <c r="J71" s="22" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="K71" s="22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="22">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="M71" s="22" t="s">
         <v>43</v>
@@ -8719,10 +8954,10 @@
     </row>
     <row r="72" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A72" s="22">
-        <v>61070001</v>
+        <v>61050001</v>
       </c>
       <c r="B72" s="22">
-        <v>6107</v>
+        <v>6105</v>
       </c>
       <c r="C72" s="22">
         <v>1</v>
@@ -8731,10 +8966,10 @@
         <v>0</v>
       </c>
       <c r="E72" s="22">
-        <v>3611300</v>
+        <v>3610900</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="G72" s="13" t="s">
         <v>254</v>
@@ -8742,13 +8977,13 @@
       <c r="H72" s="13"/>
       <c r="I72" s="13"/>
       <c r="J72" s="22" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="K72" s="22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L72" s="22">
-        <v>300000</v>
+        <v>1</v>
       </c>
       <c r="M72" s="22" t="s">
         <v>43</v>
@@ -8760,13 +8995,13 @@
         <v>0</v>
       </c>
       <c r="P72" s="22" t="s">
-        <v>306</v>
+        <v>43</v>
       </c>
       <c r="Q72" s="22">
         <v>1</v>
       </c>
       <c r="R72" s="22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S72" s="22">
         <v>0</v>
@@ -8804,10 +9039,10 @@
     </row>
     <row r="73" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A73" s="22">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B73" s="22">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="C73" s="22">
         <v>1</v>
@@ -8816,10 +9051,10 @@
         <v>0</v>
       </c>
       <c r="E73" s="22">
-        <v>3611500</v>
+        <v>3611100</v>
       </c>
       <c r="F73" s="13" t="s">
-        <v>300</v>
+        <v>369</v>
       </c>
       <c r="G73" s="13" t="s">
         <v>254</v>
@@ -8836,22 +9071,22 @@
         <v>0</v>
       </c>
       <c r="M73" s="22" t="s">
-        <v>308</v>
+        <v>43</v>
       </c>
       <c r="N73" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" s="22">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="P73" s="22" t="s">
-        <v>309</v>
+        <v>43</v>
       </c>
       <c r="Q73" s="22">
         <v>1</v>
       </c>
       <c r="R73" s="22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73" s="22">
         <v>0</v>
@@ -8860,7 +9095,7 @@
         <v>43</v>
       </c>
       <c r="U73" s="22">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V73" s="22" t="s">
         <v>43</v>
@@ -8889,10 +9124,10 @@
     </row>
     <row r="74" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A74" s="22">
-        <v>61090001</v>
+        <v>61070001</v>
       </c>
       <c r="B74" s="22">
-        <v>6109</v>
+        <v>6107</v>
       </c>
       <c r="C74" s="22">
         <v>1</v>
@@ -8901,10 +9136,10 @@
         <v>0</v>
       </c>
       <c r="E74" s="22">
-        <v>3611700</v>
+        <v>3611300</v>
       </c>
       <c r="F74" s="13" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G74" s="13" t="s">
         <v>254</v>
@@ -8912,7 +9147,7 @@
       <c r="H74" s="13"/>
       <c r="I74" s="13"/>
       <c r="J74" s="22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K74" s="22">
         <v>3</v>
@@ -8930,13 +9165,13 @@
         <v>0</v>
       </c>
       <c r="P74" s="22" t="s">
-        <v>43</v>
+        <v>305</v>
       </c>
       <c r="Q74" s="22">
         <v>1</v>
       </c>
       <c r="R74" s="22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S74" s="22">
         <v>0</v>
@@ -8974,10 +9209,10 @@
     </row>
     <row r="75" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A75" s="22">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B75" s="22">
-        <v>6110</v>
+        <v>6108</v>
       </c>
       <c r="C75" s="22">
         <v>1</v>
@@ -8986,10 +9221,10 @@
         <v>0</v>
       </c>
       <c r="E75" s="22">
-        <v>3590800</v>
+        <v>3611500</v>
       </c>
       <c r="F75" s="13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G75" s="13" t="s">
         <v>254</v>
@@ -9006,7 +9241,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="22" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="N75" s="22">
         <v>2</v>
@@ -9015,7 +9250,7 @@
         <v>10000</v>
       </c>
       <c r="P75" s="22" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="Q75" s="22">
         <v>1</v>
@@ -9057,8 +9292,1722 @@
         <v>0</v>
       </c>
     </row>
+    <row r="76" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A76" s="22">
+        <v>61090001</v>
+      </c>
+      <c r="B76" s="22">
+        <v>6109</v>
+      </c>
+      <c r="C76" s="22">
+        <v>1</v>
+      </c>
+      <c r="D76" s="22">
+        <v>0</v>
+      </c>
+      <c r="E76" s="22">
+        <v>3611700</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>319</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H76" s="13"/>
+      <c r="I76" s="13"/>
+      <c r="J76" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="K76" s="22">
+        <v>3</v>
+      </c>
+      <c r="L76" s="22">
+        <v>300000</v>
+      </c>
+      <c r="M76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="N76" s="22">
+        <v>1</v>
+      </c>
+      <c r="O76" s="22">
+        <v>0</v>
+      </c>
+      <c r="P76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q76" s="22">
+        <v>1</v>
+      </c>
+      <c r="R76" s="22">
+        <v>0</v>
+      </c>
+      <c r="S76" s="22">
+        <v>0</v>
+      </c>
+      <c r="T76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U76" s="22">
+        <v>-1</v>
+      </c>
+      <c r="V76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W76" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y76" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z76" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA76" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB76" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC76" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A77" s="22">
+        <v>61100001</v>
+      </c>
+      <c r="B77" s="22">
+        <v>6110</v>
+      </c>
+      <c r="C77" s="22">
+        <v>1</v>
+      </c>
+      <c r="D77" s="22">
+        <v>0</v>
+      </c>
+      <c r="E77" s="22">
+        <v>3590800</v>
+      </c>
+      <c r="F77" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="G77" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K77" s="22">
+        <v>1</v>
+      </c>
+      <c r="L77" s="22">
+        <v>0</v>
+      </c>
+      <c r="M77" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="N77" s="22">
+        <v>2</v>
+      </c>
+      <c r="O77" s="22">
+        <v>10000</v>
+      </c>
+      <c r="P77" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q77" s="22">
+        <v>1</v>
+      </c>
+      <c r="R77" s="22">
+        <v>1</v>
+      </c>
+      <c r="S77" s="22">
+        <v>0</v>
+      </c>
+      <c r="T77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="U77" s="22">
+        <v>0</v>
+      </c>
+      <c r="V77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="W77" s="22">
+        <v>10000</v>
+      </c>
+      <c r="X77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y77" s="22">
+        <v>1</v>
+      </c>
+      <c r="Z77" s="22">
+        <v>1</v>
+      </c>
+      <c r="AA77" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB77" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC77" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A78" s="21">
+        <v>855001001</v>
+      </c>
+      <c r="B78" s="21">
+        <v>7001</v>
+      </c>
+      <c r="C78" s="21">
+        <v>1</v>
+      </c>
+      <c r="D78" s="21">
+        <v>0</v>
+      </c>
+      <c r="E78" s="21">
+        <v>3541600</v>
+      </c>
+      <c r="F78" s="13" t="s">
+        <v>534</v>
+      </c>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="K78" s="21">
+        <v>1</v>
+      </c>
+      <c r="L78" s="21">
+        <v>0</v>
+      </c>
+      <c r="M78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N78" s="21">
+        <v>1</v>
+      </c>
+      <c r="O78" s="21">
+        <v>0</v>
+      </c>
+      <c r="P78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q78" s="21">
+        <v>1</v>
+      </c>
+      <c r="R78" s="21">
+        <v>0</v>
+      </c>
+      <c r="S78" s="26" t="s">
+        <v>535</v>
+      </c>
+      <c r="T78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="U78" s="21">
+        <v>-1</v>
+      </c>
+      <c r="V78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W78" s="21">
+        <v>10000</v>
+      </c>
+      <c r="X78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y78" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z78" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA78" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB78" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC78" s="21">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A79" s="21">
+        <v>855001002</v>
+      </c>
+      <c r="B79" s="21">
+        <v>7002</v>
+      </c>
+      <c r="C79" s="21">
+        <v>1</v>
+      </c>
+      <c r="D79" s="21">
+        <v>0</v>
+      </c>
+      <c r="E79" s="21">
+        <v>3590400</v>
+      </c>
+      <c r="F79" s="13" t="s">
+        <v>536</v>
+      </c>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
+      <c r="I79" s="13"/>
+      <c r="J79" s="21" t="s">
+        <v>281</v>
+      </c>
+      <c r="K79" s="21">
+        <v>3</v>
+      </c>
+      <c r="L79" s="21">
+        <v>200000</v>
+      </c>
+      <c r="M79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="N79" s="21">
+        <v>1</v>
+      </c>
+      <c r="O79" s="21">
+        <v>0</v>
+      </c>
+      <c r="P79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q79" s="21">
+        <v>1</v>
+      </c>
+      <c r="R79" s="21">
+        <v>0</v>
+      </c>
+      <c r="S79" s="26">
+        <v>0</v>
+      </c>
+      <c r="T79" s="21" t="s">
+        <v>537</v>
+      </c>
+      <c r="U79" s="21">
+        <v>4000</v>
+      </c>
+      <c r="V79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="W79" s="21">
+        <v>10000</v>
+      </c>
+      <c r="X79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y79" s="21">
+        <v>1</v>
+      </c>
+      <c r="Z79" s="21">
+        <v>1</v>
+      </c>
+      <c r="AA79" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB79" s="21">
+        <v>1</v>
+      </c>
+      <c r="AC79" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A80" s="27">
+        <v>85000100</v>
+      </c>
+      <c r="B80" s="27">
+        <v>7003</v>
+      </c>
+      <c r="C80" s="28">
+        <v>1</v>
+      </c>
+      <c r="D80" s="28">
+        <v>0</v>
+      </c>
+      <c r="E80" s="27">
+        <v>5000200</v>
+      </c>
+      <c r="F80" s="27" t="s">
+        <v>539</v>
+      </c>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="27"/>
+      <c r="J80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K80" s="27">
+        <v>1</v>
+      </c>
+      <c r="L80" s="27">
+        <v>0</v>
+      </c>
+      <c r="M80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N80" s="27">
+        <v>1</v>
+      </c>
+      <c r="O80" s="27">
+        <v>0</v>
+      </c>
+      <c r="P80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q80" s="27">
+        <v>1</v>
+      </c>
+      <c r="R80" s="27">
+        <v>0</v>
+      </c>
+      <c r="S80" s="28">
+        <v>95000101</v>
+      </c>
+      <c r="T80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U80" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W80" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y80" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z80" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA80" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB80" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC80" s="27">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="81" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A81" s="27">
+        <v>85000300</v>
+      </c>
+      <c r="B81" s="27">
+        <v>7004</v>
+      </c>
+      <c r="C81" s="28">
+        <v>1</v>
+      </c>
+      <c r="D81" s="28">
+        <v>0</v>
+      </c>
+      <c r="E81" s="27">
+        <v>5000400</v>
+      </c>
+      <c r="F81" s="27" t="s">
+        <v>552</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="H81" s="27"/>
+      <c r="I81" s="27" t="s">
+        <v>566</v>
+      </c>
+      <c r="J81" s="27" t="s">
+        <v>555</v>
+      </c>
+      <c r="K81" s="27">
+        <v>1</v>
+      </c>
+      <c r="L81" s="27">
+        <v>0</v>
+      </c>
+      <c r="M81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N81" s="27">
+        <v>1</v>
+      </c>
+      <c r="O81" s="27">
+        <v>0</v>
+      </c>
+      <c r="P81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q81" s="27">
+        <v>1</v>
+      </c>
+      <c r="R81" s="27">
+        <v>0</v>
+      </c>
+      <c r="S81" s="28">
+        <v>0</v>
+      </c>
+      <c r="T81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U81" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W81" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y81" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z81" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA81" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB81" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC81" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A82" s="27">
+        <v>85000500</v>
+      </c>
+      <c r="B82" s="27">
+        <v>7005</v>
+      </c>
+      <c r="C82" s="28">
+        <v>1</v>
+      </c>
+      <c r="D82" s="28">
+        <v>0</v>
+      </c>
+      <c r="E82" s="27">
+        <v>5000600</v>
+      </c>
+      <c r="F82" s="27" t="s">
+        <v>553</v>
+      </c>
+      <c r="G82" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27" t="s">
+        <v>567</v>
+      </c>
+      <c r="J82" s="27" t="s">
+        <v>556</v>
+      </c>
+      <c r="K82" s="27">
+        <v>2</v>
+      </c>
+      <c r="L82" s="27">
+        <v>0</v>
+      </c>
+      <c r="M82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N82" s="27">
+        <v>1</v>
+      </c>
+      <c r="O82" s="27">
+        <v>0</v>
+      </c>
+      <c r="P82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q82" s="27">
+        <v>1</v>
+      </c>
+      <c r="R82" s="27">
+        <v>0</v>
+      </c>
+      <c r="S82" s="28">
+        <v>0</v>
+      </c>
+      <c r="T82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U82" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W82" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y82" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z82" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA82" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB82" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC82" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A83" s="27">
+        <v>85000700</v>
+      </c>
+      <c r="B83" s="27">
+        <v>7006</v>
+      </c>
+      <c r="C83" s="28">
+        <v>1</v>
+      </c>
+      <c r="D83" s="28">
+        <v>0</v>
+      </c>
+      <c r="E83" s="27">
+        <v>5000800</v>
+      </c>
+      <c r="F83" s="27" t="s">
+        <v>554</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="H83" s="27"/>
+      <c r="I83" s="27" t="s">
+        <v>586</v>
+      </c>
+      <c r="J83" s="27" t="s">
+        <v>557</v>
+      </c>
+      <c r="K83" s="27">
+        <v>1</v>
+      </c>
+      <c r="L83" s="27">
+        <v>0</v>
+      </c>
+      <c r="M83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N83" s="27">
+        <v>1</v>
+      </c>
+      <c r="O83" s="27">
+        <v>0</v>
+      </c>
+      <c r="P83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q83" s="27">
+        <v>1</v>
+      </c>
+      <c r="R83" s="27">
+        <v>0</v>
+      </c>
+      <c r="S83" s="28">
+        <v>0</v>
+      </c>
+      <c r="T83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U83" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W83" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y83" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z83" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA83" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB83" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC83" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A84" s="27">
+        <v>85000900</v>
+      </c>
+      <c r="B84" s="27">
+        <v>7007</v>
+      </c>
+      <c r="C84" s="28">
+        <v>1</v>
+      </c>
+      <c r="D84" s="28">
+        <v>0</v>
+      </c>
+      <c r="E84" s="27">
+        <v>5001000</v>
+      </c>
+      <c r="F84" s="27" t="s">
+        <v>560</v>
+      </c>
+      <c r="G84" s="13" t="s">
+        <v>562</v>
+      </c>
+      <c r="H84" s="27"/>
+      <c r="I84" s="27" t="s">
+        <v>568</v>
+      </c>
+      <c r="J84" s="27" t="s">
+        <v>558</v>
+      </c>
+      <c r="K84" s="27">
+        <v>1</v>
+      </c>
+      <c r="L84" s="27">
+        <v>0</v>
+      </c>
+      <c r="M84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N84" s="27">
+        <v>1</v>
+      </c>
+      <c r="O84" s="27">
+        <v>0</v>
+      </c>
+      <c r="P84" s="27" t="s">
+        <v>559</v>
+      </c>
+      <c r="Q84" s="27">
+        <v>1</v>
+      </c>
+      <c r="R84" s="27">
+        <v>500</v>
+      </c>
+      <c r="S84" s="28">
+        <v>0</v>
+      </c>
+      <c r="T84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U84" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W84" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y84" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z84" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA84" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB84" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC84" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A85" s="27">
+        <v>85001100</v>
+      </c>
+      <c r="B85" s="27">
+        <v>7008</v>
+      </c>
+      <c r="C85" s="28">
+        <v>1</v>
+      </c>
+      <c r="D85" s="28">
+        <v>0</v>
+      </c>
+      <c r="E85" s="27">
+        <v>5001200</v>
+      </c>
+      <c r="F85" s="27" t="s">
+        <v>561</v>
+      </c>
+      <c r="G85" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H85" s="27"/>
+      <c r="I85" s="27" t="s">
+        <v>569</v>
+      </c>
+      <c r="J85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K85" s="27">
+        <v>1</v>
+      </c>
+      <c r="L85" s="27">
+        <v>0</v>
+      </c>
+      <c r="M85" s="27" t="s">
+        <v>563</v>
+      </c>
+      <c r="N85" s="27">
+        <v>2</v>
+      </c>
+      <c r="O85" s="27">
+        <v>0</v>
+      </c>
+      <c r="P85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q85" s="27">
+        <v>1</v>
+      </c>
+      <c r="R85" s="27">
+        <v>0</v>
+      </c>
+      <c r="S85" s="28">
+        <v>0</v>
+      </c>
+      <c r="T85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U85" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W85" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y85" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA85" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB85" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC85" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A86" s="27">
+        <v>85001300</v>
+      </c>
+      <c r="B86" s="27">
+        <v>7009</v>
+      </c>
+      <c r="C86" s="28">
+        <v>1</v>
+      </c>
+      <c r="D86" s="28">
+        <v>0</v>
+      </c>
+      <c r="E86" s="27">
+        <v>5001400</v>
+      </c>
+      <c r="F86" s="27" t="s">
+        <v>564</v>
+      </c>
+      <c r="G86" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="H86" s="27"/>
+      <c r="I86" s="27" t="s">
+        <v>591</v>
+      </c>
+      <c r="J86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K86" s="27">
+        <v>1</v>
+      </c>
+      <c r="L86" s="27">
+        <v>0</v>
+      </c>
+      <c r="M86" s="27" t="s">
+        <v>565</v>
+      </c>
+      <c r="N86" s="27">
+        <v>2</v>
+      </c>
+      <c r="O86" s="27">
+        <v>-6000</v>
+      </c>
+      <c r="P86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q86" s="27">
+        <v>1</v>
+      </c>
+      <c r="R86" s="27">
+        <v>0</v>
+      </c>
+      <c r="S86" s="28">
+        <v>0</v>
+      </c>
+      <c r="T86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U86" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W86" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y86" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z86" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA86" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB86" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC86" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A87" s="27">
+        <v>85100100</v>
+      </c>
+      <c r="B87" s="27">
+        <v>7010</v>
+      </c>
+      <c r="C87" s="28">
+        <v>1</v>
+      </c>
+      <c r="D87" s="28">
+        <v>0</v>
+      </c>
+      <c r="E87" s="27">
+        <v>5000200</v>
+      </c>
+      <c r="F87" s="27" t="s">
+        <v>540</v>
+      </c>
+      <c r="G87" s="27"/>
+      <c r="H87" s="27"/>
+      <c r="I87" s="27"/>
+      <c r="J87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K87" s="27">
+        <v>1</v>
+      </c>
+      <c r="L87" s="27">
+        <v>0</v>
+      </c>
+      <c r="M87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N87" s="27">
+        <v>1</v>
+      </c>
+      <c r="O87" s="27">
+        <v>0</v>
+      </c>
+      <c r="P87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q87" s="27">
+        <v>1</v>
+      </c>
+      <c r="R87" s="27">
+        <v>0</v>
+      </c>
+      <c r="S87" s="28">
+        <v>95100101</v>
+      </c>
+      <c r="T87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U87" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W87" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y87" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z87" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA87" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB87" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC87" s="27">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="88" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A88" s="27">
+        <v>85100300</v>
+      </c>
+      <c r="B88" s="27">
+        <v>7011</v>
+      </c>
+      <c r="C88" s="28">
+        <v>1</v>
+      </c>
+      <c r="D88" s="28">
+        <v>0</v>
+      </c>
+      <c r="E88" s="27">
+        <v>5100400</v>
+      </c>
+      <c r="F88" s="27" t="s">
+        <v>574</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="H88" s="27"/>
+      <c r="I88" s="27" t="s">
+        <v>587</v>
+      </c>
+      <c r="J88" s="27" t="s">
+        <v>579</v>
+      </c>
+      <c r="K88" s="27">
+        <v>1</v>
+      </c>
+      <c r="L88" s="27">
+        <v>0</v>
+      </c>
+      <c r="M88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N88" s="27">
+        <v>1</v>
+      </c>
+      <c r="O88" s="27">
+        <v>0</v>
+      </c>
+      <c r="P88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q88" s="27">
+        <v>1</v>
+      </c>
+      <c r="R88" s="27">
+        <v>0</v>
+      </c>
+      <c r="S88" s="28">
+        <v>0</v>
+      </c>
+      <c r="T88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U88" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W88" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y88" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z88" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA88" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB88" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC88" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A89" s="27">
+        <v>85100500</v>
+      </c>
+      <c r="B89" s="27">
+        <v>7012</v>
+      </c>
+      <c r="C89" s="28">
+        <v>1</v>
+      </c>
+      <c r="D89" s="28">
+        <v>0</v>
+      </c>
+      <c r="E89" s="27">
+        <v>5100600</v>
+      </c>
+      <c r="F89" s="27" t="s">
+        <v>575</v>
+      </c>
+      <c r="G89" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H89" s="27"/>
+      <c r="I89" s="27" t="s">
+        <v>584</v>
+      </c>
+      <c r="J89" s="27" t="s">
+        <v>580</v>
+      </c>
+      <c r="K89" s="27">
+        <v>2</v>
+      </c>
+      <c r="L89" s="27">
+        <v>0</v>
+      </c>
+      <c r="M89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N89" s="27">
+        <v>1</v>
+      </c>
+      <c r="O89" s="27">
+        <v>0</v>
+      </c>
+      <c r="P89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q89" s="27">
+        <v>1</v>
+      </c>
+      <c r="R89" s="27">
+        <v>0</v>
+      </c>
+      <c r="S89" s="28">
+        <v>0</v>
+      </c>
+      <c r="T89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U89" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W89" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y89" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA89" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB89" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC89" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A90" s="27">
+        <v>85100700</v>
+      </c>
+      <c r="B90" s="27">
+        <v>7013</v>
+      </c>
+      <c r="C90" s="28">
+        <v>1</v>
+      </c>
+      <c r="D90" s="28">
+        <v>0</v>
+      </c>
+      <c r="E90" s="27">
+        <v>5100800</v>
+      </c>
+      <c r="F90" s="27" t="s">
+        <v>576</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="H90" s="27"/>
+      <c r="I90" s="27" t="s">
+        <v>585</v>
+      </c>
+      <c r="J90" s="27" t="s">
+        <v>581</v>
+      </c>
+      <c r="K90" s="27">
+        <v>1</v>
+      </c>
+      <c r="L90" s="27">
+        <v>0</v>
+      </c>
+      <c r="M90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N90" s="27">
+        <v>1</v>
+      </c>
+      <c r="O90" s="27">
+        <v>0</v>
+      </c>
+      <c r="P90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q90" s="27">
+        <v>1</v>
+      </c>
+      <c r="R90" s="27">
+        <v>0</v>
+      </c>
+      <c r="S90" s="28">
+        <v>0</v>
+      </c>
+      <c r="T90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U90" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W90" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y90" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z90" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA90" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB90" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC90" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A91" s="27">
+        <v>85100900</v>
+      </c>
+      <c r="B91" s="27">
+        <v>7014</v>
+      </c>
+      <c r="C91" s="28">
+        <v>1</v>
+      </c>
+      <c r="D91" s="28">
+        <v>0</v>
+      </c>
+      <c r="E91" s="27">
+        <v>5101000</v>
+      </c>
+      <c r="F91" s="27" t="s">
+        <v>577</v>
+      </c>
+      <c r="G91" s="13" t="s">
+        <v>578</v>
+      </c>
+      <c r="H91" s="27"/>
+      <c r="I91" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="J91" s="27" t="s">
+        <v>582</v>
+      </c>
+      <c r="K91" s="27">
+        <v>1</v>
+      </c>
+      <c r="L91" s="27">
+        <v>0</v>
+      </c>
+      <c r="M91" s="27" t="s">
+        <v>583</v>
+      </c>
+      <c r="N91" s="27">
+        <v>2</v>
+      </c>
+      <c r="O91" s="27">
+        <v>0</v>
+      </c>
+      <c r="P91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q91" s="27">
+        <v>1</v>
+      </c>
+      <c r="R91" s="27">
+        <v>0</v>
+      </c>
+      <c r="S91" s="28">
+        <v>0</v>
+      </c>
+      <c r="T91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U91" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W91" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y91" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z91" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA91" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB91" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC91" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A92" s="27">
+        <v>85200100</v>
+      </c>
+      <c r="B92" s="27">
+        <v>7015</v>
+      </c>
+      <c r="C92" s="28">
+        <v>1</v>
+      </c>
+      <c r="D92" s="28">
+        <v>0</v>
+      </c>
+      <c r="E92" s="27">
+        <v>5000200</v>
+      </c>
+      <c r="F92" s="27" t="s">
+        <v>538</v>
+      </c>
+      <c r="G92" s="27"/>
+      <c r="H92" s="27"/>
+      <c r="I92" s="27"/>
+      <c r="J92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="K92" s="27">
+        <v>1</v>
+      </c>
+      <c r="L92" s="27">
+        <v>0</v>
+      </c>
+      <c r="M92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N92" s="27">
+        <v>1</v>
+      </c>
+      <c r="O92" s="27">
+        <v>0</v>
+      </c>
+      <c r="P92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q92" s="27">
+        <v>1</v>
+      </c>
+      <c r="R92" s="27">
+        <v>0</v>
+      </c>
+      <c r="S92" s="28">
+        <v>95200101</v>
+      </c>
+      <c r="T92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U92" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W92" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y92" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z92" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA92" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB92" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC92" s="27">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A93" s="27">
+        <v>85200300</v>
+      </c>
+      <c r="B93" s="27">
+        <v>7016</v>
+      </c>
+      <c r="C93" s="28">
+        <v>1</v>
+      </c>
+      <c r="D93" s="28">
+        <v>0</v>
+      </c>
+      <c r="E93" s="27">
+        <v>5200400</v>
+      </c>
+      <c r="F93" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="G93" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="H93" s="27"/>
+      <c r="I93" s="27" t="s">
+        <v>588</v>
+      </c>
+      <c r="J93" s="27" t="s">
+        <v>550</v>
+      </c>
+      <c r="K93" s="27">
+        <v>1</v>
+      </c>
+      <c r="L93" s="27">
+        <v>0</v>
+      </c>
+      <c r="M93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N93" s="27">
+        <v>1</v>
+      </c>
+      <c r="O93" s="27">
+        <v>0</v>
+      </c>
+      <c r="P93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q93" s="27">
+        <v>1</v>
+      </c>
+      <c r="R93" s="27">
+        <v>0</v>
+      </c>
+      <c r="S93" s="28">
+        <v>0</v>
+      </c>
+      <c r="T93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U93" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W93" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y93" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z93" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA93" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB93" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC93" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A94" s="27">
+        <v>85200500</v>
+      </c>
+      <c r="B94" s="27">
+        <v>7017</v>
+      </c>
+      <c r="C94" s="28">
+        <v>1</v>
+      </c>
+      <c r="D94" s="28">
+        <v>0</v>
+      </c>
+      <c r="E94" s="27">
+        <v>5200600</v>
+      </c>
+      <c r="F94" s="27" t="s">
+        <v>548</v>
+      </c>
+      <c r="G94" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H94" s="27"/>
+      <c r="I94" s="27" t="s">
+        <v>589</v>
+      </c>
+      <c r="J94" s="27" t="s">
+        <v>551</v>
+      </c>
+      <c r="K94" s="27">
+        <v>2</v>
+      </c>
+      <c r="L94" s="27">
+        <v>0</v>
+      </c>
+      <c r="M94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N94" s="27">
+        <v>1</v>
+      </c>
+      <c r="O94" s="27">
+        <v>0</v>
+      </c>
+      <c r="P94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q94" s="27">
+        <v>1</v>
+      </c>
+      <c r="R94" s="27">
+        <v>0</v>
+      </c>
+      <c r="S94" s="28">
+        <v>0</v>
+      </c>
+      <c r="T94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="U94" s="27">
+        <v>-1</v>
+      </c>
+      <c r="V94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="W94" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y94" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z94" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA94" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB94" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC94" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A95" s="27">
+        <v>85200700</v>
+      </c>
+      <c r="B95" s="27">
+        <v>7018</v>
+      </c>
+      <c r="C95" s="28">
+        <v>1</v>
+      </c>
+      <c r="D95" s="28">
+        <v>0</v>
+      </c>
+      <c r="E95" s="27">
+        <v>5200800</v>
+      </c>
+      <c r="F95" s="27" t="s">
+        <v>571</v>
+      </c>
+      <c r="G95" s="13"/>
+      <c r="H95" s="27"/>
+      <c r="I95" s="27" t="s">
+        <v>570</v>
+      </c>
+      <c r="J95" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="K95" s="27">
+        <v>1</v>
+      </c>
+      <c r="L95" s="27">
+        <v>0</v>
+      </c>
+      <c r="M95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="N95" s="27">
+        <v>1</v>
+      </c>
+      <c r="O95" s="27">
+        <v>0</v>
+      </c>
+      <c r="P95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q95" s="27">
+        <v>1</v>
+      </c>
+      <c r="R95" s="27">
+        <v>0</v>
+      </c>
+      <c r="S95" s="28">
+        <v>0</v>
+      </c>
+      <c r="T95" s="27" t="s">
+        <v>573</v>
+      </c>
+      <c r="U95" s="27">
+        <v>2000</v>
+      </c>
+      <c r="V95" s="27" t="s">
+        <v>572</v>
+      </c>
+      <c r="W95" s="27">
+        <v>7500</v>
+      </c>
+      <c r="X95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y95" s="27">
+        <v>1</v>
+      </c>
+      <c r="Z95" s="27">
+        <v>1</v>
+      </c>
+      <c r="AA95" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB95" s="27">
+        <v>1</v>
+      </c>
+      <c r="AC95" s="27">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:AC75" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AC77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -9110,7 +11059,7 @@
         <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="5:19" x14ac:dyDescent="0.15">
@@ -9118,7 +11067,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="5:19" x14ac:dyDescent="0.15">
@@ -9126,7 +11075,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" spans="5:19" x14ac:dyDescent="0.15">
@@ -9137,10 +11086,10 @@
         <v>29</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="5:19" x14ac:dyDescent="0.15">
@@ -9148,19 +11097,19 @@
         <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K14" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>515</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="15" spans="5:19" x14ac:dyDescent="0.15">
@@ -9168,19 +11117,19 @@
         <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>2</v>
       </c>
       <c r="K15" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="L15" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="L15" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="S15" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16" spans="5:19" x14ac:dyDescent="0.15">
@@ -9191,19 +11140,19 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="L16" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="S16" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" spans="5:19" x14ac:dyDescent="0.15">
@@ -9214,19 +11163,19 @@
         <v>31</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K17" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>482</v>
-      </c>
       <c r="S17" s="1" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" spans="5:19" x14ac:dyDescent="0.15">
@@ -9240,16 +11189,16 @@
         <v>38</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K18" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="L18" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="L18" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="S18" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" spans="5:19" x14ac:dyDescent="0.15">
@@ -9264,22 +11213,22 @@
         <v>参数4LIST-触发的技能id</v>
       </c>
       <c r="H19" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="J19" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="L19" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="S19" s="1" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="5:19" x14ac:dyDescent="0.15">
@@ -9294,22 +11243,22 @@
         <v>参数5-持续时间（毫秒）</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="L20" s="1" t="s">
-        <v>489</v>
-      </c>
       <c r="S20" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="21" spans="5:19" x14ac:dyDescent="0.15">
@@ -9324,22 +11273,22 @@
         <v>参数6-效果基础命中率（万分比）</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K21" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>491</v>
-      </c>
       <c r="S21" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" spans="5:19" x14ac:dyDescent="0.15">
@@ -9357,19 +11306,19 @@
         <v>106</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K22" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="L22" s="1" t="s">
-        <v>493</v>
-      </c>
       <c r="S22" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="23" spans="5:19" x14ac:dyDescent="0.15">
@@ -9384,22 +11333,22 @@
         <v>参数8-效果触发间隔（毫秒）</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K23" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="L23" s="1" t="s">
-        <v>495</v>
-      </c>
       <c r="S23" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="24" spans="5:19" x14ac:dyDescent="0.15">
@@ -9414,22 +11363,22 @@
         <v>参数9-击中回复生命值-固定值</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K24" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>497</v>
-      </c>
       <c r="S24" s="1" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="5:19" x14ac:dyDescent="0.15">
@@ -9444,22 +11393,22 @@
         <v>参数10-击中回复生命值-自身最大生命值百万分比</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K25" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="L25" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>499</v>
-      </c>
       <c r="S25" s="1" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="26" spans="5:19" x14ac:dyDescent="0.15">
@@ -9474,22 +11423,22 @@
         <v>参数11-击中回复效果提高万分比</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="S26" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="27" spans="5:19" x14ac:dyDescent="0.15">
@@ -9504,22 +11453,22 @@
         <v>参数12-击杀回复生命-固定值</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K27" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="S27" s="1" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28" spans="5:19" x14ac:dyDescent="0.15">
@@ -9534,19 +11483,19 @@
         <v>参数13-击杀回复生命-自身最大生命值百万分比</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J28" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="29" spans="5:19" x14ac:dyDescent="0.15">
@@ -9561,19 +11510,19 @@
         <v>参数14-击杀回复生命-目标最大生命值百万分比</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K29" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="L29" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>246</v>
@@ -9591,22 +11540,22 @@
         <v>参数15-击杀回复生命效果提高万分比</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K30" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="L30" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>510</v>
-      </c>
       <c r="S30" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" spans="5:19" x14ac:dyDescent="0.15">
@@ -9621,22 +11570,22 @@
         <v>参数16-获得护盾-固定值</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>512</v>
-      </c>
       <c r="S31" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="32" spans="5:19" x14ac:dyDescent="0.15">
@@ -9644,80 +11593,80 @@
         <v>103</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数17-获得护盾-自身生命百万分比</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="L32" s="1" t="s">
         <v>513</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="33" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E33" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G33" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数18-获得护盾-自身已损失生命万分比</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="34" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E34" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数19-获得护盾效果提高万分比</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="35" spans="5:9" x14ac:dyDescent="0.15">
       <c r="E35" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>参数20-技能增加-固定值</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="36" spans="5:9" x14ac:dyDescent="0.15">
@@ -9726,10 +11675,10 @@
         <v>参数21-技能增加-万分比</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37" spans="5:9" x14ac:dyDescent="0.15">
@@ -9738,10 +11687,10 @@
         <v>参数22-技能增加-普通攻击范围万分比</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="38" spans="5:9" x14ac:dyDescent="0.15">
@@ -9750,10 +11699,10 @@
         <v>参数25LIST-攻击提高-攻击的元素类型</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="39" spans="5:9" x14ac:dyDescent="0.15">
@@ -9762,10 +11711,10 @@
         <v>参数25LIST-攻击提高-固定值</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="40" spans="5:9" x14ac:dyDescent="0.15">
@@ -9774,10 +11723,10 @@
         <v>参数25LIST-攻击提高-万分比</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41" spans="5:9" x14ac:dyDescent="0.15">
@@ -9786,10 +11735,10 @@
         <v>参数28-防御提高-固定值</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="42" spans="5:9" x14ac:dyDescent="0.15">
@@ -9798,10 +11747,10 @@
         <v>参数29-防御提高-万分比</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43" spans="5:9" x14ac:dyDescent="0.15">
@@ -9810,10 +11759,10 @@
         <v>参数30-生命上限提高-固定值</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="44" spans="5:9" x14ac:dyDescent="0.15">
@@ -9822,10 +11771,10 @@
         <v>参数31-生命上限提高-百万分比</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="45" spans="5:9" x14ac:dyDescent="0.15">
@@ -9834,10 +11783,10 @@
         <v>参数32-攻击速度提高-万分比</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="46" spans="5:9" x14ac:dyDescent="0.15">
@@ -9846,10 +11795,10 @@
         <v>参数33-移动速度提高-万分比</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="47" spans="5:9" x14ac:dyDescent="0.15">
@@ -9858,10 +11807,10 @@
         <v>参数34-攻击范围提高-万分比</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="48" spans="5:9" x14ac:dyDescent="0.15">
@@ -9870,10 +11819,10 @@
         <v>参数35-攻击目标数量提高-固定值</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="49" spans="7:8" x14ac:dyDescent="0.15">
@@ -9882,7 +11831,7 @@
         <v>参数36-</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="7:8" x14ac:dyDescent="0.15">
@@ -9891,7 +11840,7 @@
         <v>参数37-</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="51" spans="7:8" x14ac:dyDescent="0.15">
@@ -9900,7 +11849,7 @@
         <v>参数38-</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="52" spans="7:8" x14ac:dyDescent="0.15">
@@ -9909,7 +11858,7 @@
         <v>参数39-</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="53" spans="7:8" x14ac:dyDescent="0.15">
@@ -9918,7 +11867,7 @@
         <v>参数40-</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" spans="7:8" x14ac:dyDescent="0.15">
@@ -9927,7 +11876,7 @@
         <v>参数41-</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="55" spans="7:8" x14ac:dyDescent="0.15">
@@ -9936,7 +11885,7 @@
         <v>参数42-</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="56" spans="7:8" x14ac:dyDescent="0.15">
@@ -9945,7 +11894,7 @@
         <v>参数41-</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="57" spans="7:8" x14ac:dyDescent="0.15">
@@ -9954,7 +11903,7 @@
         <v>参数42-</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="58" spans="7:8" x14ac:dyDescent="0.15">
@@ -9963,7 +11912,7 @@
         <v>参数43-</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="59" spans="7:8" x14ac:dyDescent="0.15">
@@ -9972,7 +11921,7 @@
         <v>参数44-</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="60" spans="7:8" x14ac:dyDescent="0.15">
@@ -9981,7 +11930,7 @@
         <v>参数45-</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="61" spans="7:8" x14ac:dyDescent="0.15">
@@ -9990,7 +11939,7 @@
         <v>参数46-</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="62" spans="7:8" x14ac:dyDescent="0.15">
@@ -9999,7 +11948,7 @@
         <v>参数47-</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="63" spans="7:8" x14ac:dyDescent="0.15">
@@ -10008,7 +11957,7 @@
         <v>参数48-</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="7:8" x14ac:dyDescent="0.15">
@@ -10017,7 +11966,7 @@
         <v>参数49-</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="65" spans="7:8" x14ac:dyDescent="0.15">
@@ -10026,7 +11975,7 @@
         <v>参数50-</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="66" spans="7:8" x14ac:dyDescent="0.15">
@@ -10035,7 +11984,7 @@
         <v>参数51-</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="67" spans="7:8" x14ac:dyDescent="0.15">
@@ -10044,7 +11993,7 @@
         <v>参数52-</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="68" spans="7:8" x14ac:dyDescent="0.15">
@@ -10053,7 +12002,7 @@
         <v>参数53-</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="69" spans="7:8" x14ac:dyDescent="0.15">
@@ -10062,7 +12011,7 @@
         <v>参数54-</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="70" spans="7:8" x14ac:dyDescent="0.15">
@@ -10071,7 +12020,7 @@
         <v>参数55-</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="71" spans="7:8" x14ac:dyDescent="0.15">
@@ -10080,7 +12029,7 @@
         <v>参数56-</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
